--- a/p6_deployment/data/italy/missing/data_preparation/df_integrated_missing.xlsx
+++ b/p6_deployment/data/italy/missing/data_preparation/df_integrated_missing.xlsx
@@ -834,12 +834,12 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>EJLKYOz</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>tjY4uUe</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="W2" t="n">
@@ -883,22 +883,22 @@
         <v>83</v>
       </c>
       <c r="AI2" t="n">
-        <v>24.81818181818182</v>
+        <v>24.8</v>
       </c>
       <c r="AJ2" t="n">
-        <v>181.7272727272727</v>
+        <v>183.2</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.636363636363636</v>
+        <v>1.7</v>
       </c>
       <c r="AL2" t="n">
-        <v>74.18181818181819</v>
+        <v>73.8</v>
       </c>
       <c r="AM2" t="n">
-        <v>12290909.09090909</v>
+        <v>11670000</v>
       </c>
       <c r="AN2" t="n">
-        <v>79.54545454545455</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="AO2" t="n">
         <v>26.04</v>
@@ -919,65 +919,37 @@
         <v>78.92</v>
       </c>
       <c r="AU2" t="n">
-        <v>25.59259259259259</v>
+        <v>25.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>181.6666666666667</v>
+        <v>181.5416666666667</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.444444444444444</v>
+        <v>1.458333333333333</v>
       </c>
       <c r="AX2" t="n">
-        <v>74.88888888888889</v>
+        <v>74.58333333333333</v>
       </c>
       <c r="AY2" t="n">
-        <v>10618518.51851852</v>
+        <v>10445833.33333333</v>
       </c>
       <c r="AZ2" t="n">
-        <v>78.88888888888889</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>31</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>184</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>2</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>159</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>28500000</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>159</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>25</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>181.5</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>2</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>152</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>21000000</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>160</v>
-      </c>
+        <v>79.04166666666667</v>
+      </c>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1054,12 +1026,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>MLVBCoY</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>xjigzK8</t>
+          <t>xjigzK81</t>
         </is>
       </c>
       <c r="W3" t="n">
@@ -1103,22 +1075,22 @@
         <v>76.54545454545455</v>
       </c>
       <c r="AI3" t="n">
-        <v>25.1</v>
+        <v>24.88888888888889</v>
       </c>
       <c r="AJ3" t="n">
-        <v>181.3</v>
+        <v>180.3333333333333</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.9</v>
+        <v>1.888888888888889</v>
       </c>
       <c r="AL3" t="n">
-        <v>78</v>
+        <v>77.44444444444444</v>
       </c>
       <c r="AM3" t="n">
-        <v>21450000</v>
+        <v>19555555.55555556</v>
       </c>
       <c r="AN3" t="n">
-        <v>81.40000000000001</v>
+        <v>81</v>
       </c>
       <c r="AO3" t="n">
         <v>25.92592592592593</v>
@@ -1274,12 +1246,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>n10g3Kf</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>A1CicVE</t>
+          <t>A1CicVEU</t>
         </is>
       </c>
       <c r="W4" t="n">
@@ -1398,25 +1370,25 @@
         <v>227</v>
       </c>
       <c r="BH4" t="n">
-        <v>27.4</v>
+        <v>26.25</v>
       </c>
       <c r="BI4" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BL4" t="n">
-        <v>375</v>
+        <v>297</v>
       </c>
       <c r="BM4" t="n">
-        <v>37200000</v>
+        <v>30200000</v>
       </c>
       <c r="BN4" t="n">
-        <v>384</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5">
@@ -1494,12 +1466,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Qu12kvX</t>
+          <t>Qu12kvXf</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>AcgUMf0</t>
+          <t>AcgUMf0E</t>
         </is>
       </c>
       <c r="W5" t="n">
@@ -1561,22 +1533,22 @@
         <v>77.81818181818181</v>
       </c>
       <c r="AO5" t="n">
-        <v>26.2</v>
+        <v>26.69565217391304</v>
       </c>
       <c r="AP5" t="n">
-        <v>181.45</v>
+        <v>180.6086956521739</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2</v>
+        <v>2.130434782608696</v>
       </c>
       <c r="AR5" t="n">
-        <v>76.75</v>
+        <v>77.30434782608695</v>
       </c>
       <c r="AS5" t="n">
-        <v>19073000</v>
+        <v>19846086.95652174</v>
       </c>
       <c r="AT5" t="n">
-        <v>80.15000000000001</v>
+        <v>80.26086956521739</v>
       </c>
       <c r="AU5" t="n">
         <v>23.80769230769231</v>
@@ -1714,12 +1686,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>S8Ygn9M</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>j32a3mq</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="W6" t="n">
@@ -1781,22 +1753,22 @@
         <v>83.72727272727273</v>
       </c>
       <c r="AO6" t="n">
-        <v>23.38888888888889</v>
+        <v>23.33333333333333</v>
       </c>
       <c r="AP6" t="n">
-        <v>184.3888888888889</v>
+        <v>183.7619047619048</v>
       </c>
       <c r="AQ6" t="n">
         <v>1</v>
       </c>
       <c r="AR6" t="n">
-        <v>68.88888888888889</v>
+        <v>68.9047619047619</v>
       </c>
       <c r="AS6" t="n">
-        <v>2679166.666666667</v>
+        <v>2696428.571428571</v>
       </c>
       <c r="AT6" t="n">
-        <v>75</v>
+        <v>75.14285714285714</v>
       </c>
       <c r="AU6" t="n">
         <v>28.68965517241379</v>
@@ -1920,12 +1892,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>EJLKYOz</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>4IdjsvY</t>
+          <t>4IdjsvY2</t>
         </is>
       </c>
       <c r="W7" t="n">
@@ -2005,22 +1977,22 @@
         <v>77.92</v>
       </c>
       <c r="AU7" t="n">
-        <v>24.83333333333333</v>
+        <v>24.77272727272727</v>
       </c>
       <c r="AV7" t="n">
-        <v>184.375</v>
+        <v>184.8636363636364</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.208333333333333</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="AX7" t="n">
-        <v>72</v>
+        <v>71.40909090909091</v>
       </c>
       <c r="AY7" t="n">
-        <v>5979166.666666667</v>
+        <v>4863636.363636363</v>
       </c>
       <c r="AZ7" t="n">
-        <v>76.16666666666667</v>
+        <v>75.95454545454545</v>
       </c>
       <c r="BA7" t="n">
         <v>30.33333333333333</v>
@@ -2140,12 +2112,12 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>MVSS7qF</t>
+          <t>MVSS7qFe</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>KtGrCa5</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
       <c r="W8" t="n">
@@ -2167,22 +2139,22 @@
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
-        <v>26.8</v>
+        <v>26.45454545454545</v>
       </c>
       <c r="AD8" t="n">
-        <v>182.1</v>
+        <v>182.0909090909091</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.7</v>
+        <v>1.636363636363636</v>
       </c>
       <c r="AF8" t="n">
-        <v>79.8</v>
+        <v>79.18181818181819</v>
       </c>
       <c r="AG8" t="n">
-        <v>30010000</v>
+        <v>27872727.27272727</v>
       </c>
       <c r="AH8" t="n">
-        <v>81.59999999999999</v>
+        <v>81.63636363636364</v>
       </c>
       <c r="AI8" t="n">
         <v>23.72727272727273</v>
@@ -2221,22 +2193,22 @@
         <v>81.09090909090909</v>
       </c>
       <c r="AU8" t="n">
-        <v>22.62962962962963</v>
+        <v>22.73076923076923</v>
       </c>
       <c r="AV8" t="n">
-        <v>185.1851851851852</v>
+        <v>185.1538461538462</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
       </c>
       <c r="AX8" t="n">
-        <v>67.74074074074075</v>
+        <v>67.69230769230769</v>
       </c>
       <c r="AY8" t="n">
-        <v>2596296.296296296</v>
+        <v>2576923.076923077</v>
       </c>
       <c r="AZ8" t="n">
-        <v>75.07407407407408</v>
+        <v>74.96153846153847</v>
       </c>
       <c r="BA8" t="n">
         <v>30.5</v>
@@ -2356,12 +2328,12 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>A72TGDl</t>
+          <t>A72TGDlt</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>rTrn0h4</t>
+          <t>rTrn0h4a</t>
         </is>
       </c>
       <c r="W9" t="n">
@@ -2387,76 +2359,76 @@
         </is>
       </c>
       <c r="AC9" t="n">
-        <v>27.9</v>
+        <v>27.54545454545455</v>
       </c>
       <c r="AD9" t="n">
-        <v>182.7</v>
+        <v>183.1818181818182</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.2</v>
+        <v>2.181818181818182</v>
       </c>
       <c r="AF9" t="n">
-        <v>80</v>
+        <v>80.54545454545455</v>
       </c>
       <c r="AG9" t="n">
-        <v>29165000</v>
+        <v>35831818.18181818</v>
       </c>
       <c r="AH9" t="n">
-        <v>82.59999999999999</v>
+        <v>83.36363636363636</v>
       </c>
       <c r="AI9" t="n">
-        <v>26.4</v>
+        <v>25.33333333333333</v>
       </c>
       <c r="AJ9" t="n">
-        <v>184.2</v>
+        <v>184.6666666666667</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AL9" t="n">
-        <v>71.59999999999999</v>
+        <v>70.88888888888889</v>
       </c>
       <c r="AM9" t="n">
-        <v>3390000</v>
+        <v>3233333.333333333</v>
       </c>
       <c r="AN9" t="n">
-        <v>75.8</v>
+        <v>75.55555555555556</v>
       </c>
       <c r="AO9" t="n">
-        <v>25.96153846153846</v>
+        <v>25.88888888888889</v>
       </c>
       <c r="AP9" t="n">
-        <v>186.9615384615385</v>
+        <v>187</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.538461538461539</v>
+        <v>1.555555555555556</v>
       </c>
       <c r="AR9" t="n">
-        <v>74.11538461538461</v>
+        <v>74.55555555555556</v>
       </c>
       <c r="AS9" t="n">
-        <v>11104807.69230769</v>
+        <v>14489814.81481482</v>
       </c>
       <c r="AT9" t="n">
-        <v>78.92307692307692</v>
+        <v>79.37037037037037</v>
       </c>
       <c r="AU9" t="n">
-        <v>24.42105263157895</v>
+        <v>23.77777777777778</v>
       </c>
       <c r="AV9" t="n">
-        <v>183.6315789473684</v>
+        <v>183.8333333333333</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.157894736842105</v>
+        <v>1.055555555555556</v>
       </c>
       <c r="AX9" t="n">
-        <v>68.21052631578948</v>
+        <v>67.66666666666667</v>
       </c>
       <c r="AY9" t="n">
-        <v>2755263.157894737</v>
+        <v>2641666.666666667</v>
       </c>
       <c r="AZ9" t="n">
-        <v>75.47368421052632</v>
+        <v>75.33333333333333</v>
       </c>
       <c r="BA9" t="n">
         <v>25.5</v>
@@ -2576,12 +2548,12 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>tYVGfTo</t>
+          <t>tYVGfTo2</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>619UPLr</t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="W10" t="n">
@@ -2621,22 +2593,22 @@
         <v>82.25</v>
       </c>
       <c r="AI10" t="n">
-        <v>25.90909090909091</v>
+        <v>25.6</v>
       </c>
       <c r="AJ10" t="n">
-        <v>184.8181818181818</v>
+        <v>184</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.454545454545455</v>
+        <v>1.4</v>
       </c>
       <c r="AL10" t="n">
-        <v>73.09090909090909</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="AM10" t="n">
-        <v>7190909.090909091</v>
+        <v>7440000</v>
       </c>
       <c r="AN10" t="n">
-        <v>78</v>
+        <v>78.3</v>
       </c>
       <c r="AO10" t="n">
         <v>25.69565217391304</v>
@@ -2792,12 +2764,12 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>tSiEeKv</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>bBhpZV2</t>
+          <t>bBhpZV2s</t>
         </is>
       </c>
       <c r="W11" t="n">
@@ -2994,12 +2966,12 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>zFLwLRZ</t>
+          <t>zFLwLRZS</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>tjY4uUe</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="W12" t="n">
@@ -3079,22 +3051,22 @@
         <v>73.13793103448276</v>
       </c>
       <c r="AU12" t="n">
-        <v>24.96551724137931</v>
+        <v>24.72</v>
       </c>
       <c r="AV12" t="n">
-        <v>180.551724137931</v>
+        <v>181.96</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.586206896551724</v>
+        <v>1.56</v>
       </c>
       <c r="AX12" t="n">
-        <v>75.34482758620689</v>
+        <v>74.92</v>
       </c>
       <c r="AY12" t="n">
-        <v>13617241.37931035</v>
+        <v>13416000</v>
       </c>
       <c r="AZ12" t="n">
-        <v>79.68965517241379</v>
+        <v>79.95999999999999</v>
       </c>
       <c r="BA12" t="n">
         <v>25</v>
@@ -3214,12 +3186,12 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>bBhpZV2</t>
+          <t>bBhpZV2s</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>tYVGfTo</t>
+          <t>tYVGfTo2</t>
         </is>
       </c>
       <c r="W13" t="n">
@@ -3430,12 +3402,12 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>rTrn0h4</t>
+          <t>rTrn0h4a</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>S8Ygn9M</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
       <c r="W14" t="n">
@@ -3497,40 +3469,40 @@
         <v>77.18181818181819</v>
       </c>
       <c r="AO14" t="n">
-        <v>26.88888888888889</v>
+        <v>25.06666666666667</v>
       </c>
       <c r="AP14" t="n">
-        <v>181.4444444444445</v>
+        <v>181.7333333333333</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AR14" t="n">
-        <v>72.61111111111111</v>
+        <v>71.53333333333333</v>
       </c>
       <c r="AS14" t="n">
-        <v>4312500</v>
+        <v>4215000</v>
       </c>
       <c r="AT14" t="n">
-        <v>77</v>
+        <v>76.8</v>
       </c>
       <c r="AU14" t="n">
-        <v>24.47619047619047</v>
+        <v>24.29166666666667</v>
       </c>
       <c r="AV14" t="n">
-        <v>182.952380952381</v>
+        <v>182.5833333333333</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
       </c>
       <c r="AX14" t="n">
-        <v>70.61904761904762</v>
+        <v>70.41666666666667</v>
       </c>
       <c r="AY14" t="n">
-        <v>3307142.857142857</v>
+        <v>3243750</v>
       </c>
       <c r="AZ14" t="n">
-        <v>75.23809523809524</v>
+        <v>75.33333333333333</v>
       </c>
       <c r="BA14" t="n">
         <v>27.55555555555556</v>
@@ -3650,12 +3622,12 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>xjigzK8</t>
+          <t>xjigzK81</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>tSiEeKv</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="W15" t="n">
@@ -3713,22 +3685,22 @@
         <v>77.90000000000001</v>
       </c>
       <c r="AO15" t="n">
-        <v>26.39285714285714</v>
+        <v>26.32</v>
       </c>
       <c r="AP15" t="n">
-        <v>184.3571428571429</v>
+        <v>183.68</v>
       </c>
       <c r="AQ15" t="n">
-        <v>2.142857142857143</v>
+        <v>2.16</v>
       </c>
       <c r="AR15" t="n">
-        <v>78.60714285714286</v>
+        <v>78.08</v>
       </c>
       <c r="AS15" t="n">
-        <v>26226785.71428571</v>
+        <v>24754000</v>
       </c>
       <c r="AT15" t="n">
-        <v>81.96428571428571</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="AU15" t="n">
         <v>26.07142857142857</v>
@@ -3866,12 +3838,12 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>j32a3mq</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Qu12kvX</t>
+          <t>Qu12kvXf</t>
         </is>
       </c>
       <c r="W16" t="n">
@@ -3951,22 +3923,22 @@
         <v>81.27586206896552</v>
       </c>
       <c r="AU16" t="n">
-        <v>25.91304347826087</v>
+        <v>26.38461538461538</v>
       </c>
       <c r="AV16" t="n">
-        <v>182.0434782608696</v>
+        <v>181.2307692307692</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.739130434782609</v>
+        <v>1.884615384615385</v>
       </c>
       <c r="AX16" t="n">
-        <v>76</v>
+        <v>76.57692307692308</v>
       </c>
       <c r="AY16" t="n">
-        <v>17333043.47826087</v>
+        <v>18217692.30769231</v>
       </c>
       <c r="AZ16" t="n">
-        <v>79.08695652173913</v>
+        <v>79.30769230769231</v>
       </c>
       <c r="BA16" t="inlineStr"/>
       <c r="BB16" t="inlineStr"/>
@@ -4072,12 +4044,12 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>619UPLr</t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>n10g3Kf</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
       <c r="W17" t="n">
@@ -4099,22 +4071,22 @@
         </is>
       </c>
       <c r="AC17" t="n">
-        <v>25.4</v>
+        <v>25</v>
       </c>
       <c r="AD17" t="n">
-        <v>183.8</v>
+        <v>182.7777777777778</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.4</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AF17" t="n">
-        <v>72.7</v>
+        <v>72.44444444444444</v>
       </c>
       <c r="AG17" t="n">
-        <v>7550000</v>
+        <v>7866666.666666667</v>
       </c>
       <c r="AH17" t="n">
-        <v>77.40000000000001</v>
+        <v>77.66666666666667</v>
       </c>
       <c r="AI17" t="n">
         <v>24.18181818181818</v>
@@ -4288,12 +4260,12 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>A1CicVE</t>
+          <t>A1CicVEU</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>MLVBCoY</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="W18" t="n">
@@ -4391,25 +4363,25 @@
         <v>75.35714285714286</v>
       </c>
       <c r="BA18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB18" t="n">
-        <v>182.8</v>
+        <v>180.75</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BE18" t="n">
-        <v>377</v>
+        <v>299</v>
       </c>
       <c r="BF18" t="n">
-        <v>38800000</v>
+        <v>31800000</v>
       </c>
       <c r="BG18" t="n">
-        <v>386</v>
+        <v>308</v>
       </c>
       <c r="BH18" t="n">
         <v>30.5</v>
@@ -4508,12 +4480,12 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>AcgUMf0</t>
+          <t>AcgUMf0E</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>zFLwLRZ</t>
+          <t>zFLwLRZS</t>
         </is>
       </c>
       <c r="W19" t="n">
@@ -4728,12 +4700,12 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>4IdjsvY</t>
+          <t>4IdjsvY2</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>A72TGDl</t>
+          <t>A72TGDlt</t>
         </is>
       </c>
       <c r="W20" t="n">
@@ -4759,22 +4731,22 @@
         </is>
       </c>
       <c r="AC20" t="n">
-        <v>25.6</v>
+        <v>26</v>
       </c>
       <c r="AD20" t="n">
-        <v>187.2</v>
+        <v>186.7272727272727</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.2</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="AF20" t="n">
-        <v>75.40000000000001</v>
+        <v>75.54545454545455</v>
       </c>
       <c r="AG20" t="n">
-        <v>11930000</v>
+        <v>11618181.81818182</v>
       </c>
       <c r="AH20" t="n">
-        <v>79.40000000000001</v>
+        <v>79.18181818181819</v>
       </c>
       <c r="AI20" t="n">
         <v>23.8</v>
@@ -4795,40 +4767,40 @@
         <v>83.59999999999999</v>
       </c>
       <c r="AO20" t="n">
-        <v>24.95454545454545</v>
+        <v>24.9</v>
       </c>
       <c r="AP20" t="n">
-        <v>185.0909090909091</v>
+        <v>185.7</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.136363636363636</v>
+        <v>1.2</v>
       </c>
       <c r="AR20" t="n">
-        <v>72.36363636363636</v>
+        <v>71.75</v>
       </c>
       <c r="AS20" t="n">
-        <v>6095454.545454546</v>
+        <v>4880000</v>
       </c>
       <c r="AT20" t="n">
-        <v>76.40909090909091</v>
+        <v>76.2</v>
       </c>
       <c r="AU20" t="n">
-        <v>26.95</v>
+        <v>26.56521739130435</v>
       </c>
       <c r="AV20" t="n">
-        <v>184.2</v>
+        <v>184.695652173913</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.9</v>
+        <v>1.91304347826087</v>
       </c>
       <c r="AX20" t="n">
-        <v>75.8</v>
+        <v>77.1304347826087</v>
       </c>
       <c r="AY20" t="n">
-        <v>13952500</v>
+        <v>25502173.91304348</v>
       </c>
       <c r="AZ20" t="n">
-        <v>80.15000000000001</v>
+        <v>81.56521739130434</v>
       </c>
       <c r="BA20" t="n">
         <v>22.33333333333333</v>
@@ -4948,12 +4920,12 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>KtGrCa5</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>ryme5Xs</t>
+          <t>ryme5Xs1</t>
         </is>
       </c>
       <c r="W21" t="n">
@@ -5011,22 +4983,22 @@
         <v>79.90909090909091</v>
       </c>
       <c r="AO21" t="n">
-        <v>23.44444444444444</v>
+        <v>23.57692307692308</v>
       </c>
       <c r="AP21" t="n">
-        <v>183.1481481481482</v>
+        <v>183.0384615384615</v>
       </c>
       <c r="AQ21" t="n">
         <v>1</v>
       </c>
       <c r="AR21" t="n">
-        <v>67.44444444444444</v>
+        <v>67.38461538461539</v>
       </c>
       <c r="AS21" t="n">
-        <v>2033333.333333333</v>
+        <v>1992307.692307692</v>
       </c>
       <c r="AT21" t="n">
-        <v>73.77777777777777</v>
+        <v>73.61538461538461</v>
       </c>
       <c r="AU21" t="n">
         <v>24.33333333333333</v>
@@ -5164,12 +5136,12 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>tjY4uUe</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>MVSS7qF</t>
+          <t>MVSS7qFe</t>
         </is>
       </c>
       <c r="W22" t="n">
@@ -5195,58 +5167,58 @@
         </is>
       </c>
       <c r="AC22" t="n">
-        <v>26.90909090909091</v>
+        <v>27.22222222222222</v>
       </c>
       <c r="AD22" t="n">
-        <v>181.7272727272727</v>
+        <v>182.5555555555555</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.545454545454545</v>
+        <v>1.555555555555556</v>
       </c>
       <c r="AF22" t="n">
-        <v>78.27272727272727</v>
+        <v>78.44444444444444</v>
       </c>
       <c r="AG22" t="n">
-        <v>15909090.90909091</v>
+        <v>16055555.55555556</v>
       </c>
       <c r="AH22" t="n">
-        <v>80.36363636363636</v>
+        <v>80.55555555555556</v>
       </c>
       <c r="AI22" t="n">
-        <v>26.3</v>
+        <v>26</v>
       </c>
       <c r="AJ22" t="n">
-        <v>182.5</v>
+        <v>182.4545454545455</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.5</v>
+        <v>1.454545454545455</v>
       </c>
       <c r="AL22" t="n">
-        <v>79.2</v>
+        <v>78.63636363636364</v>
       </c>
       <c r="AM22" t="n">
-        <v>27060000</v>
+        <v>25190909.09090909</v>
       </c>
       <c r="AN22" t="n">
-        <v>81</v>
+        <v>81.09090909090909</v>
       </c>
       <c r="AO22" t="n">
-        <v>25.18518518518519</v>
+        <v>24.8</v>
       </c>
       <c r="AP22" t="n">
-        <v>180.3333333333333</v>
+        <v>181.84</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.703703703703704</v>
+        <v>1.72</v>
       </c>
       <c r="AR22" t="n">
-        <v>74.62962962962963</v>
+        <v>74.28</v>
       </c>
       <c r="AS22" t="n">
-        <v>11114814.81481482</v>
+        <v>11264000</v>
       </c>
       <c r="AT22" t="n">
-        <v>78.96296296296296</v>
+        <v>79.52</v>
       </c>
       <c r="AU22" t="n">
         <v>24.33333333333333</v>
@@ -5384,12 +5356,12 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>tjY4uUe</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>619UPLr</t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="W23" t="n">
@@ -5411,76 +5383,76 @@
       </c>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="n">
-        <v>26</v>
+        <v>25.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>184.6</v>
+        <v>185.3</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AF23" t="n">
-        <v>77</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="AG23" t="n">
-        <v>14460000</v>
+        <v>15060000</v>
       </c>
       <c r="AH23" t="n">
-        <v>79.90000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="AI23" t="n">
-        <v>25.3</v>
+        <v>24.88888888888889</v>
       </c>
       <c r="AJ23" t="n">
-        <v>182.7</v>
+        <v>181.5555555555555</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.3</v>
+        <v>1.222222222222222</v>
       </c>
       <c r="AL23" t="n">
-        <v>73.90000000000001</v>
+        <v>73.77777777777777</v>
       </c>
       <c r="AM23" t="n">
-        <v>9110000</v>
+        <v>9600000</v>
       </c>
       <c r="AN23" t="n">
-        <v>78</v>
+        <v>78.33333333333333</v>
       </c>
       <c r="AO23" t="n">
-        <v>25.74074074074074</v>
+        <v>25.69565217391304</v>
       </c>
       <c r="AP23" t="n">
-        <v>180.8148148148148</v>
+        <v>181.1739130434783</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.333333333333333</v>
+        <v>1.347826086956522</v>
       </c>
       <c r="AR23" t="n">
-        <v>74.37037037037037</v>
+        <v>73.82608695652173</v>
       </c>
       <c r="AS23" t="n">
-        <v>10103703.7037037</v>
+        <v>9491304.347826088</v>
       </c>
       <c r="AT23" t="n">
-        <v>78.70370370370371</v>
+        <v>78.73913043478261</v>
       </c>
       <c r="AU23" t="n">
-        <v>26.81481481481481</v>
+        <v>26.73076923076923</v>
       </c>
       <c r="AV23" t="n">
-        <v>182.7037037037037</v>
+        <v>182.3076923076923</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.37037037037037</v>
+        <v>1.346153846153846</v>
       </c>
       <c r="AX23" t="n">
-        <v>72</v>
+        <v>71.88461538461539</v>
       </c>
       <c r="AY23" t="n">
-        <v>4128703.703703704</v>
+        <v>4106730.769230769</v>
       </c>
       <c r="AZ23" t="n">
-        <v>76.5925925925926</v>
+        <v>76.65384615384616</v>
       </c>
       <c r="BA23" t="n">
         <v>24</v>
@@ -5600,12 +5572,12 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>KtGrCa5</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>A1CicVE</t>
+          <t>A1CicVEU</t>
         </is>
       </c>
       <c r="W24" t="n">
@@ -5663,22 +5635,22 @@
         <v>77.54545454545455</v>
       </c>
       <c r="AO24" t="n">
-        <v>22.04347826086957</v>
+        <v>22.13636363636364</v>
       </c>
       <c r="AP24" t="n">
-        <v>184.9130434782609</v>
+        <v>184.8636363636364</v>
       </c>
       <c r="AQ24" t="n">
         <v>1</v>
       </c>
       <c r="AR24" t="n">
-        <v>66.30434782608695</v>
+        <v>66.18181818181819</v>
       </c>
       <c r="AS24" t="n">
-        <v>2006521.739130435</v>
+        <v>1956818.181818182</v>
       </c>
       <c r="AT24" t="n">
-        <v>74.78260869565217</v>
+        <v>74.63636363636364</v>
       </c>
       <c r="AU24" t="n">
         <v>25.07407407407407</v>
@@ -5720,25 +5692,25 @@
         <v>377</v>
       </c>
       <c r="BH24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BI24" t="n">
-        <v>182.8</v>
+        <v>180.75</v>
       </c>
       <c r="BJ24" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="BK24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BL24" t="n">
-        <v>377</v>
+        <v>299</v>
       </c>
       <c r="BM24" t="n">
-        <v>38800000</v>
+        <v>31800000</v>
       </c>
       <c r="BN24" t="n">
-        <v>386</v>
+        <v>308</v>
       </c>
     </row>
     <row r="25">
@@ -5816,12 +5788,12 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>EJLKYOz</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>xjigzK8</t>
+          <t>xjigzK81</t>
         </is>
       </c>
       <c r="W25" t="n">
@@ -5865,22 +5837,22 @@
         <v>82</v>
       </c>
       <c r="AI25" t="n">
-        <v>26.5</v>
+        <v>26.44444444444444</v>
       </c>
       <c r="AJ25" t="n">
-        <v>182.8</v>
+        <v>182</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.2</v>
+        <v>2.222222222222222</v>
       </c>
       <c r="AL25" t="n">
-        <v>79.09999999999999</v>
+        <v>78.66666666666667</v>
       </c>
       <c r="AM25" t="n">
-        <v>22750000</v>
+        <v>21000000</v>
       </c>
       <c r="AN25" t="n">
-        <v>81.3</v>
+        <v>80.88888888888889</v>
       </c>
       <c r="AO25" t="n">
         <v>24.76923076923077</v>
@@ -6036,12 +6008,12 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>lUkw2EZ</t>
+          <t>lUkw2EZn</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>rTrn0h4</t>
+          <t>rTrn0h4a</t>
         </is>
       </c>
       <c r="W26" t="n">
@@ -6160,25 +6132,25 @@
         <v>324</v>
       </c>
       <c r="BH26" t="n">
-        <v>29.25</v>
+        <v>28.28571428571428</v>
       </c>
       <c r="BI26" t="n">
-        <v>183.5</v>
+        <v>184</v>
       </c>
       <c r="BJ26" t="n">
-        <v>1.625</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="BK26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BL26" t="n">
-        <v>599</v>
+        <v>521</v>
       </c>
       <c r="BM26" t="n">
-        <v>58500000</v>
+        <v>53700000</v>
       </c>
       <c r="BN26" t="n">
-        <v>613</v>
+        <v>535</v>
       </c>
     </row>
     <row r="27">
@@ -6256,12 +6228,12 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>tSiEeKv</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>AcgUMf0</t>
+          <t>AcgUMf0E</t>
         </is>
       </c>
       <c r="W27" t="n">
@@ -6472,12 +6444,12 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>S8Ygn9M</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>4IdjsvY</t>
+          <t>4IdjsvY2</t>
         </is>
       </c>
       <c r="W28" t="n">
@@ -6521,58 +6493,58 @@
         <v>75.54545454545455</v>
       </c>
       <c r="AI28" t="n">
-        <v>26</v>
+        <v>26.3</v>
       </c>
       <c r="AJ28" t="n">
-        <v>187.2</v>
+        <v>187.4</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AL28" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="AM28" t="n">
-        <v>10930000</v>
+        <v>10280000</v>
       </c>
       <c r="AN28" t="n">
-        <v>79.09999999999999</v>
+        <v>79</v>
       </c>
       <c r="AO28" t="n">
-        <v>24.25</v>
+        <v>24.11111111111111</v>
       </c>
       <c r="AP28" t="n">
-        <v>182.5833333333333</v>
+        <v>182.2962962962963</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.041666666666667</v>
+        <v>1.037037037037037</v>
       </c>
       <c r="AR28" t="n">
-        <v>70.75</v>
+        <v>70.55555555555556</v>
       </c>
       <c r="AS28" t="n">
-        <v>3431250</v>
+        <v>3361111.111111111</v>
       </c>
       <c r="AT28" t="n">
-        <v>75.54166666666667</v>
+        <v>75.5925925925926</v>
       </c>
       <c r="AU28" t="n">
-        <v>25</v>
+        <v>25.23809523809524</v>
       </c>
       <c r="AV28" t="n">
-        <v>185</v>
+        <v>184.8571428571429</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.35</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="AX28" t="n">
-        <v>71.3</v>
+        <v>71.57142857142857</v>
       </c>
       <c r="AY28" t="n">
-        <v>5418750</v>
+        <v>5565476.19047619</v>
       </c>
       <c r="AZ28" t="n">
-        <v>75</v>
+        <v>75.0952380952381</v>
       </c>
       <c r="BA28" t="n">
         <v>26.66666666666667</v>
@@ -6692,12 +6664,12 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>Qu12kvX</t>
+          <t>Qu12kvXf</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>MLVBCoY</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="W29" t="n">
@@ -6723,22 +6695,22 @@
         </is>
       </c>
       <c r="AC29" t="n">
-        <v>27.8</v>
+        <v>28</v>
       </c>
       <c r="AD29" t="n">
-        <v>183</v>
+        <v>182.2727272727273</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AF29" t="n">
-        <v>78.3</v>
+        <v>78.54545454545455</v>
       </c>
       <c r="AG29" t="n">
-        <v>19870000</v>
+        <v>20336363.63636364</v>
       </c>
       <c r="AH29" t="n">
-        <v>79.5</v>
+        <v>79.63636363636364</v>
       </c>
       <c r="AI29" t="n">
         <v>26.27272727272727</v>
@@ -6759,22 +6731,22 @@
         <v>76.54545454545455</v>
       </c>
       <c r="AO29" t="n">
-        <v>25.45454545454545</v>
+        <v>25.65217391304348</v>
       </c>
       <c r="AP29" t="n">
-        <v>182.2727272727273</v>
+        <v>181.9565217391304</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.772727272727273</v>
+        <v>1.826086956521739</v>
       </c>
       <c r="AR29" t="n">
-        <v>76.63636363636364</v>
+        <v>76.82608695652173</v>
       </c>
       <c r="AS29" t="n">
-        <v>17307272.72727273</v>
+        <v>17641739.13043478</v>
       </c>
       <c r="AT29" t="n">
-        <v>80.40909090909091</v>
+        <v>80.43478260869566</v>
       </c>
       <c r="AU29" t="n">
         <v>24.5</v>
@@ -6912,12 +6884,12 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>A72TGDl</t>
+          <t>A72TGDlt</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>zFLwLRZ</t>
+          <t>zFLwLRZS</t>
         </is>
       </c>
       <c r="W30" t="n">
@@ -6979,22 +6951,22 @@
         <v>76.90909090909091</v>
       </c>
       <c r="AO30" t="n">
-        <v>24.45833333333333</v>
+        <v>24.40740740740741</v>
       </c>
       <c r="AP30" t="n">
-        <v>183.375</v>
+        <v>183.8888888888889</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.666666666666667</v>
+        <v>1.703703703703704</v>
       </c>
       <c r="AR30" t="n">
-        <v>77.20833333333333</v>
+        <v>78.18518518518519</v>
       </c>
       <c r="AS30" t="n">
-        <v>25576041.66666667</v>
+        <v>34123148.14814815</v>
       </c>
       <c r="AT30" t="n">
-        <v>82.5</v>
+        <v>83.44444444444444</v>
       </c>
       <c r="AU30" t="n">
         <v>27.03571428571428</v>
@@ -7132,12 +7104,12 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>MVSS7qF</t>
+          <t>MVSS7qFe</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>bBhpZV2</t>
+          <t>bBhpZV2s</t>
         </is>
       </c>
       <c r="W31" t="n">
@@ -7199,22 +7171,22 @@
         <v>79.36363636363636</v>
       </c>
       <c r="AO31" t="n">
-        <v>25.19230769230769</v>
+        <v>25.11111111111111</v>
       </c>
       <c r="AP31" t="n">
-        <v>180.3461538461538</v>
+        <v>180.4074074074074</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.461538461538461</v>
+        <v>1.444444444444444</v>
       </c>
       <c r="AR31" t="n">
-        <v>76.19230769230769</v>
+        <v>76.07407407407408</v>
       </c>
       <c r="AS31" t="n">
-        <v>16131730.76923077</v>
+        <v>15775000</v>
       </c>
       <c r="AT31" t="n">
-        <v>79.73076923076923</v>
+        <v>79.81481481481481</v>
       </c>
       <c r="AU31" t="n">
         <v>23.24137931034483</v>
@@ -7352,12 +7324,12 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>n10g3Kf</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>j32a3mq</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="W32" t="n">
@@ -7572,12 +7544,12 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>A1CicVE</t>
+          <t>A1CicVEU</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>MVSS7qF</t>
+          <t>MVSS7qFe</t>
         </is>
       </c>
       <c r="W33" t="n">
@@ -7621,22 +7593,22 @@
         <v>77.63636363636364</v>
       </c>
       <c r="AI33" t="n">
-        <v>26.3</v>
+        <v>26</v>
       </c>
       <c r="AJ33" t="n">
-        <v>183.2</v>
+        <v>183.0909090909091</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.7</v>
+        <v>1.636363636363636</v>
       </c>
       <c r="AL33" t="n">
-        <v>80.40000000000001</v>
+        <v>79.72727272727273</v>
       </c>
       <c r="AM33" t="n">
-        <v>31640000</v>
+        <v>29354545.45454545</v>
       </c>
       <c r="AN33" t="n">
-        <v>82.5</v>
+        <v>82.45454545454545</v>
       </c>
       <c r="AO33" t="n">
         <v>25.04761904761905</v>
@@ -7675,25 +7647,25 @@
         <v>78.61111111111111</v>
       </c>
       <c r="BA33" t="n">
-        <v>27</v>
+        <v>26.28571428571428</v>
       </c>
       <c r="BB33" t="n">
-        <v>183.125</v>
+        <v>182</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.25</v>
+        <v>1.285714285714286</v>
       </c>
       <c r="BD33" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BE33" t="n">
-        <v>599</v>
+        <v>521</v>
       </c>
       <c r="BF33" t="n">
-        <v>54600000</v>
+        <v>47600000</v>
       </c>
       <c r="BG33" t="n">
-        <v>618</v>
+        <v>540</v>
       </c>
       <c r="BH33" t="n">
         <v>26</v>
@@ -7792,12 +7764,12 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>rTrn0h4</t>
+          <t>rTrn0h4a</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>EJLKYOz</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="W34" t="n">
@@ -8012,12 +7984,12 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>xjigzK8</t>
+          <t>xjigzK81</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>lUkw2EZ</t>
+          <t>lUkw2EZn</t>
         </is>
       </c>
       <c r="W35" t="n">
@@ -8079,22 +8051,22 @@
         <v>84.09999999999999</v>
       </c>
       <c r="AO35" t="n">
-        <v>25.40740740740741</v>
+        <v>25.34615384615385</v>
       </c>
       <c r="AP35" t="n">
-        <v>183.0740740740741</v>
+        <v>182.8076923076923</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.962962962962963</v>
+        <v>1.961538461538461</v>
       </c>
       <c r="AR35" t="n">
-        <v>77.55555555555556</v>
+        <v>77.34615384615384</v>
       </c>
       <c r="AS35" t="n">
-        <v>19234259.25925926</v>
+        <v>18493269.23076923</v>
       </c>
       <c r="AT35" t="n">
-        <v>82</v>
+        <v>81.88461538461539</v>
       </c>
       <c r="AU35" t="n">
         <v>25.30434782608696</v>
@@ -8218,12 +8190,12 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>A72TGDl</t>
+          <t>A72TGDlt</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>tSiEeKv</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="W36" t="n">
@@ -8245,22 +8217,22 @@
       </c>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="n">
-        <v>26.9</v>
+        <v>26.63636363636364</v>
       </c>
       <c r="AD36" t="n">
-        <v>182.1</v>
+        <v>182.6363636363636</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.1</v>
+        <v>2.090909090909091</v>
       </c>
       <c r="AF36" t="n">
-        <v>80.5</v>
+        <v>81</v>
       </c>
       <c r="AG36" t="n">
-        <v>30640000</v>
+        <v>37172727.27272727</v>
       </c>
       <c r="AH36" t="n">
-        <v>83.5</v>
+        <v>84.18181818181819</v>
       </c>
       <c r="AI36" t="n">
         <v>25.2</v>
@@ -8281,22 +8253,22 @@
         <v>77.90000000000001</v>
       </c>
       <c r="AO36" t="n">
-        <v>22.5</v>
+        <v>22.57894736842105</v>
       </c>
       <c r="AP36" t="n">
-        <v>184.4444444444445</v>
+        <v>184.6315789473684</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.222222222222222</v>
+        <v>1.263157894736842</v>
       </c>
       <c r="AR36" t="n">
-        <v>73.5</v>
+        <v>74.15789473684211</v>
       </c>
       <c r="AS36" t="n">
-        <v>13740277.77777778</v>
+        <v>18411842.10526316</v>
       </c>
       <c r="AT36" t="n">
-        <v>81.11111111111111</v>
+        <v>81.63157894736842</v>
       </c>
       <c r="AU36" t="n">
         <v>27.58823529411765</v>
@@ -8434,12 +8406,12 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>MLVBCoY</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>n10g3Kf</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
       <c r="W37" t="n">
@@ -8654,12 +8626,12 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>S8Ygn9M</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>tjY4uUe</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="W38" t="n">
@@ -8703,58 +8675,58 @@
         <v>75.81818181818181</v>
       </c>
       <c r="AI38" t="n">
-        <v>26.4</v>
+        <v>26.1</v>
       </c>
       <c r="AJ38" t="n">
-        <v>183.4</v>
+        <v>184.5</v>
       </c>
       <c r="AK38" t="n">
         <v>1.5</v>
       </c>
       <c r="AL38" t="n">
-        <v>76.2</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="AM38" t="n">
-        <v>11550000</v>
+        <v>11950000</v>
       </c>
       <c r="AN38" t="n">
-        <v>78.3</v>
+        <v>78.8</v>
       </c>
       <c r="AO38" t="n">
-        <v>24.29166666666667</v>
+        <v>24.14814814814815</v>
       </c>
       <c r="AP38" t="n">
-        <v>183.5833333333333</v>
+        <v>183.1851851851852</v>
       </c>
       <c r="AQ38" t="n">
         <v>1</v>
       </c>
       <c r="AR38" t="n">
-        <v>71.20833333333333</v>
+        <v>70.96296296296296</v>
       </c>
       <c r="AS38" t="n">
-        <v>3785416.666666667</v>
+        <v>3675925.925925926</v>
       </c>
       <c r="AT38" t="n">
-        <v>76.16666666666667</v>
+        <v>76.14814814814815</v>
       </c>
       <c r="AU38" t="n">
-        <v>26.35714285714286</v>
+        <v>26.60869565217391</v>
       </c>
       <c r="AV38" t="n">
-        <v>180.0357142857143</v>
+        <v>180.3478260869565</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.678571428571429</v>
+        <v>1.782608695652174</v>
       </c>
       <c r="AX38" t="n">
-        <v>75.85714285714286</v>
+        <v>75.52173913043478</v>
       </c>
       <c r="AY38" t="n">
-        <v>11439285.71428571</v>
+        <v>10578260.86956522</v>
       </c>
       <c r="AZ38" t="n">
-        <v>79.35714285714286</v>
+        <v>79.21739130434783</v>
       </c>
       <c r="BA38" t="n">
         <v>25.66666666666667</v>
@@ -8874,12 +8846,12 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>zFLwLRZ</t>
+          <t>zFLwLRZS</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>KtGrCa5</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
       <c r="W39" t="n">
@@ -9090,12 +9062,12 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>AcgUMf0</t>
+          <t>AcgUMf0E</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>j32a3mq</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="W40" t="n">
@@ -9310,12 +9282,12 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>619UPLr</t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>Qu12kvX</t>
+          <t>Qu12kvXf</t>
         </is>
       </c>
       <c r="W41" t="n">
@@ -9337,40 +9309,40 @@
         </is>
       </c>
       <c r="AC41" t="n">
-        <v>24.6</v>
+        <v>24.11111111111111</v>
       </c>
       <c r="AD41" t="n">
-        <v>183.2</v>
+        <v>182.1111111111111</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.3</v>
+        <v>1.222222222222222</v>
       </c>
       <c r="AF41" t="n">
-        <v>72.90000000000001</v>
+        <v>72.66666666666667</v>
       </c>
       <c r="AG41" t="n">
-        <v>8720000</v>
+        <v>9166666.666666666</v>
       </c>
       <c r="AH41" t="n">
-        <v>78.7</v>
+        <v>79.11111111111111</v>
       </c>
       <c r="AI41" t="n">
-        <v>27.9</v>
+        <v>28.09090909090909</v>
       </c>
       <c r="AJ41" t="n">
-        <v>183.9</v>
+        <v>183.0909090909091</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AL41" t="n">
-        <v>78.8</v>
+        <v>79</v>
       </c>
       <c r="AM41" t="n">
-        <v>22370000</v>
+        <v>22609090.90909091</v>
       </c>
       <c r="AN41" t="n">
-        <v>80</v>
+        <v>80.09090909090909</v>
       </c>
       <c r="AO41" t="n">
         <v>27.44</v>
@@ -9391,22 +9363,22 @@
         <v>75.2</v>
       </c>
       <c r="AU41" t="n">
-        <v>26.8695652173913</v>
+        <v>27</v>
       </c>
       <c r="AV41" t="n">
-        <v>182.6086956521739</v>
+        <v>182.2916666666667</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.782608695652174</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="AX41" t="n">
-        <v>78.04347826086956</v>
+        <v>78.16666666666667</v>
       </c>
       <c r="AY41" t="n">
-        <v>17700000</v>
+        <v>18004166.66666667</v>
       </c>
       <c r="AZ41" t="n">
-        <v>80.30434782608695</v>
+        <v>80.33333333333333</v>
       </c>
       <c r="BA41" t="n">
         <v>26.5</v>
@@ -9526,12 +9498,12 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>4IdjsvY</t>
+          <t>4IdjsvY2</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>bBhpZV2</t>
+          <t>bBhpZV2s</t>
         </is>
       </c>
       <c r="W42" t="n">
@@ -9557,22 +9529,22 @@
         </is>
       </c>
       <c r="AC42" t="n">
-        <v>25.7</v>
+        <v>26</v>
       </c>
       <c r="AD42" t="n">
-        <v>187.1</v>
+        <v>187.3</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AF42" t="n">
-        <v>76.7</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="AG42" t="n">
-        <v>14740000</v>
+        <v>14090000</v>
       </c>
       <c r="AH42" t="n">
-        <v>80.2</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="AI42" t="n">
         <v>24.45454545454545</v>
@@ -9593,22 +9565,22 @@
         <v>80.72727272727273</v>
       </c>
       <c r="AO42" t="n">
-        <v>24.61111111111111</v>
+        <v>24.47058823529412</v>
       </c>
       <c r="AP42" t="n">
-        <v>182.8888888888889</v>
+        <v>183.0588235294118</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.388888888888889</v>
+        <v>1.411764705882353</v>
       </c>
       <c r="AR42" t="n">
-        <v>71.44444444444444</v>
+        <v>71.05882352941177</v>
       </c>
       <c r="AS42" t="n">
-        <v>5022222.222222222</v>
+        <v>4435294.117647059</v>
       </c>
       <c r="AT42" t="n">
-        <v>75.55555555555556</v>
+        <v>75.41176470588235</v>
       </c>
       <c r="AU42" t="n">
         <v>23.07142857142857</v>
@@ -9746,12 +9718,12 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>tSiEeKv</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>zFLwLRZ</t>
+          <t>zFLwLRZS</t>
         </is>
       </c>
       <c r="W43" t="n">
@@ -9962,12 +9934,12 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>tjY4uUe</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>AcgUMf0</t>
+          <t>AcgUMf0E</t>
         </is>
       </c>
       <c r="W44" t="n">
@@ -9993,22 +9965,22 @@
         </is>
       </c>
       <c r="AC44" t="n">
-        <v>25.1</v>
+        <v>24.66666666666667</v>
       </c>
       <c r="AD44" t="n">
-        <v>181.8</v>
+        <v>182.2222222222222</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.5</v>
+        <v>1.444444444444444</v>
       </c>
       <c r="AF44" t="n">
-        <v>74.8</v>
+        <v>74.44444444444444</v>
       </c>
       <c r="AG44" t="n">
-        <v>9500000</v>
+        <v>9666666.666666666</v>
       </c>
       <c r="AH44" t="n">
-        <v>78.90000000000001</v>
+        <v>79.55555555555556</v>
       </c>
       <c r="AI44" t="n">
         <v>25.27272727272727</v>
@@ -10029,22 +10001,22 @@
         <v>77.81818181818181</v>
       </c>
       <c r="AO44" t="n">
-        <v>25.20689655172414</v>
+        <v>25.20833333333333</v>
       </c>
       <c r="AP44" t="n">
-        <v>180.6206896551724</v>
+        <v>182.5416666666667</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.655172413793103</v>
+        <v>1.75</v>
       </c>
       <c r="AR44" t="n">
-        <v>75.10344827586206</v>
+        <v>74.54166666666667</v>
       </c>
       <c r="AS44" t="n">
-        <v>13837931.03448276</v>
+        <v>13137500</v>
       </c>
       <c r="AT44" t="n">
-        <v>79.48275862068965</v>
+        <v>79.29166666666667</v>
       </c>
       <c r="AU44" t="n">
         <v>23.77777777777778</v>
@@ -10182,12 +10154,12 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>EJLKYOz</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>MLVBCoY</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="W45" t="n">
@@ -10402,12 +10374,12 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>MVSS7qF</t>
+          <t>MVSS7qFe</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>xjigzK8</t>
+          <t>xjigzK81</t>
         </is>
       </c>
       <c r="W46" t="n">
@@ -10451,40 +10423,40 @@
         <v>82.63636363636364</v>
       </c>
       <c r="AI46" t="n">
-        <v>26.8</v>
+        <v>26.77777777777778</v>
       </c>
       <c r="AJ46" t="n">
-        <v>184</v>
+        <v>183.3333333333333</v>
       </c>
       <c r="AK46" t="n">
         <v>2</v>
       </c>
       <c r="AL46" t="n">
-        <v>79.3</v>
+        <v>78.88888888888889</v>
       </c>
       <c r="AM46" t="n">
-        <v>24800000</v>
+        <v>23277777.77777778</v>
       </c>
       <c r="AN46" t="n">
-        <v>81.5</v>
+        <v>81.11111111111111</v>
       </c>
       <c r="AO46" t="n">
-        <v>24.33333333333333</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="AP46" t="n">
-        <v>179.5238095238095</v>
+        <v>179.8333333333333</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.428571428571429</v>
+        <v>1.375</v>
       </c>
       <c r="AR46" t="n">
-        <v>75.14285714285714</v>
+        <v>74.875</v>
       </c>
       <c r="AS46" t="n">
-        <v>16917857.14285714</v>
+        <v>15615625</v>
       </c>
       <c r="AT46" t="n">
-        <v>79.95238095238095</v>
+        <v>80.20833333333333</v>
       </c>
       <c r="AU46" t="n">
         <v>23.91666666666667</v>
@@ -10511,27 +10483,13 @@
       <c r="BE46" t="inlineStr"/>
       <c r="BF46" t="inlineStr"/>
       <c r="BG46" t="inlineStr"/>
-      <c r="BH46" t="n">
-        <v>30.25</v>
-      </c>
-      <c r="BI46" t="n">
-        <v>187.75</v>
-      </c>
-      <c r="BJ46" t="n">
-        <v>3</v>
-      </c>
-      <c r="BK46" t="n">
-        <v>4</v>
-      </c>
-      <c r="BL46" t="n">
-        <v>324</v>
-      </c>
-      <c r="BM46" t="n">
-        <v>87000000</v>
-      </c>
-      <c r="BN46" t="n">
-        <v>324</v>
-      </c>
+      <c r="BH46" t="inlineStr"/>
+      <c r="BI46" t="inlineStr"/>
+      <c r="BJ46" t="inlineStr"/>
+      <c r="BK46" t="inlineStr"/>
+      <c r="BL46" t="inlineStr"/>
+      <c r="BM46" t="inlineStr"/>
+      <c r="BN46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
@@ -10608,12 +10566,12 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>bBhpZV2</t>
+          <t>bBhpZV2s</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>A1CicVE</t>
+          <t>A1CicVEU</t>
         </is>
       </c>
       <c r="W47" t="n">
@@ -10828,12 +10786,12 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>j32a3mq</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>4IdjsvY</t>
+          <t>4IdjsvY2</t>
         </is>
       </c>
       <c r="W48" t="n">
@@ -10877,22 +10835,22 @@
         <v>84.81818181818181</v>
       </c>
       <c r="AI48" t="n">
-        <v>25.2</v>
+        <v>25.63636363636364</v>
       </c>
       <c r="AJ48" t="n">
-        <v>186.5</v>
+        <v>186.0909090909091</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.3</v>
+        <v>1.363636363636364</v>
       </c>
       <c r="AL48" t="n">
-        <v>76.2</v>
+        <v>76.27272727272727</v>
       </c>
       <c r="AM48" t="n">
-        <v>13920000</v>
+        <v>13427272.72727273</v>
       </c>
       <c r="AN48" t="n">
-        <v>80.59999999999999</v>
+        <v>80.27272727272727</v>
       </c>
       <c r="AO48" t="n">
         <v>27.67857142857143</v>
@@ -10913,22 +10871,22 @@
         <v>81.60714285714286</v>
       </c>
       <c r="AU48" t="n">
-        <v>26.3125</v>
+        <v>26.42857142857143</v>
       </c>
       <c r="AV48" t="n">
-        <v>185.8125</v>
+        <v>186.7857142857143</v>
       </c>
       <c r="AW48" t="n">
-        <v>1.125</v>
+        <v>1.214285714285714</v>
       </c>
       <c r="AX48" t="n">
-        <v>72.4375</v>
+        <v>71.57142857142857</v>
       </c>
       <c r="AY48" t="n">
-        <v>5956250</v>
+        <v>4200000</v>
       </c>
       <c r="AZ48" t="n">
-        <v>75</v>
+        <v>74.5</v>
       </c>
       <c r="BA48" t="n">
         <v>27</v>
@@ -11048,12 +11006,12 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>Qu12kvX</t>
+          <t>Qu12kvXf</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>S8Ygn9M</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
       <c r="W49" t="n">
@@ -11079,22 +11037,22 @@
         </is>
       </c>
       <c r="AC49" t="n">
-        <v>26</v>
+        <v>26.36363636363636</v>
       </c>
       <c r="AD49" t="n">
-        <v>184.2</v>
+        <v>183.3636363636364</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.7</v>
+        <v>1.818181818181818</v>
       </c>
       <c r="AF49" t="n">
-        <v>77.7</v>
+        <v>78</v>
       </c>
       <c r="AG49" t="n">
-        <v>20770000</v>
+        <v>21154545.45454545</v>
       </c>
       <c r="AH49" t="n">
-        <v>80.40000000000001</v>
+        <v>80.45454545454545</v>
       </c>
       <c r="AI49" t="n">
         <v>24.45454545454545</v>
@@ -11115,40 +11073,40 @@
         <v>77</v>
       </c>
       <c r="AO49" t="n">
-        <v>27.60869565217391</v>
+        <v>27.70833333333333</v>
       </c>
       <c r="AP49" t="n">
-        <v>182.0434782608696</v>
+        <v>181.75</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.869565217391304</v>
+        <v>1.916666666666667</v>
       </c>
       <c r="AR49" t="n">
-        <v>77.21739130434783</v>
+        <v>77.375</v>
       </c>
       <c r="AS49" t="n">
-        <v>17141739.13043478</v>
+        <v>17469166.66666667</v>
       </c>
       <c r="AT49" t="n">
-        <v>79.47826086956522</v>
+        <v>79.54166666666667</v>
       </c>
       <c r="AU49" t="n">
-        <v>25.07407407407407</v>
+        <v>25</v>
       </c>
       <c r="AV49" t="n">
-        <v>182.6666666666667</v>
+        <v>182.5714285714286</v>
       </c>
       <c r="AW49" t="n">
-        <v>1.111111111111111</v>
+        <v>1.107142857142857</v>
       </c>
       <c r="AX49" t="n">
-        <v>70.88888888888889</v>
+        <v>70.82142857142857</v>
       </c>
       <c r="AY49" t="n">
-        <v>3257407.407407407</v>
+        <v>3241071.428571429</v>
       </c>
       <c r="AZ49" t="n">
-        <v>74.77777777777777</v>
+        <v>74.82142857142857</v>
       </c>
       <c r="BA49" t="n">
         <v>25.5</v>
@@ -11268,12 +11226,12 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>lUkw2EZ</t>
+          <t>lUkw2EZn</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>A72TGDl</t>
+          <t>A72TGDlt</t>
         </is>
       </c>
       <c r="W50" t="n">
@@ -11317,22 +11275,22 @@
         <v>84.33333333333333</v>
       </c>
       <c r="AI50" t="n">
-        <v>26</v>
+        <v>25.81818181818182</v>
       </c>
       <c r="AJ50" t="n">
-        <v>185.1</v>
+        <v>185.3636363636364</v>
       </c>
       <c r="AK50" t="n">
-        <v>1.7</v>
+        <v>1.727272727272727</v>
       </c>
       <c r="AL50" t="n">
-        <v>78</v>
+        <v>78.72727272727273</v>
       </c>
       <c r="AM50" t="n">
-        <v>17190000</v>
+        <v>24945454.54545455</v>
       </c>
       <c r="AN50" t="n">
-        <v>81.7</v>
+        <v>82.54545454545455</v>
       </c>
       <c r="AO50" t="n">
         <v>24.68181818181818</v>
@@ -11488,12 +11446,12 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>KtGrCa5</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>619UPLr</t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="W51" t="n">
@@ -11529,22 +11487,22 @@
         <v>77.72727272727273</v>
       </c>
       <c r="AI51" t="n">
-        <v>24.81818181818182</v>
+        <v>24.4</v>
       </c>
       <c r="AJ51" t="n">
-        <v>182.8181818181818</v>
+        <v>181.8</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.272727272727273</v>
+        <v>1.2</v>
       </c>
       <c r="AL51" t="n">
-        <v>72.45454545454545</v>
+        <v>72.2</v>
       </c>
       <c r="AM51" t="n">
-        <v>6236363.636363637</v>
+        <v>6390000</v>
       </c>
       <c r="AN51" t="n">
-        <v>78</v>
+        <v>78.3</v>
       </c>
       <c r="AO51" t="n">
         <v>23.68</v>
@@ -11700,12 +11658,12 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>n10g3Kf</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>rTrn0h4</t>
+          <t>rTrn0h4a</t>
         </is>
       </c>
       <c r="W52" t="n">
@@ -11824,25 +11782,25 @@
         <v>220</v>
       </c>
       <c r="BH52" t="n">
-        <v>30.42857142857143</v>
+        <v>29.5</v>
       </c>
       <c r="BI52" t="n">
-        <v>183.8571428571429</v>
+        <v>184.5</v>
       </c>
       <c r="BJ52" t="n">
-        <v>1.714285714285714</v>
+        <v>1.5</v>
       </c>
       <c r="BK52" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BL52" t="n">
-        <v>532</v>
+        <v>454</v>
       </c>
       <c r="BM52" t="n">
-        <v>57100000</v>
+        <v>52300000</v>
       </c>
       <c r="BN52" t="n">
-        <v>539</v>
+        <v>461</v>
       </c>
     </row>
     <row r="53">
@@ -11920,12 +11878,12 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>A1CicVE</t>
+          <t>A1CicVEU</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>xjigzK8</t>
+          <t>xjigzK81</t>
         </is>
       </c>
       <c r="W53" t="n">
@@ -11987,40 +11945,40 @@
         <v>81.2</v>
       </c>
       <c r="AO53" t="n">
-        <v>26.04761904761905</v>
+        <v>25.75</v>
       </c>
       <c r="AP53" t="n">
-        <v>182.9047619047619</v>
+        <v>182.5</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.047619047619048</v>
+        <v>1.05</v>
       </c>
       <c r="AR53" t="n">
-        <v>70.71428571428571</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="AS53" t="n">
-        <v>2961904.761904762</v>
+        <v>2760000</v>
       </c>
       <c r="AT53" t="n">
-        <v>74.80952380952381</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="AU53" t="n">
-        <v>27.4</v>
+        <v>27.42857142857143</v>
       </c>
       <c r="AV53" t="n">
-        <v>185.0888888888889</v>
+        <v>184.7380952380952</v>
       </c>
       <c r="AW53" t="n">
-        <v>2.244444444444444</v>
+        <v>2.261904761904762</v>
       </c>
       <c r="AX53" t="n">
-        <v>78.86666666666666</v>
+        <v>78.57142857142857</v>
       </c>
       <c r="AY53" t="n">
-        <v>22118888.88888889</v>
+        <v>20948809.52380952</v>
       </c>
       <c r="AZ53" t="n">
-        <v>81.2</v>
+        <v>80.92857142857143</v>
       </c>
       <c r="BA53" t="n">
         <v>27</v>
@@ -12126,12 +12084,12 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>A72TGDl</t>
+          <t>A72TGDlt</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>j32a3mq</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="W54" t="n">
@@ -12157,22 +12115,22 @@
         </is>
       </c>
       <c r="AC54" t="n">
-        <v>24.3</v>
+        <v>24.27272727272727</v>
       </c>
       <c r="AD54" t="n">
-        <v>183.9</v>
+        <v>184.2727272727273</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.8</v>
+        <v>1.818181818181818</v>
       </c>
       <c r="AF54" t="n">
-        <v>80.5</v>
+        <v>81</v>
       </c>
       <c r="AG54" t="n">
-        <v>35350000</v>
+        <v>41454545.45454545</v>
       </c>
       <c r="AH54" t="n">
-        <v>84.5</v>
+        <v>85.09090909090909</v>
       </c>
       <c r="AI54" t="n">
         <v>28.81818181818182</v>
@@ -12332,12 +12290,12 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>xjigzK8</t>
+          <t>xjigzK81</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>bBhpZV2</t>
+          <t>bBhpZV2s</t>
         </is>
       </c>
       <c r="W55" t="n">
@@ -12363,22 +12321,22 @@
         </is>
       </c>
       <c r="AC55" t="n">
-        <v>27.18181818181818</v>
+        <v>27.2</v>
       </c>
       <c r="AD55" t="n">
-        <v>183.4545454545455</v>
+        <v>182.8</v>
       </c>
       <c r="AE55" t="n">
-        <v>2.272727272727273</v>
+        <v>2.3</v>
       </c>
       <c r="AF55" t="n">
-        <v>79.45454545454545</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="AG55" t="n">
-        <v>24590909.09090909</v>
+        <v>23200000</v>
       </c>
       <c r="AH55" t="n">
-        <v>80.63636363636364</v>
+        <v>80.2</v>
       </c>
       <c r="AI55" t="n">
         <v>25</v>
@@ -12552,12 +12510,12 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>619UPLr</t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>EJLKYOz</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="W56" t="n">
@@ -12579,22 +12537,22 @@
         </is>
       </c>
       <c r="AC56" t="n">
-        <v>25.7</v>
+        <v>25.33333333333333</v>
       </c>
       <c r="AD56" t="n">
-        <v>183.7</v>
+        <v>182.6666666666667</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.4</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AF56" t="n">
-        <v>74</v>
+        <v>73.88888888888889</v>
       </c>
       <c r="AG56" t="n">
-        <v>9040000</v>
+        <v>9522222.222222222</v>
       </c>
       <c r="AH56" t="n">
-        <v>77.8</v>
+        <v>78.11111111111111</v>
       </c>
       <c r="AI56" t="n">
         <v>24.90909090909091</v>
@@ -12768,12 +12726,12 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>rTrn0h4</t>
+          <t>rTrn0h4a</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>tjY4uUe</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="W57" t="n">
@@ -12799,76 +12757,76 @@
         </is>
       </c>
       <c r="AC57" t="n">
-        <v>26.66666666666667</v>
+        <v>25.5</v>
       </c>
       <c r="AD57" t="n">
-        <v>185.7777777777778</v>
+        <v>186.5</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.444444444444444</v>
+        <v>1.25</v>
       </c>
       <c r="AF57" t="n">
-        <v>72</v>
+        <v>71.25</v>
       </c>
       <c r="AG57" t="n">
-        <v>3025000</v>
+        <v>2803125</v>
       </c>
       <c r="AH57" t="n">
-        <v>77.77777777777777</v>
+        <v>77.75</v>
       </c>
       <c r="AI57" t="n">
-        <v>26</v>
+        <v>25.7</v>
       </c>
       <c r="AJ57" t="n">
-        <v>181.9</v>
+        <v>183</v>
       </c>
       <c r="AK57" t="n">
         <v>1.5</v>
       </c>
       <c r="AL57" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="AM57" t="n">
-        <v>10130000</v>
+        <v>10530000</v>
       </c>
       <c r="AN57" t="n">
-        <v>79.09999999999999</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="AO57" t="n">
-        <v>24.6</v>
+        <v>24.125</v>
       </c>
       <c r="AP57" t="n">
-        <v>185.28</v>
+        <v>185.5</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.12</v>
+        <v>1.041666666666667</v>
       </c>
       <c r="AR57" t="n">
-        <v>69.95999999999999</v>
+        <v>69.625</v>
       </c>
       <c r="AS57" t="n">
-        <v>3333000</v>
+        <v>3271875</v>
       </c>
       <c r="AT57" t="n">
-        <v>75.88</v>
+        <v>75.79166666666667</v>
       </c>
       <c r="AU57" t="n">
-        <v>25.64</v>
+        <v>25.72222222222222</v>
       </c>
       <c r="AV57" t="n">
-        <v>182.36</v>
+        <v>184.6666666666667</v>
       </c>
       <c r="AW57" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AX57" t="n">
-        <v>75.28</v>
+        <v>74.38888888888889</v>
       </c>
       <c r="AY57" t="n">
-        <v>11500000</v>
+        <v>9861111.111111112</v>
       </c>
       <c r="AZ57" t="n">
-        <v>79.04000000000001</v>
+        <v>78.77777777777777</v>
       </c>
       <c r="BA57" t="n">
         <v>27.83333333333333</v>
@@ -12988,12 +12946,12 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>KdJpmvQ</t>
+          <t>KdJpmvQM</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>n10g3Kf</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
       <c r="W58" t="n">
@@ -13019,22 +12977,22 @@
         </is>
       </c>
       <c r="AC58" t="n">
-        <v>26.2</v>
+        <v>26.54545454545455</v>
       </c>
       <c r="AD58" t="n">
-        <v>185.7</v>
+        <v>185.3636363636364</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.3</v>
+        <v>1.363636363636364</v>
       </c>
       <c r="AF58" t="n">
-        <v>76.3</v>
+        <v>76.36363636363636</v>
       </c>
       <c r="AG58" t="n">
-        <v>12910000</v>
+        <v>12509090.90909091</v>
       </c>
       <c r="AH58" t="n">
-        <v>79.09999999999999</v>
+        <v>78.90909090909091</v>
       </c>
       <c r="AI58" t="n">
         <v>24.09090909090909</v>
@@ -13055,22 +13013,22 @@
         <v>76.54545454545455</v>
       </c>
       <c r="AO58" t="n">
-        <v>24.94117647058824</v>
+        <v>24.5</v>
       </c>
       <c r="AP58" t="n">
-        <v>184.2352941176471</v>
+        <v>185.1428571428571</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.176470588235294</v>
+        <v>1.214285714285714</v>
       </c>
       <c r="AR58" t="n">
-        <v>72.29411764705883</v>
+        <v>71.07142857142857</v>
       </c>
       <c r="AS58" t="n">
-        <v>6305882.352941177</v>
+        <v>4442857.142857143</v>
       </c>
       <c r="AT58" t="n">
-        <v>76.52941176470588</v>
+        <v>76.21428571428571</v>
       </c>
       <c r="AU58" t="n">
         <v>23.11538461538462</v>
@@ -13208,12 +13166,12 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>AcgUMf0</t>
+          <t>AcgUMf0E</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>KtGrCa5</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
       <c r="W59" t="n">
@@ -13424,12 +13382,12 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>S8Ygn9M</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>EDkXRoL</t>
+          <t>EDkXRoLT</t>
         </is>
       </c>
       <c r="W60" t="n">
@@ -13455,22 +13413,22 @@
         </is>
       </c>
       <c r="AC60" t="n">
-        <v>24.8</v>
+        <v>24.63636363636364</v>
       </c>
       <c r="AD60" t="n">
-        <v>185</v>
+        <v>184.5454545454545</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.1</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="AF60" t="n">
-        <v>72.5</v>
+        <v>72.18181818181819</v>
       </c>
       <c r="AG60" t="n">
-        <v>4560000</v>
+        <v>4400000</v>
       </c>
       <c r="AH60" t="n">
-        <v>76.5</v>
+        <v>76.45454545454545</v>
       </c>
       <c r="AI60" t="n">
         <v>25</v>
@@ -13491,40 +13449,40 @@
         <v>78.09090909090909</v>
       </c>
       <c r="AO60" t="n">
-        <v>24.42307692307692</v>
+        <v>24.37037037037037</v>
       </c>
       <c r="AP60" t="n">
-        <v>181.3846153846154</v>
+        <v>181.3333333333333</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.153846153846154</v>
+        <v>1.148148148148148</v>
       </c>
       <c r="AR60" t="n">
-        <v>70.84615384615384</v>
+        <v>70.77777777777777</v>
       </c>
       <c r="AS60" t="n">
-        <v>3455769.230769231</v>
+        <v>3431481.481481481</v>
       </c>
       <c r="AT60" t="n">
-        <v>75.42307692307692</v>
+        <v>75.44444444444444</v>
       </c>
       <c r="AU60" t="n">
-        <v>25.41176470588235</v>
+        <v>25</v>
       </c>
       <c r="AV60" t="n">
-        <v>185.2352941176471</v>
+        <v>184.875</v>
       </c>
       <c r="AW60" t="n">
-        <v>1.058823529411765</v>
+        <v>1.0625</v>
       </c>
       <c r="AX60" t="n">
-        <v>70.41176470588235</v>
+        <v>69.9375</v>
       </c>
       <c r="AY60" t="n">
-        <v>2917647.05882353</v>
+        <v>2662500</v>
       </c>
       <c r="AZ60" t="n">
-        <v>74.70588235294117</v>
+        <v>74.5</v>
       </c>
       <c r="BA60" t="n">
         <v>27.5</v>
@@ -13644,12 +13602,12 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>MLVBCoY</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>MVSS7qF</t>
+          <t>MVSS7qFe</t>
         </is>
       </c>
       <c r="W61" t="n">
@@ -13693,22 +13651,22 @@
         <v>76.54545454545455</v>
       </c>
       <c r="AI61" t="n">
-        <v>26.8</v>
+        <v>26.45454545454545</v>
       </c>
       <c r="AJ61" t="n">
-        <v>182.2</v>
+        <v>182.1818181818182</v>
       </c>
       <c r="AK61" t="n">
-        <v>2</v>
+        <v>1.909090909090909</v>
       </c>
       <c r="AL61" t="n">
-        <v>81.5</v>
+        <v>80.72727272727273</v>
       </c>
       <c r="AM61" t="n">
-        <v>42270000</v>
+        <v>39018181.81818182</v>
       </c>
       <c r="AN61" t="n">
-        <v>83.59999999999999</v>
+        <v>83.45454545454545</v>
       </c>
       <c r="AO61" t="n">
         <v>24.81481481481481</v>
@@ -13864,12 +13822,12 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>zFLwLRZ</t>
+          <t>zFLwLRZS</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>lUkw2EZ</t>
+          <t>lUkw2EZn</t>
         </is>
       </c>
       <c r="W62" t="n">
@@ -14084,12 +14042,12 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>tSiEeKv</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>Qu12kvX</t>
+          <t>Qu12kvXf</t>
         </is>
       </c>
       <c r="W63" t="n">
@@ -14129,22 +14087,22 @@
         <v>78.5</v>
       </c>
       <c r="AI63" t="n">
-        <v>26.8</v>
+        <v>27.09090909090909</v>
       </c>
       <c r="AJ63" t="n">
-        <v>184</v>
+        <v>183.1818181818182</v>
       </c>
       <c r="AK63" t="n">
-        <v>1.7</v>
+        <v>1.818181818181818</v>
       </c>
       <c r="AL63" t="n">
-        <v>76.3</v>
+        <v>76.72727272727273</v>
       </c>
       <c r="AM63" t="n">
-        <v>16690000</v>
+        <v>17445454.54545455</v>
       </c>
       <c r="AN63" t="n">
-        <v>78.40000000000001</v>
+        <v>78.63636363636364</v>
       </c>
       <c r="AO63" t="n">
         <v>26.90909090909091</v>
@@ -14165,22 +14123,22 @@
         <v>72.54545454545455</v>
       </c>
       <c r="AU63" t="n">
-        <v>26.05</v>
+        <v>26.23809523809524</v>
       </c>
       <c r="AV63" t="n">
-        <v>181.8</v>
+        <v>181.4761904761905</v>
       </c>
       <c r="AW63" t="n">
-        <v>1.65</v>
+        <v>1.714285714285714</v>
       </c>
       <c r="AX63" t="n">
-        <v>76.65000000000001</v>
+        <v>76.85714285714286</v>
       </c>
       <c r="AY63" t="n">
-        <v>16583000</v>
+        <v>16983809.52380952</v>
       </c>
       <c r="AZ63" t="n">
-        <v>79.7</v>
+        <v>79.76190476190476</v>
       </c>
       <c r="BA63" t="n">
         <v>26.4</v>
@@ -14300,12 +14258,12 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>EJLKYOz</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>S8Ygn9M</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
       <c r="W64" t="n">
@@ -14349,22 +14307,22 @@
         <v>82.27272727272727</v>
       </c>
       <c r="AI64" t="n">
-        <v>25.8</v>
+        <v>25.54545454545455</v>
       </c>
       <c r="AJ64" t="n">
-        <v>183.7</v>
+        <v>183.3636363636364</v>
       </c>
       <c r="AK64" t="n">
         <v>1</v>
       </c>
       <c r="AL64" t="n">
-        <v>72.7</v>
+        <v>72.36363636363636</v>
       </c>
       <c r="AM64" t="n">
-        <v>4550000</v>
+        <v>4390909.090909091</v>
       </c>
       <c r="AN64" t="n">
-        <v>76.09999999999999</v>
+        <v>76.09090909090909</v>
       </c>
       <c r="AO64" t="n">
         <v>26.40909090909091</v>
@@ -14520,12 +14478,12 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>tjY4uUe</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>tSiEeKv</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="W65" t="n">
@@ -14547,22 +14505,22 @@
       </c>
       <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="n">
-        <v>26.5</v>
+        <v>26.09090909090909</v>
       </c>
       <c r="AD65" t="n">
-        <v>181.2</v>
+        <v>180.9090909090909</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.7</v>
+        <v>1.636363636363636</v>
       </c>
       <c r="AF65" t="n">
-        <v>75.40000000000001</v>
+        <v>75.54545454545455</v>
       </c>
       <c r="AG65" t="n">
-        <v>9280000</v>
+        <v>10481818.18181818</v>
       </c>
       <c r="AH65" t="n">
-        <v>79.3</v>
+        <v>79.90909090909091</v>
       </c>
       <c r="AI65" t="n">
         <v>27.2</v>
@@ -14583,22 +14541,22 @@
         <v>76.2</v>
       </c>
       <c r="AO65" t="n">
-        <v>25.4</v>
+        <v>25.39130434782609</v>
       </c>
       <c r="AP65" t="n">
-        <v>182</v>
+        <v>183.695652173913</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.6</v>
+        <v>1.652173913043478</v>
       </c>
       <c r="AR65" t="n">
-        <v>75.93333333333334</v>
+        <v>75.43478260869566</v>
       </c>
       <c r="AS65" t="n">
-        <v>14093333.33333333</v>
+        <v>13600000</v>
       </c>
       <c r="AT65" t="n">
-        <v>79.56666666666666</v>
+        <v>79.52173913043478</v>
       </c>
       <c r="AU65" t="n">
         <v>26.76923076923077</v>
@@ -14670,7 +14628,12 @@
       <c r="B66" s="2" t="n">
         <v>45396.65625</v>
       </c>
-      <c r="C66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fourneau f 
+  ita </t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio giuseppe meazza  san siro 
@@ -14731,12 +14694,12 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>j32a3mq</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>zFLwLRZ</t>
+          <t>zFLwLRZS</t>
         </is>
       </c>
       <c r="W66" t="n">
@@ -14951,12 +14914,12 @@
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>AcgUMf0</t>
+          <t>AcgUMf0E</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>A72TGDl</t>
+          <t>A72TGDlt</t>
         </is>
       </c>
       <c r="W67" t="n">
@@ -15000,22 +14963,22 @@
         <v>77.54545454545455</v>
       </c>
       <c r="AI67" t="n">
-        <v>26.1</v>
+        <v>25.90909090909091</v>
       </c>
       <c r="AJ67" t="n">
-        <v>183.8</v>
+        <v>184.1818181818182</v>
       </c>
       <c r="AK67" t="n">
-        <v>1.7</v>
+        <v>1.727272727272727</v>
       </c>
       <c r="AL67" t="n">
-        <v>78.40000000000001</v>
+        <v>79.09090909090909</v>
       </c>
       <c r="AM67" t="n">
-        <v>20040000</v>
+        <v>27536363.63636364</v>
       </c>
       <c r="AN67" t="n">
-        <v>81.59999999999999</v>
+        <v>82.45454545454545</v>
       </c>
       <c r="AO67" t="n">
         <v>24.92857142857143</v>
@@ -15171,12 +15134,12 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>MVSS7qF</t>
+          <t>MVSS7qFe</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>n10g3Kf</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
       <c r="W68" t="n">
@@ -15202,22 +15165,22 @@
         </is>
       </c>
       <c r="AC68" t="n">
-        <v>27.5</v>
+        <v>27.09090909090909</v>
       </c>
       <c r="AD68" t="n">
-        <v>181.1</v>
+        <v>181.1818181818182</v>
       </c>
       <c r="AE68" t="n">
-        <v>2</v>
+        <v>1.909090909090909</v>
       </c>
       <c r="AF68" t="n">
-        <v>82.7</v>
+        <v>81.81818181818181</v>
       </c>
       <c r="AG68" t="n">
-        <v>44350000</v>
+        <v>40909090.90909091</v>
       </c>
       <c r="AH68" t="n">
-        <v>83.90000000000001</v>
+        <v>83.72727272727273</v>
       </c>
       <c r="AI68" t="n">
         <v>24.09090909090909</v>
@@ -15391,12 +15354,12 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>bBhpZV2</t>
+          <t>bBhpZV2s</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>619UPLr</t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="W69" t="n">
@@ -15436,22 +15399,22 @@
         <v>79.81818181818181</v>
       </c>
       <c r="AI69" t="n">
-        <v>25.3</v>
+        <v>24.88888888888889</v>
       </c>
       <c r="AJ69" t="n">
-        <v>183.6</v>
+        <v>182.5555555555555</v>
       </c>
       <c r="AK69" t="n">
-        <v>1.3</v>
+        <v>1.222222222222222</v>
       </c>
       <c r="AL69" t="n">
-        <v>73.5</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="AM69" t="n">
-        <v>8890000</v>
+        <v>9355555.555555556</v>
       </c>
       <c r="AN69" t="n">
-        <v>78.3</v>
+        <v>78.66666666666667</v>
       </c>
       <c r="AO69" t="n">
         <v>23</v>
@@ -15607,12 +15570,12 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>4IdjsvY</t>
+          <t>4IdjsvY2</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>lUkw2EZ</t>
+          <t>lUkw2EZn</t>
         </is>
       </c>
       <c r="W70" t="n">
@@ -15638,22 +15601,22 @@
         </is>
       </c>
       <c r="AC70" t="n">
-        <v>26.3</v>
+        <v>26.6</v>
       </c>
       <c r="AD70" t="n">
-        <v>185.1</v>
+        <v>185.3</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AF70" t="n">
-        <v>76.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="AG70" t="n">
-        <v>13110000</v>
+        <v>12460000</v>
       </c>
       <c r="AH70" t="n">
-        <v>79.3</v>
+        <v>79.2</v>
       </c>
       <c r="AI70" t="n">
         <v>26.2</v>
@@ -15674,22 +15637,22 @@
         <v>84.5</v>
       </c>
       <c r="AO70" t="n">
-        <v>25.05263157894737</v>
+        <v>24.94444444444444</v>
       </c>
       <c r="AP70" t="n">
-        <v>185.3684210526316</v>
+        <v>185.6666666666667</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.157894736842105</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="AR70" t="n">
-        <v>72.36842105263158</v>
+        <v>72.05555555555556</v>
       </c>
       <c r="AS70" t="n">
-        <v>5468421.052631579</v>
+        <v>4938888.888888889</v>
       </c>
       <c r="AT70" t="n">
-        <v>76.15789473684211</v>
+        <v>76.05555555555556</v>
       </c>
       <c r="AU70" t="n">
         <v>23.71428571428572</v>
@@ -15827,12 +15790,12 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>KtGrCa5</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>MLVBCoY</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="W71" t="n">
@@ -16043,12 +16006,12 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>Qu12kvX</t>
+          <t>Qu12kvXf</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>rTrn0h4</t>
+          <t>rTrn0h4a</t>
         </is>
       </c>
       <c r="W72" t="n">
@@ -16074,40 +16037,40 @@
         </is>
       </c>
       <c r="AC72" t="n">
-        <v>26.8</v>
+        <v>27.09090909090909</v>
       </c>
       <c r="AD72" t="n">
-        <v>184</v>
+        <v>183.1818181818182</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.7</v>
+        <v>1.818181818181818</v>
       </c>
       <c r="AF72" t="n">
-        <v>76.3</v>
+        <v>76.72727272727273</v>
       </c>
       <c r="AG72" t="n">
-        <v>16690000</v>
+        <v>17445454.54545455</v>
       </c>
       <c r="AH72" t="n">
-        <v>78.40000000000001</v>
+        <v>78.63636363636364</v>
       </c>
       <c r="AI72" t="n">
-        <v>26.63636363636364</v>
+        <v>25.7</v>
       </c>
       <c r="AJ72" t="n">
-        <v>185.3636363636364</v>
+        <v>185.9</v>
       </c>
       <c r="AK72" t="n">
-        <v>1.545454545454545</v>
+        <v>1.4</v>
       </c>
       <c r="AL72" t="n">
-        <v>72.18181818181819</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="AM72" t="n">
-        <v>3404545.454545455</v>
+        <v>3265000</v>
       </c>
       <c r="AN72" t="n">
-        <v>77</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="AO72" t="n">
         <v>25.45</v>
@@ -16128,22 +16091,22 @@
         <v>78.40000000000001</v>
       </c>
       <c r="AU72" t="n">
-        <v>26.1</v>
+        <v>25.57894736842105</v>
       </c>
       <c r="AV72" t="n">
-        <v>184.55</v>
+        <v>184.7894736842105</v>
       </c>
       <c r="AW72" t="n">
-        <v>1.35</v>
+        <v>1.263157894736842</v>
       </c>
       <c r="AX72" t="n">
-        <v>71.34999999999999</v>
+        <v>71</v>
       </c>
       <c r="AY72" t="n">
-        <v>3487500</v>
+        <v>3418421.052631579</v>
       </c>
       <c r="AZ72" t="n">
-        <v>76.09999999999999</v>
+        <v>76</v>
       </c>
       <c r="BA72" t="n">
         <v>28.4</v>
@@ -16263,12 +16226,12 @@
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>EDkXRoL</t>
+          <t>EDkXRoLT</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>j32a3mq</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="W73" t="n">
@@ -16330,22 +16293,22 @@
         <v>84.63636363636364</v>
       </c>
       <c r="AO73" t="n">
-        <v>24.80769230769231</v>
+        <v>24.52</v>
       </c>
       <c r="AP73" t="n">
-        <v>181.8076923076923</v>
+        <v>181.44</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.038461538461539</v>
+        <v>1.04</v>
       </c>
       <c r="AR73" t="n">
-        <v>71.42307692307692</v>
+        <v>71.16</v>
       </c>
       <c r="AS73" t="n">
-        <v>3984615.384615385</v>
+        <v>3864000</v>
       </c>
       <c r="AT73" t="n">
-        <v>76.07692307692308</v>
+        <v>76</v>
       </c>
       <c r="AU73" t="n">
         <v>28.42307692307692</v>
@@ -16483,12 +16446,12 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>lUkw2EZ</t>
+          <t>lUkw2EZn</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>tjY4uUe</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="W74" t="n">
@@ -16532,22 +16495,22 @@
         <v>84.5</v>
       </c>
       <c r="AI74" t="n">
-        <v>26.90909090909091</v>
+        <v>27.1</v>
       </c>
       <c r="AJ74" t="n">
-        <v>185.2727272727273</v>
+        <v>185.3</v>
       </c>
       <c r="AK74" t="n">
-        <v>1.636363636363636</v>
+        <v>1.7</v>
       </c>
       <c r="AL74" t="n">
-        <v>76.81818181818181</v>
+        <v>76.8</v>
       </c>
       <c r="AM74" t="n">
-        <v>12981818.18181818</v>
+        <v>12880000</v>
       </c>
       <c r="AN74" t="n">
-        <v>79.63636363636364</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="AO74" t="n">
         <v>23.65</v>
@@ -16568,22 +16531,22 @@
         <v>82.65000000000001</v>
       </c>
       <c r="AU74" t="n">
-        <v>24.68965517241379</v>
+        <v>24.48</v>
       </c>
       <c r="AV74" t="n">
-        <v>178.1379310344828</v>
+        <v>179.48</v>
       </c>
       <c r="AW74" t="n">
-        <v>1.310344827586207</v>
+        <v>1.32</v>
       </c>
       <c r="AX74" t="n">
-        <v>75.48275862068965</v>
+        <v>75.08</v>
       </c>
       <c r="AY74" t="n">
-        <v>12310344.82758621</v>
+        <v>11740000</v>
       </c>
       <c r="AZ74" t="n">
-        <v>79.72413793103448</v>
+        <v>79.84</v>
       </c>
       <c r="BA74" t="n">
         <v>27</v>
@@ -16689,12 +16652,12 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>zFLwLRZ</t>
+          <t>zFLwLRZS</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>EJLKYOz</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="W75" t="n">
@@ -16909,12 +16872,12 @@
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>S8Ygn9M</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>tSiEeKv</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="W76" t="n">
@@ -16972,22 +16935,22 @@
         <v>75.72727272727273</v>
       </c>
       <c r="AO76" t="n">
-        <v>24.41666666666667</v>
+        <v>24.25925925925926</v>
       </c>
       <c r="AP76" t="n">
-        <v>183.7083333333333</v>
+        <v>183.2962962962963</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.083333333333333</v>
+        <v>1.074074074074074</v>
       </c>
       <c r="AR76" t="n">
-        <v>71</v>
+        <v>70.77777777777777</v>
       </c>
       <c r="AS76" t="n">
-        <v>3727083.333333333</v>
+        <v>3624074.074074074</v>
       </c>
       <c r="AT76" t="n">
-        <v>75.5</v>
+        <v>75.55555555555556</v>
       </c>
       <c r="AU76" t="n">
         <v>25.65</v>
@@ -17125,12 +17088,12 @@
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>619UPLr</t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>MVSS7qF</t>
+          <t>MVSS7qFe</t>
         </is>
       </c>
       <c r="W77" t="n">
@@ -17152,22 +17115,22 @@
         </is>
       </c>
       <c r="AC77" t="n">
-        <v>27.2</v>
+        <v>27</v>
       </c>
       <c r="AD77" t="n">
-        <v>184.1</v>
+        <v>183.1111111111111</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.4</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AF77" t="n">
-        <v>74.7</v>
+        <v>74.66666666666667</v>
       </c>
       <c r="AG77" t="n">
-        <v>7940000</v>
+        <v>8300000</v>
       </c>
       <c r="AH77" t="n">
-        <v>76.90000000000001</v>
+        <v>77.11111111111111</v>
       </c>
       <c r="AI77" t="n">
         <v>26.72727272727273</v>
@@ -17206,22 +17169,22 @@
         <v>77.19230769230769</v>
       </c>
       <c r="AU77" t="n">
-        <v>26.17391304347826</v>
+        <v>26.04166666666667</v>
       </c>
       <c r="AV77" t="n">
-        <v>179.4347826086957</v>
+        <v>179.5416666666667</v>
       </c>
       <c r="AW77" t="n">
-        <v>1.652173913043478</v>
+        <v>1.625</v>
       </c>
       <c r="AX77" t="n">
-        <v>77.1304347826087</v>
+        <v>76.95833333333333</v>
       </c>
       <c r="AY77" t="n">
-        <v>18514130.43478261</v>
+        <v>18013541.66666667</v>
       </c>
       <c r="AZ77" t="n">
-        <v>80.30434782608695</v>
+        <v>80.375</v>
       </c>
       <c r="BA77" t="n">
         <v>27</v>
@@ -17341,12 +17304,12 @@
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>n10g3Kf</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>bBhpZV2</t>
+          <t>bBhpZV2s</t>
         </is>
       </c>
       <c r="W78" t="n">
@@ -17561,12 +17524,12 @@
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>MLVBCoY</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>4IdjsvY</t>
+          <t>4IdjsvY2</t>
         </is>
       </c>
       <c r="W79" t="n">
@@ -17610,22 +17573,22 @@
         <v>76.18181818181819</v>
       </c>
       <c r="AI79" t="n">
-        <v>26.3</v>
+        <v>26.6</v>
       </c>
       <c r="AJ79" t="n">
-        <v>185.1</v>
+        <v>185.3</v>
       </c>
       <c r="AK79" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AL79" t="n">
-        <v>76.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="AM79" t="n">
-        <v>13110000</v>
+        <v>12460000</v>
       </c>
       <c r="AN79" t="n">
-        <v>79.3</v>
+        <v>79.2</v>
       </c>
       <c r="AO79" t="n">
         <v>24.18518518518519</v>
@@ -17646,22 +17609,22 @@
         <v>75.29629629629629</v>
       </c>
       <c r="AU79" t="n">
-        <v>24.89473684210526</v>
+        <v>25.15</v>
       </c>
       <c r="AV79" t="n">
-        <v>185.3684210526316</v>
+        <v>185.2</v>
       </c>
       <c r="AW79" t="n">
-        <v>1.210526315789474</v>
+        <v>1.25</v>
       </c>
       <c r="AX79" t="n">
-        <v>71.73684210526316</v>
+        <v>72</v>
       </c>
       <c r="AY79" t="n">
-        <v>4231578.947368421</v>
+        <v>4445000</v>
       </c>
       <c r="AZ79" t="n">
-        <v>76.15789473684211</v>
+        <v>76.2</v>
       </c>
       <c r="BA79" t="n">
         <v>29</v>
@@ -17781,12 +17744,12 @@
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>xjigzK8</t>
+          <t>xjigzK81</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>Qu12kvX</t>
+          <t>Qu12kvXf</t>
         </is>
       </c>
       <c r="W80" t="n">
@@ -17812,40 +17775,40 @@
         </is>
       </c>
       <c r="AC80" t="n">
-        <v>27.63636363636364</v>
+        <v>27.7</v>
       </c>
       <c r="AD80" t="n">
-        <v>183.0909090909091</v>
+        <v>182.4</v>
       </c>
       <c r="AE80" t="n">
-        <v>2.454545454545455</v>
+        <v>2.5</v>
       </c>
       <c r="AF80" t="n">
-        <v>79.81818181818181</v>
+        <v>79.5</v>
       </c>
       <c r="AG80" t="n">
-        <v>25772727.27272727</v>
+        <v>24500000</v>
       </c>
       <c r="AH80" t="n">
-        <v>80.72727272727273</v>
+        <v>80.3</v>
       </c>
       <c r="AI80" t="n">
-        <v>26.2</v>
+        <v>26.54545454545455</v>
       </c>
       <c r="AJ80" t="n">
-        <v>185.4</v>
+        <v>184.4545454545455</v>
       </c>
       <c r="AK80" t="n">
-        <v>1.8</v>
+        <v>1.909090909090909</v>
       </c>
       <c r="AL80" t="n">
-        <v>76.59999999999999</v>
+        <v>77</v>
       </c>
       <c r="AM80" t="n">
-        <v>17990000</v>
+        <v>18627272.72727273</v>
       </c>
       <c r="AN80" t="n">
-        <v>79.5</v>
+        <v>79.63636363636364</v>
       </c>
       <c r="AO80" t="n">
         <v>25.76923076923077</v>
@@ -18001,12 +17964,12 @@
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>A72TGDl</t>
+          <t>A72TGDlt</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>KtGrCa5</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
       <c r="W81" t="n">
@@ -18028,22 +17991,22 @@
       </c>
       <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="n">
-        <v>25.6</v>
+        <v>25.45454545454545</v>
       </c>
       <c r="AD81" t="n">
-        <v>183.5</v>
+        <v>183.9090909090909</v>
       </c>
       <c r="AE81" t="n">
         <v>2</v>
       </c>
       <c r="AF81" t="n">
-        <v>81.2</v>
+        <v>81.63636363636364</v>
       </c>
       <c r="AG81" t="n">
-        <v>35800000</v>
+        <v>41863636.36363637</v>
       </c>
       <c r="AH81" t="n">
-        <v>84.90000000000001</v>
+        <v>85.45454545454545</v>
       </c>
       <c r="AI81" t="n">
         <v>24.27272727272727</v>
@@ -18217,12 +18180,12 @@
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>rTrn0h4</t>
+          <t>rTrn0h4a</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>AcgUMf0</t>
+          <t>AcgUMf0E</t>
         </is>
       </c>
       <c r="W82" t="n">
@@ -18248,22 +18211,22 @@
         </is>
       </c>
       <c r="AC82" t="n">
-        <v>25.1</v>
+        <v>23.88888888888889</v>
       </c>
       <c r="AD82" t="n">
-        <v>183.8</v>
+        <v>184.2222222222222</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.3</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="AF82" t="n">
-        <v>71.2</v>
+        <v>70.44444444444444</v>
       </c>
       <c r="AG82" t="n">
-        <v>3345000</v>
+        <v>3183333.333333333</v>
       </c>
       <c r="AH82" t="n">
-        <v>77.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="AI82" t="n">
         <v>26.63636363636364</v>
@@ -18437,12 +18400,12 @@
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>EJLKYOz</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>lUkw2EZ</t>
+          <t>lUkw2EZn</t>
         </is>
       </c>
       <c r="W83" t="n">
@@ -18629,12 +18592,12 @@
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>EJLKYOz</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>tjY4uUe</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="W84" t="n">
@@ -18678,19 +18641,19 @@
         <v>82.09090909090909</v>
       </c>
       <c r="AI84" t="n">
-        <v>26.90909090909091</v>
+        <v>27.1</v>
       </c>
       <c r="AJ84" t="n">
-        <v>182.8181818181818</v>
+        <v>182.6</v>
       </c>
       <c r="AK84" t="n">
-        <v>1.636363636363636</v>
+        <v>1.7</v>
       </c>
       <c r="AL84" t="n">
-        <v>77.63636363636364</v>
+        <v>77.7</v>
       </c>
       <c r="AM84" t="n">
-        <v>14200000</v>
+        <v>14220000</v>
       </c>
       <c r="AN84" t="n">
         <v>80</v>
@@ -18714,22 +18677,22 @@
         <v>78.10526315789474</v>
       </c>
       <c r="AU84" t="n">
-        <v>24.17241379310345</v>
+        <v>23.96296296296296</v>
       </c>
       <c r="AV84" t="n">
-        <v>180.1724137931035</v>
+        <v>180.7407407407407</v>
       </c>
       <c r="AW84" t="n">
-        <v>1.586206896551724</v>
+        <v>1.592592592592593</v>
       </c>
       <c r="AX84" t="n">
-        <v>72.58620689655173</v>
+        <v>72.18518518518519</v>
       </c>
       <c r="AY84" t="n">
-        <v>8717241.379310345</v>
+        <v>8381481.481481481</v>
       </c>
       <c r="AZ84" t="n">
-        <v>78.82758620689656</v>
+        <v>78.96296296296296</v>
       </c>
       <c r="BA84" t="inlineStr"/>
       <c r="BB84" t="inlineStr"/>
@@ -18821,12 +18784,12 @@
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>Qu12kvX</t>
+          <t>Qu12kvXf</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>lUkw2EZ</t>
+          <t>lUkw2EZn</t>
         </is>
       </c>
       <c r="W85" t="n">
@@ -18852,22 +18815,22 @@
         </is>
       </c>
       <c r="AC85" t="n">
-        <v>26.1</v>
+        <v>26.45454545454545</v>
       </c>
       <c r="AD85" t="n">
-        <v>184.3</v>
+        <v>183.4545454545455</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.8</v>
+        <v>1.909090909090909</v>
       </c>
       <c r="AF85" t="n">
-        <v>76.5</v>
+        <v>76.90909090909091</v>
       </c>
       <c r="AG85" t="n">
-        <v>17890000</v>
+        <v>18536363.63636364</v>
       </c>
       <c r="AH85" t="n">
-        <v>78.90000000000001</v>
+        <v>79.09090909090909</v>
       </c>
       <c r="AI85" t="n">
         <v>26</v>
@@ -18888,22 +18851,22 @@
         <v>84</v>
       </c>
       <c r="AO85" t="n">
-        <v>26.57142857142857</v>
+        <v>26.72727272727273</v>
       </c>
       <c r="AP85" t="n">
-        <v>182.952380952381</v>
+        <v>182.5909090909091</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.761904761904762</v>
+        <v>1.818181818181818</v>
       </c>
       <c r="AR85" t="n">
-        <v>75.57142857142857</v>
+        <v>75.81818181818181</v>
       </c>
       <c r="AS85" t="n">
-        <v>14188571.42857143</v>
+        <v>14680000</v>
       </c>
       <c r="AT85" t="n">
-        <v>79.23809523809524</v>
+        <v>79.31818181818181</v>
       </c>
       <c r="AU85" t="n">
         <v>24.52631578947368</v>

--- a/p6_deployment/data/italy/missing/data_preparation/df_integrated_missing.xlsx
+++ b/p6_deployment/data/italy/missing/data_preparation/df_integrated_missing.xlsx
@@ -865,22 +865,22 @@
         </is>
       </c>
       <c r="AC2" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>187.1818181818182</v>
+        <v>187.6</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.272727272727273</v>
+        <v>1.3</v>
       </c>
       <c r="AF2" t="n">
-        <v>78.27272727272727</v>
+        <v>78.2</v>
       </c>
       <c r="AG2" t="n">
-        <v>21454545.45454545</v>
+        <v>20950000</v>
       </c>
       <c r="AH2" t="n">
-        <v>83</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="AI2" t="n">
         <v>24.8</v>
@@ -919,22 +919,22 @@
         <v>78.88</v>
       </c>
       <c r="AU2" t="n">
-        <v>25.5</v>
+        <v>25.51851851851852</v>
       </c>
       <c r="AV2" t="n">
-        <v>181.5416666666667</v>
+        <v>182.1111111111111</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.458333333333333</v>
+        <v>1.444444444444444</v>
       </c>
       <c r="AX2" t="n">
-        <v>74.58333333333333</v>
+        <v>74.88888888888889</v>
       </c>
       <c r="AY2" t="n">
-        <v>10258333.33333333</v>
+        <v>10766666.66666667</v>
       </c>
       <c r="AZ2" t="n">
-        <v>78.79166666666667</v>
+        <v>78.85185185185185</v>
       </c>
       <c r="BA2" t="n">
         <v>31</v>
@@ -1103,22 +1103,22 @@
         <v>76.27272727272727</v>
       </c>
       <c r="AI3" t="n">
-        <v>24.88888888888889</v>
+        <v>25.1</v>
       </c>
       <c r="AJ3" t="n">
-        <v>180.3333333333333</v>
+        <v>181.3</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.888888888888889</v>
+        <v>1.9</v>
       </c>
       <c r="AL3" t="n">
-        <v>77.44444444444444</v>
+        <v>78</v>
       </c>
       <c r="AM3" t="n">
-        <v>19033333.33333333</v>
+        <v>20780000</v>
       </c>
       <c r="AN3" t="n">
-        <v>80.22222222222223</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="AO3" t="n">
         <v>25.92592592592593</v>
@@ -1341,22 +1341,22 @@
         <v>77.54545454545455</v>
       </c>
       <c r="AO4" t="n">
-        <v>23.06666666666667</v>
+        <v>22.74074074074074</v>
       </c>
       <c r="AP4" t="n">
-        <v>183.5333333333333</v>
+        <v>184.7037037037037</v>
       </c>
       <c r="AQ4" t="n">
         <v>1</v>
       </c>
       <c r="AR4" t="n">
-        <v>66.76666666666667</v>
+        <v>66.74074074074075</v>
       </c>
       <c r="AS4" t="n">
-        <v>2299166.666666667</v>
+        <v>2421296.296296296</v>
       </c>
       <c r="AT4" t="n">
-        <v>73.73333333333333</v>
+        <v>74.37037037037037</v>
       </c>
       <c r="AU4" t="n">
         <v>25.875</v>
@@ -1398,25 +1398,25 @@
         <v>228</v>
       </c>
       <c r="BH4" t="n">
-        <v>26.25</v>
+        <v>27.4</v>
       </c>
       <c r="BI4" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="BK4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BL4" t="n">
-        <v>297</v>
+        <v>375</v>
       </c>
       <c r="BM4" t="n">
-        <v>29600000</v>
+        <v>36600000</v>
       </c>
       <c r="BN4" t="n">
-        <v>304</v>
+        <v>382</v>
       </c>
     </row>
     <row r="5">
@@ -1561,22 +1561,22 @@
         <v>77.81818181818181</v>
       </c>
       <c r="AO5" t="n">
-        <v>26.69565217391304</v>
+        <v>26.2</v>
       </c>
       <c r="AP5" t="n">
-        <v>180.6086956521739</v>
+        <v>181.45</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.130434782608696</v>
+        <v>2</v>
       </c>
       <c r="AR5" t="n">
-        <v>77.34782608695652</v>
+        <v>76.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>18911304.34782609</v>
+        <v>17998000</v>
       </c>
       <c r="AT5" t="n">
-        <v>80.39130434782609</v>
+        <v>80.3</v>
       </c>
       <c r="AU5" t="n">
         <v>23.80769230769231</v>
@@ -1618,25 +1618,25 @@
         <v>230</v>
       </c>
       <c r="BH5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BI5" t="n">
-        <v>179.3333333333333</v>
+        <v>182.5</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1.666666666666667</v>
+        <v>2</v>
       </c>
       <c r="BK5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BL5" t="n">
-        <v>235</v>
+        <v>160</v>
       </c>
       <c r="BM5" t="n">
-        <v>67500000</v>
+        <v>60000000</v>
       </c>
       <c r="BN5" t="n">
-        <v>238</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6">
@@ -1799,22 +1799,22 @@
         <v>74.95238095238095</v>
       </c>
       <c r="AU6" t="n">
-        <v>28.68965517241379</v>
+        <v>28.07692307692308</v>
       </c>
       <c r="AV6" t="n">
-        <v>180.7241379310345</v>
+        <v>182.0769230769231</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.206896551724138</v>
+        <v>2</v>
       </c>
       <c r="AX6" t="n">
-        <v>78.44827586206897</v>
+        <v>78.26923076923077</v>
       </c>
       <c r="AY6" t="n">
-        <v>19903448.27586207</v>
+        <v>20988461.53846154</v>
       </c>
       <c r="AZ6" t="n">
-        <v>80.48275862068965</v>
+        <v>80.53846153846153</v>
       </c>
       <c r="BA6" t="n">
         <v>27</v>
@@ -1987,40 +1987,40 @@
         <v>78.09090909090909</v>
       </c>
       <c r="AO7" t="n">
-        <v>24.44</v>
+        <v>24.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>188.24</v>
+        <v>188.4583333333333</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.04</v>
+        <v>1.041666666666667</v>
       </c>
       <c r="AR7" t="n">
-        <v>72.95999999999999</v>
+        <v>72.70833333333333</v>
       </c>
       <c r="AS7" t="n">
-        <v>10966200</v>
+        <v>10318958.33333333</v>
       </c>
       <c r="AT7" t="n">
-        <v>78</v>
+        <v>77.75</v>
       </c>
       <c r="AU7" t="n">
-        <v>24.77272727272727</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="AV7" t="n">
-        <v>184.8636363636364</v>
+        <v>184.375</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.272727272727273</v>
+        <v>1.208333333333333</v>
       </c>
       <c r="AX7" t="n">
-        <v>71.45454545454545</v>
+        <v>72.04166666666667</v>
       </c>
       <c r="AY7" t="n">
-        <v>4886363.636363637</v>
+        <v>6000000</v>
       </c>
       <c r="AZ7" t="n">
-        <v>75.90909090909091</v>
+        <v>76.125</v>
       </c>
       <c r="BA7" t="n">
         <v>30.33333333333333</v>
@@ -2165,24 +2165,28 @@
           <t>C06aJvIB</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
       <c r="AC8" t="n">
-        <v>26.45454545454545</v>
+        <v>25.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>182.0909090909091</v>
+        <v>181.8</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.636363636363636</v>
+        <v>1.6</v>
       </c>
       <c r="AF8" t="n">
-        <v>79.18181818181819</v>
+        <v>79.7</v>
       </c>
       <c r="AG8" t="n">
-        <v>27400000</v>
+        <v>29870000</v>
       </c>
       <c r="AH8" t="n">
-        <v>81.09090909090909</v>
+        <v>81.8</v>
       </c>
       <c r="AI8" t="n">
         <v>23.72727272727273</v>
@@ -2387,40 +2391,40 @@
         </is>
       </c>
       <c r="AC9" t="n">
-        <v>27.54545454545455</v>
+        <v>27.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>183.1818181818182</v>
+        <v>184.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.181818181818182</v>
+        <v>2.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>80.54545454545455</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="AG9" t="n">
-        <v>34968181.81818182</v>
+        <v>38075000</v>
       </c>
       <c r="AH9" t="n">
-        <v>83.18181818181819</v>
+        <v>84</v>
       </c>
       <c r="AI9" t="n">
-        <v>25.33333333333333</v>
+        <v>26.4</v>
       </c>
       <c r="AJ9" t="n">
-        <v>184.6666666666667</v>
+        <v>184.2</v>
       </c>
       <c r="AK9" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AL9" t="n">
-        <v>70.77777777777777</v>
+        <v>71.5</v>
       </c>
       <c r="AM9" t="n">
-        <v>3000000</v>
+        <v>3180000</v>
       </c>
       <c r="AN9" t="n">
-        <v>75.33333333333333</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="AO9" t="n">
         <v>25.88888888888889</v>
@@ -2441,22 +2445,22 @@
         <v>79.25925925925925</v>
       </c>
       <c r="AU9" t="n">
-        <v>23.77777777777778</v>
+        <v>24.42105263157895</v>
       </c>
       <c r="AV9" t="n">
-        <v>183.8333333333333</v>
+        <v>183.6315789473684</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.055555555555556</v>
+        <v>1.157894736842105</v>
       </c>
       <c r="AX9" t="n">
-        <v>67.61111111111111</v>
+        <v>68.15789473684211</v>
       </c>
       <c r="AY9" t="n">
-        <v>2530555.555555556</v>
+        <v>2650000</v>
       </c>
       <c r="AZ9" t="n">
-        <v>75.27777777777777</v>
+        <v>75.42105263157895</v>
       </c>
       <c r="BA9" t="n">
         <v>25.5</v>
@@ -2601,60 +2605,64 @@
           <t>Iw7eKK25</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
       <c r="AC10" t="n">
-        <v>24.5</v>
+        <v>25.375</v>
       </c>
       <c r="AD10" t="n">
-        <v>182.5</v>
+        <v>183.125</v>
       </c>
       <c r="AE10" t="n">
         <v>1.875</v>
       </c>
       <c r="AF10" t="n">
-        <v>77</v>
+        <v>76.125</v>
       </c>
       <c r="AG10" t="n">
-        <v>17062500</v>
+        <v>11625000</v>
       </c>
       <c r="AH10" t="n">
-        <v>82.125</v>
+        <v>81.125</v>
       </c>
       <c r="AI10" t="n">
-        <v>25.6</v>
+        <v>25.90909090909091</v>
       </c>
       <c r="AJ10" t="n">
-        <v>184</v>
+        <v>184.8181818181818</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.4</v>
+        <v>1.454545454545455</v>
       </c>
       <c r="AL10" t="n">
-        <v>72.90000000000001</v>
+        <v>73.09090909090909</v>
       </c>
       <c r="AM10" t="n">
-        <v>6590000</v>
+        <v>6418181.818181818</v>
       </c>
       <c r="AN10" t="n">
-        <v>77.90000000000001</v>
+        <v>77.63636363636364</v>
       </c>
       <c r="AO10" t="n">
-        <v>25.69565217391304</v>
+        <v>25.95833333333333</v>
       </c>
       <c r="AP10" t="n">
-        <v>186.2608695652174</v>
+        <v>186</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.608695652173913</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="AR10" t="n">
-        <v>77.1304347826087</v>
+        <v>77.125</v>
       </c>
       <c r="AS10" t="n">
-        <v>22367391.30434782</v>
+        <v>21727083.33333333</v>
       </c>
       <c r="AT10" t="n">
-        <v>81.73913043478261</v>
+        <v>81.54166666666667</v>
       </c>
       <c r="AU10" t="n">
         <v>24.65217391304348</v>
@@ -2812,7 +2820,11 @@
       <c r="Z11" t="n">
         <v>20232024</v>
       </c>
-      <c r="AA11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
       <c r="AB11" t="inlineStr">
         <is>
           <t>Q3A3IbXH</t>
@@ -3043,22 +3055,22 @@
         <v>75.81818181818181</v>
       </c>
       <c r="AI12" t="n">
-        <v>27.54545454545455</v>
+        <v>27.9</v>
       </c>
       <c r="AJ12" t="n">
-        <v>183.8181818181818</v>
+        <v>185.6</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.818181818181818</v>
+        <v>1.9</v>
       </c>
       <c r="AL12" t="n">
-        <v>77.54545454545455</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="AM12" t="n">
-        <v>12609090.90909091</v>
+        <v>12470000</v>
       </c>
       <c r="AN12" t="n">
-        <v>79.09090909090909</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="AO12" t="n">
         <v>26.3448275862069</v>
@@ -3079,22 +3091,22 @@
         <v>73.31034482758621</v>
       </c>
       <c r="AU12" t="n">
-        <v>24.72</v>
+        <v>24.86206896551724</v>
       </c>
       <c r="AV12" t="n">
-        <v>181.96</v>
+        <v>180.9310344827586</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.56</v>
+        <v>1.586206896551724</v>
       </c>
       <c r="AX12" t="n">
-        <v>74.92</v>
+        <v>75.31034482758621</v>
       </c>
       <c r="AY12" t="n">
-        <v>13236000</v>
+        <v>13600000</v>
       </c>
       <c r="AZ12" t="n">
-        <v>79.76000000000001</v>
+        <v>79.68965517241379</v>
       </c>
       <c r="BA12" t="n">
         <v>25</v>
@@ -3263,22 +3275,22 @@
         <v>79.18181818181819</v>
       </c>
       <c r="AI13" t="n">
-        <v>24.6</v>
+        <v>24.55555555555556</v>
       </c>
       <c r="AJ13" t="n">
-        <v>185.8</v>
+        <v>187</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.7</v>
+        <v>1.555555555555556</v>
       </c>
       <c r="AL13" t="n">
-        <v>80.8</v>
+        <v>80.44444444444444</v>
       </c>
       <c r="AM13" t="n">
-        <v>33450000</v>
+        <v>31555555.55555556</v>
       </c>
       <c r="AN13" t="n">
-        <v>85.8</v>
+        <v>85.88888888888889</v>
       </c>
       <c r="AO13" t="n">
         <v>23.58620689655172</v>
@@ -3299,22 +3311,22 @@
         <v>78.06896551724138</v>
       </c>
       <c r="AU13" t="n">
-        <v>24.625</v>
+        <v>24.92</v>
       </c>
       <c r="AV13" t="n">
-        <v>183.5416666666667</v>
+        <v>183.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.708333333333333</v>
+        <v>1.76</v>
       </c>
       <c r="AX13" t="n">
-        <v>76.83333333333333</v>
+        <v>76.84</v>
       </c>
       <c r="AY13" t="n">
-        <v>18131250</v>
+        <v>17686000</v>
       </c>
       <c r="AZ13" t="n">
-        <v>81.875</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="BA13" t="n">
         <v>22.5</v>
@@ -3497,22 +3509,22 @@
         <v>77.36363636363636</v>
       </c>
       <c r="AO14" t="n">
-        <v>25.06666666666667</v>
+        <v>26.88888888888889</v>
       </c>
       <c r="AP14" t="n">
-        <v>181.7333333333333</v>
+        <v>181.4444444444445</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>71.33333333333333</v>
+        <v>72.44444444444444</v>
       </c>
       <c r="AS14" t="n">
-        <v>3808333.333333333</v>
+        <v>3973611.111111111</v>
       </c>
       <c r="AT14" t="n">
-        <v>76.53333333333333</v>
+        <v>76.77777777777777</v>
       </c>
       <c r="AU14" t="n">
         <v>24.29166666666667</v>
@@ -3675,7 +3687,11 @@
           <t>URcSl02h</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
       <c r="AC15" t="n">
         <v>25.9</v>
       </c>
@@ -3713,22 +3729,22 @@
         <v>77.90000000000001</v>
       </c>
       <c r="AO15" t="n">
-        <v>26.32</v>
+        <v>26.39285714285714</v>
       </c>
       <c r="AP15" t="n">
-        <v>183.68</v>
+        <v>184.3571428571429</v>
       </c>
       <c r="AQ15" t="n">
-        <v>2.16</v>
+        <v>2.142857142857143</v>
       </c>
       <c r="AR15" t="n">
-        <v>78.08</v>
+        <v>78.60714285714286</v>
       </c>
       <c r="AS15" t="n">
-        <v>24132000</v>
+        <v>25457142.85714286</v>
       </c>
       <c r="AT15" t="n">
-        <v>80.92</v>
+        <v>81.25</v>
       </c>
       <c r="AU15" t="n">
         <v>26.07142857142857</v>
@@ -3933,40 +3949,40 @@
         <v>79.72727272727273</v>
       </c>
       <c r="AO16" t="n">
-        <v>27.44827586206896</v>
+        <v>26.69230769230769</v>
       </c>
       <c r="AP16" t="n">
-        <v>181.7241379310345</v>
+        <v>183.1923076923077</v>
       </c>
       <c r="AQ16" t="n">
-        <v>2</v>
+        <v>1.769230769230769</v>
       </c>
       <c r="AR16" t="n">
-        <v>78.96551724137932</v>
+        <v>78.84615384615384</v>
       </c>
       <c r="AS16" t="n">
-        <v>21086206.89655172</v>
+        <v>22307692.30769231</v>
       </c>
       <c r="AT16" t="n">
-        <v>81.20689655172414</v>
+        <v>81.34615384615384</v>
       </c>
       <c r="AU16" t="n">
-        <v>26.38461538461538</v>
+        <v>25.91304347826087</v>
       </c>
       <c r="AV16" t="n">
-        <v>181.2307692307692</v>
+        <v>182.0434782608696</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.884615384615385</v>
+        <v>1.739130434782609</v>
       </c>
       <c r="AX16" t="n">
-        <v>76.69230769230769</v>
+        <v>76.1304347826087</v>
       </c>
       <c r="AY16" t="n">
-        <v>17967692.30769231</v>
+        <v>17050434.7826087</v>
       </c>
       <c r="AZ16" t="n">
-        <v>79.5</v>
+        <v>79.30434782608695</v>
       </c>
       <c r="BA16" t="inlineStr"/>
       <c r="BB16" t="inlineStr"/>
@@ -4092,29 +4108,33 @@
       <c r="Z17" t="n">
         <v>20232024</v>
       </c>
-      <c r="AA17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
       <c r="AB17" t="inlineStr">
         <is>
           <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="AC17" t="n">
-        <v>25</v>
+        <v>25.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>182.7777777777778</v>
+        <v>183.8</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.333333333333333</v>
+        <v>1.4</v>
       </c>
       <c r="AF17" t="n">
-        <v>72.44444444444444</v>
+        <v>72.7</v>
       </c>
       <c r="AG17" t="n">
-        <v>6922222.222222222</v>
+        <v>6700000</v>
       </c>
       <c r="AH17" t="n">
-        <v>77.22222222222223</v>
+        <v>77</v>
       </c>
       <c r="AI17" t="n">
         <v>24.18181818181818</v>
@@ -4153,22 +4173,22 @@
         <v>76.46153846153847</v>
       </c>
       <c r="AU17" t="n">
-        <v>23.77777777777778</v>
+        <v>23.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>182.8518518518518</v>
+        <v>184.0833333333333</v>
       </c>
       <c r="AW17" t="n">
         <v>1</v>
       </c>
       <c r="AX17" t="n">
-        <v>68.03703703703704</v>
+        <v>68.16666666666667</v>
       </c>
       <c r="AY17" t="n">
-        <v>2687962.962962963</v>
+        <v>2873958.333333333</v>
       </c>
       <c r="AZ17" t="n">
-        <v>74.18518518518519</v>
+        <v>74.95833333333333</v>
       </c>
       <c r="BA17" t="n">
         <v>25.66666666666667</v>
@@ -4391,25 +4411,25 @@
         <v>75.21428571428571</v>
       </c>
       <c r="BA18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB18" t="n">
-        <v>180.75</v>
+        <v>182.8</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="BD18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BE18" t="n">
-        <v>299</v>
+        <v>377</v>
       </c>
       <c r="BF18" t="n">
-        <v>31200000</v>
+        <v>38200000</v>
       </c>
       <c r="BG18" t="n">
-        <v>306</v>
+        <v>384</v>
       </c>
       <c r="BH18" t="n">
         <v>30.5</v>
@@ -4539,22 +4559,22 @@
         </is>
       </c>
       <c r="AC19" t="n">
-        <v>25.27272727272727</v>
+        <v>25.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>186.1818181818182</v>
+        <v>187.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.090909090909091</v>
+        <v>1.1</v>
       </c>
       <c r="AF19" t="n">
-        <v>73.36363636363636</v>
+        <v>73.2</v>
       </c>
       <c r="AG19" t="n">
-        <v>5927272.727272728</v>
+        <v>5770000</v>
       </c>
       <c r="AH19" t="n">
-        <v>77.63636363636364</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="AI19" t="n">
         <v>26.18181818181818</v>
@@ -4759,22 +4779,22 @@
         </is>
       </c>
       <c r="AC20" t="n">
-        <v>26</v>
+        <v>25.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>186.7272727272727</v>
+        <v>187.2</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.272727272727273</v>
+        <v>1.2</v>
       </c>
       <c r="AF20" t="n">
-        <v>75.81818181818181</v>
+        <v>75.7</v>
       </c>
       <c r="AG20" t="n">
-        <v>12663636.36363636</v>
+        <v>13080000</v>
       </c>
       <c r="AH20" t="n">
-        <v>79.18181818181819</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="AI20" t="n">
         <v>23.8</v>
@@ -4795,40 +4815,40 @@
         <v>83.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>24.9</v>
+        <v>24.95454545454545</v>
       </c>
       <c r="AP20" t="n">
-        <v>185.7</v>
+        <v>185.0909090909091</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.2</v>
+        <v>1.136363636363636</v>
       </c>
       <c r="AR20" t="n">
-        <v>71.8</v>
+        <v>72.40909090909091</v>
       </c>
       <c r="AS20" t="n">
-        <v>5055000</v>
+        <v>6254545.454545454</v>
       </c>
       <c r="AT20" t="n">
-        <v>76.09999999999999</v>
+        <v>76.31818181818181</v>
       </c>
       <c r="AU20" t="n">
-        <v>26.56521739130435</v>
+        <v>25.75</v>
       </c>
       <c r="AV20" t="n">
-        <v>185.1739130434783</v>
+        <v>187</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.91304347826087</v>
+        <v>1.75</v>
       </c>
       <c r="AX20" t="n">
-        <v>77.17391304347827</v>
+        <v>77.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>24250000</v>
+        <v>27302500</v>
       </c>
       <c r="AZ20" t="n">
-        <v>81.34782608695652</v>
+        <v>82.3</v>
       </c>
       <c r="BA20" t="n">
         <v>22.33333333333333</v>
@@ -4968,7 +4988,11 @@
       <c r="Z21" t="n">
         <v>20232024</v>
       </c>
-      <c r="AA21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
       <c r="AB21" t="inlineStr">
         <is>
           <t>8Sa8HInO</t>
@@ -5029,22 +5053,22 @@
         <v>73.26923076923077</v>
       </c>
       <c r="AU21" t="n">
-        <v>24.33333333333333</v>
+        <v>24.52380952380953</v>
       </c>
       <c r="AV21" t="n">
-        <v>187.2083333333333</v>
+        <v>187.8095238095238</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.125</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="AX21" t="n">
-        <v>73.875</v>
+        <v>73.14285714285714</v>
       </c>
       <c r="AY21" t="n">
-        <v>14041041.66666667</v>
+        <v>12261190.47619048</v>
       </c>
       <c r="AZ21" t="n">
-        <v>78.83333333333333</v>
+        <v>78.0952380952381</v>
       </c>
       <c r="BA21" t="n">
         <v>26.25</v>
@@ -5195,22 +5219,22 @@
         </is>
       </c>
       <c r="AC22" t="n">
-        <v>27.22222222222222</v>
+        <v>27.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>182.5555555555555</v>
+        <v>183.3</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.555555555555556</v>
+        <v>1.6</v>
       </c>
       <c r="AF22" t="n">
-        <v>78.44444444444444</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="AG22" t="n">
-        <v>15944444.44444444</v>
+        <v>16000000</v>
       </c>
       <c r="AH22" t="n">
-        <v>80.44444444444444</v>
+        <v>80.2</v>
       </c>
       <c r="AI22" t="n">
         <v>26</v>
@@ -5231,40 +5255,40 @@
         <v>80.54545454545455</v>
       </c>
       <c r="AO22" t="n">
-        <v>24.8</v>
+        <v>24.85185185185185</v>
       </c>
       <c r="AP22" t="n">
-        <v>181.84</v>
+        <v>181.5555555555555</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.72</v>
+        <v>1.703703703703704</v>
       </c>
       <c r="AR22" t="n">
-        <v>74.28</v>
+        <v>74.51851851851852</v>
       </c>
       <c r="AS22" t="n">
-        <v>11084000</v>
+        <v>11392592.59259259</v>
       </c>
       <c r="AT22" t="n">
-        <v>79.28</v>
+        <v>79.29629629629629</v>
       </c>
       <c r="AU22" t="n">
-        <v>24.33333333333333</v>
+        <v>23.88235294117647</v>
       </c>
       <c r="AV22" t="n">
-        <v>180.5555555555555</v>
+        <v>180.2941176470588</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.611111111111111</v>
+        <v>1.588235294117647</v>
       </c>
       <c r="AX22" t="n">
-        <v>74.94444444444444</v>
+        <v>75</v>
       </c>
       <c r="AY22" t="n">
-        <v>16159722.22222222</v>
+        <v>16951470.58823529</v>
       </c>
       <c r="AZ22" t="n">
-        <v>79.27777777777777</v>
+        <v>79.58823529411765</v>
       </c>
       <c r="BA22" t="n">
         <v>24</v>
@@ -5409,78 +5433,82 @@
           <t>C06aJvIB</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
       <c r="AC23" t="n">
-        <v>25.6</v>
+        <v>25.63636363636364</v>
       </c>
       <c r="AD23" t="n">
-        <v>185.3</v>
+        <v>184</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.5</v>
+        <v>1.545454545454545</v>
       </c>
       <c r="AF23" t="n">
-        <v>76.90000000000001</v>
+        <v>77</v>
       </c>
       <c r="AG23" t="n">
-        <v>14960000</v>
+        <v>15100000</v>
       </c>
       <c r="AH23" t="n">
-        <v>80.5</v>
+        <v>80.36363636363636</v>
       </c>
       <c r="AI23" t="n">
-        <v>24.88888888888889</v>
+        <v>25.3</v>
       </c>
       <c r="AJ23" t="n">
-        <v>181.5555555555555</v>
+        <v>182.7</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.222222222222222</v>
+        <v>1.3</v>
       </c>
       <c r="AL23" t="n">
-        <v>73.77777777777777</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="AM23" t="n">
-        <v>8655555.555555556</v>
+        <v>8260000</v>
       </c>
       <c r="AN23" t="n">
-        <v>77.88888888888889</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="AO23" t="n">
-        <v>25.69565217391304</v>
+        <v>25.69230769230769</v>
       </c>
       <c r="AP23" t="n">
-        <v>181.1739130434783</v>
+        <v>181.8076923076923</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.347826086956522</v>
+        <v>1.346153846153846</v>
       </c>
       <c r="AR23" t="n">
-        <v>73.82608695652173</v>
+        <v>74.23076923076923</v>
       </c>
       <c r="AS23" t="n">
-        <v>9491304.347826088</v>
+        <v>10107692.30769231</v>
       </c>
       <c r="AT23" t="n">
-        <v>78.73913043478261</v>
+        <v>78.80769230769231</v>
       </c>
       <c r="AU23" t="n">
-        <v>26.73076923076923</v>
+        <v>26.81481481481481</v>
       </c>
       <c r="AV23" t="n">
-        <v>182.3076923076923</v>
+        <v>182.7037037037037</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.346153846153846</v>
+        <v>1.37037037037037</v>
       </c>
       <c r="AX23" t="n">
-        <v>71.88461538461539</v>
+        <v>72</v>
       </c>
       <c r="AY23" t="n">
-        <v>3837500</v>
+        <v>3869444.444444444</v>
       </c>
       <c r="AZ23" t="n">
-        <v>76.57692307692308</v>
+        <v>76.51851851851852</v>
       </c>
       <c r="BA23" t="n">
         <v>24</v>
@@ -5620,7 +5648,11 @@
       <c r="Z24" t="n">
         <v>20232024</v>
       </c>
-      <c r="AA24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
       <c r="AB24" t="inlineStr">
         <is>
           <t>69Dxbc61</t>
@@ -5720,25 +5752,25 @@
         <v>377</v>
       </c>
       <c r="BH24" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BI24" t="n">
-        <v>180.75</v>
+        <v>182.8</v>
       </c>
       <c r="BJ24" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="BK24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BL24" t="n">
-        <v>299</v>
+        <v>377</v>
       </c>
       <c r="BM24" t="n">
-        <v>31200000</v>
+        <v>38200000</v>
       </c>
       <c r="BN24" t="n">
-        <v>306</v>
+        <v>384</v>
       </c>
     </row>
     <row r="25">
@@ -5847,58 +5879,58 @@
         </is>
       </c>
       <c r="AC25" t="n">
-        <v>25.45454545454545</v>
+        <v>25.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>188.1818181818182</v>
+        <v>188.7</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.636363636363636</v>
+        <v>1.7</v>
       </c>
       <c r="AF25" t="n">
-        <v>78.63636363636364</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="AG25" t="n">
-        <v>20590909.09090909</v>
+        <v>20000000</v>
       </c>
       <c r="AH25" t="n">
-        <v>82.09090909090909</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="AI25" t="n">
-        <v>26.44444444444444</v>
+        <v>26.5</v>
       </c>
       <c r="AJ25" t="n">
-        <v>182</v>
+        <v>182.8</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.222222222222222</v>
+        <v>2.2</v>
       </c>
       <c r="AL25" t="n">
-        <v>78.66666666666667</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="AM25" t="n">
-        <v>20422222.22222222</v>
+        <v>22030000</v>
       </c>
       <c r="AN25" t="n">
-        <v>80.44444444444444</v>
+        <v>80.8</v>
       </c>
       <c r="AO25" t="n">
-        <v>24.76923076923077</v>
+        <v>24.84</v>
       </c>
       <c r="AP25" t="n">
-        <v>185.5384615384615</v>
+        <v>185.64</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.230769230769231</v>
+        <v>1.24</v>
       </c>
       <c r="AR25" t="n">
-        <v>75.42307692307692</v>
+        <v>75.28</v>
       </c>
       <c r="AS25" t="n">
-        <v>15147500</v>
+        <v>14693400</v>
       </c>
       <c r="AT25" t="n">
-        <v>79.88461538461539</v>
+        <v>79.72</v>
       </c>
       <c r="AU25" t="n">
         <v>24.30769230769231</v>
@@ -6103,22 +6135,22 @@
         <v>76.90000000000001</v>
       </c>
       <c r="AO26" t="n">
-        <v>24.28571428571428</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="AP26" t="n">
-        <v>182.9047619047619</v>
+        <v>184.2222222222222</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.904761904761905</v>
+        <v>1.722222222222222</v>
       </c>
       <c r="AR26" t="n">
-        <v>77.47619047619048</v>
+        <v>76.38888888888889</v>
       </c>
       <c r="AS26" t="n">
-        <v>21530952.38095238</v>
+        <v>16702777.77777778</v>
       </c>
       <c r="AT26" t="n">
-        <v>83.04761904761905</v>
+        <v>82.72222222222223</v>
       </c>
       <c r="AU26" t="n">
         <v>23.94117647058824</v>
@@ -6139,46 +6171,46 @@
         <v>75.94117647058823</v>
       </c>
       <c r="BA26" t="n">
-        <v>26.25</v>
+        <v>27.4</v>
       </c>
       <c r="BB26" t="n">
+        <v>182.8</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>386</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>72500000</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>400</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="BI26" t="n">
         <v>183.5</v>
       </c>
-      <c r="BC26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>309</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>65500000</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>323</v>
-      </c>
-      <c r="BH26" t="n">
-        <v>28.28571428571428</v>
-      </c>
-      <c r="BI26" t="n">
-        <v>184</v>
-      </c>
       <c r="BJ26" t="n">
-        <v>1.714285714285714</v>
+        <v>1.875</v>
       </c>
       <c r="BK26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BL26" t="n">
-        <v>516</v>
+        <v>594</v>
       </c>
       <c r="BM26" t="n">
-        <v>39500000</v>
+        <v>44300000</v>
       </c>
       <c r="BN26" t="n">
-        <v>530</v>
+        <v>608</v>
       </c>
     </row>
     <row r="27">
@@ -6276,7 +6308,11 @@
       <c r="Z27" t="n">
         <v>20232024</v>
       </c>
-      <c r="AA27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
       <c r="AB27" t="inlineStr">
         <is>
           <t>0M9xNN8N</t>
@@ -6301,22 +6337,22 @@
         <v>78.09999999999999</v>
       </c>
       <c r="AI27" t="n">
-        <v>26.54545454545455</v>
+        <v>26.7</v>
       </c>
       <c r="AJ27" t="n">
-        <v>185.9090909090909</v>
+        <v>187.2</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.272727272727273</v>
+        <v>1.3</v>
       </c>
       <c r="AL27" t="n">
-        <v>74.45454545454545</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="AM27" t="n">
-        <v>6190909.090909091</v>
+        <v>6060000</v>
       </c>
       <c r="AN27" t="n">
-        <v>76.81818181818181</v>
+        <v>76.7</v>
       </c>
       <c r="AO27" t="n">
         <v>25.96</v>
@@ -6337,19 +6373,19 @@
         <v>74.04000000000001</v>
       </c>
       <c r="AU27" t="n">
-        <v>23.39285714285714</v>
+        <v>23.33333333333333</v>
       </c>
       <c r="AV27" t="n">
-        <v>185.3928571428571</v>
+        <v>185.8518518518518</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.035714285714286</v>
+        <v>1.037037037037037</v>
       </c>
       <c r="AX27" t="n">
-        <v>70.32142857142857</v>
+        <v>70.14814814814815</v>
       </c>
       <c r="AY27" t="n">
-        <v>3703571.428571429</v>
+        <v>3562962.962962963</v>
       </c>
       <c r="AZ27" t="n">
         <v>78</v>
@@ -6521,22 +6557,22 @@
         <v>75.72727272727273</v>
       </c>
       <c r="AI28" t="n">
-        <v>26.3</v>
+        <v>26</v>
       </c>
       <c r="AJ28" t="n">
-        <v>187.4</v>
+        <v>187.2</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AL28" t="n">
-        <v>75.59999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="AM28" t="n">
-        <v>11030000</v>
+        <v>11680000</v>
       </c>
       <c r="AN28" t="n">
-        <v>79</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="AO28" t="n">
         <v>24.11111111111111</v>
@@ -6557,22 +6593,22 @@
         <v>75.48148148148148</v>
       </c>
       <c r="AU28" t="n">
-        <v>25.23809523809524</v>
+        <v>25</v>
       </c>
       <c r="AV28" t="n">
-        <v>184.8571428571429</v>
+        <v>185</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.380952380952381</v>
+        <v>1.35</v>
       </c>
       <c r="AX28" t="n">
-        <v>71.61904761904762</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="AY28" t="n">
-        <v>5732142.857142857</v>
+        <v>5593750</v>
       </c>
       <c r="AZ28" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="BA28" t="n">
         <v>26.66666666666667</v>
@@ -6723,22 +6759,22 @@
         </is>
       </c>
       <c r="AC29" t="n">
-        <v>28</v>
+        <v>27.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>182.2727272727273</v>
+        <v>183</v>
       </c>
       <c r="AE29" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AF29" t="n">
-        <v>78.72727272727273</v>
+        <v>78.5</v>
       </c>
       <c r="AG29" t="n">
-        <v>19472727.27272727</v>
+        <v>18920000</v>
       </c>
       <c r="AH29" t="n">
-        <v>80.09090909090909</v>
+        <v>80</v>
       </c>
       <c r="AI29" t="n">
         <v>26.27272727272727</v>
@@ -6759,22 +6795,22 @@
         <v>76.09090909090909</v>
       </c>
       <c r="AO29" t="n">
-        <v>25.65217391304348</v>
+        <v>25.45454545454545</v>
       </c>
       <c r="AP29" t="n">
-        <v>181.9565217391304</v>
+        <v>182.2727272727273</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.826086956521739</v>
+        <v>1.772727272727273</v>
       </c>
       <c r="AR29" t="n">
-        <v>76.73913043478261</v>
+        <v>76.54545454545455</v>
       </c>
       <c r="AS29" t="n">
-        <v>17141739.13043478</v>
+        <v>16784545.45454545</v>
       </c>
       <c r="AT29" t="n">
-        <v>80.21739130434783</v>
+        <v>80.18181818181819</v>
       </c>
       <c r="AU29" t="n">
         <v>24.5</v>
@@ -6943,22 +6979,22 @@
         </is>
       </c>
       <c r="AC30" t="n">
-        <v>26</v>
+        <v>25.33333333333333</v>
       </c>
       <c r="AD30" t="n">
-        <v>182.4</v>
+        <v>183.4444444444445</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.8</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="AF30" t="n">
-        <v>78.7</v>
+        <v>79.11111111111111</v>
       </c>
       <c r="AG30" t="n">
-        <v>21290000</v>
+        <v>23222222.22222222</v>
       </c>
       <c r="AH30" t="n">
-        <v>82.40000000000001</v>
+        <v>83.22222222222223</v>
       </c>
       <c r="AI30" t="n">
         <v>24</v>
@@ -6979,22 +7015,22 @@
         <v>77</v>
       </c>
       <c r="AO30" t="n">
-        <v>24.40740740740741</v>
+        <v>24.11538461538462</v>
       </c>
       <c r="AP30" t="n">
-        <v>184.2962962962963</v>
+        <v>184.7307692307692</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.703703703703704</v>
+        <v>1.653846153846154</v>
       </c>
       <c r="AR30" t="n">
-        <v>78.22222222222223</v>
+        <v>78.34615384615384</v>
       </c>
       <c r="AS30" t="n">
-        <v>32945370.37037037</v>
+        <v>34062500</v>
       </c>
       <c r="AT30" t="n">
-        <v>83.18518518518519</v>
+        <v>83.5</v>
       </c>
       <c r="AU30" t="n">
         <v>27.03571428571428</v>
@@ -7163,22 +7199,22 @@
         </is>
       </c>
       <c r="AC31" t="n">
-        <v>26.72727272727273</v>
+        <v>26.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>183.4545454545455</v>
+        <v>183.3</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.727272727272727</v>
+        <v>1.7</v>
       </c>
       <c r="AF31" t="n">
-        <v>80.72727272727273</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="AG31" t="n">
-        <v>36945454.54545455</v>
+        <v>40370000</v>
       </c>
       <c r="AH31" t="n">
-        <v>82.18181818181819</v>
+        <v>83</v>
       </c>
       <c r="AI31" t="n">
         <v>23.45454545454545</v>
@@ -7419,40 +7455,40 @@
         <v>83.72727272727273</v>
       </c>
       <c r="AO32" t="n">
-        <v>23.10344827586207</v>
+        <v>22.76923076923077</v>
       </c>
       <c r="AP32" t="n">
-        <v>183.0344827586207</v>
+        <v>184.1923076923077</v>
       </c>
       <c r="AQ32" t="n">
         <v>1</v>
       </c>
       <c r="AR32" t="n">
-        <v>67.44827586206897</v>
+        <v>67.5</v>
       </c>
       <c r="AS32" t="n">
-        <v>2166379.310344827</v>
+        <v>2277884.615384615</v>
       </c>
       <c r="AT32" t="n">
-        <v>74.75862068965517</v>
+        <v>75.53846153846153</v>
       </c>
       <c r="AU32" t="n">
-        <v>28.35714285714286</v>
+        <v>28.14814814814815</v>
       </c>
       <c r="AV32" t="n">
-        <v>179.1428571428571</v>
+        <v>179.5185185185185</v>
       </c>
       <c r="AW32" t="n">
-        <v>2.178571428571428</v>
+        <v>2.111111111111111</v>
       </c>
       <c r="AX32" t="n">
-        <v>79.85714285714286</v>
+        <v>79.85185185185185</v>
       </c>
       <c r="AY32" t="n">
-        <v>31125000</v>
+        <v>31888888.88888889</v>
       </c>
       <c r="AZ32" t="n">
-        <v>81.17857142857143</v>
+        <v>81.22222222222223</v>
       </c>
       <c r="BA32" t="n">
         <v>21.4</v>
@@ -7657,43 +7693,43 @@
         <v>74.23809523809524</v>
       </c>
       <c r="AU33" t="n">
-        <v>25</v>
+        <v>24.58823529411765</v>
       </c>
       <c r="AV33" t="n">
-        <v>181.5555555555555</v>
+        <v>181.3529411764706</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.444444444444444</v>
+        <v>1.411764705882353</v>
       </c>
       <c r="AX33" t="n">
-        <v>74.55555555555556</v>
+        <v>74.58823529411765</v>
       </c>
       <c r="AY33" t="n">
-        <v>13404166.66666667</v>
+        <v>14033823.52941176</v>
       </c>
       <c r="AZ33" t="n">
-        <v>77.88888888888889</v>
+        <v>78.11764705882354</v>
       </c>
       <c r="BA33" t="n">
-        <v>26.28571428571428</v>
+        <v>27</v>
       </c>
       <c r="BB33" t="n">
-        <v>182</v>
+        <v>183.125</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.285714285714286</v>
+        <v>1.25</v>
       </c>
       <c r="BD33" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BE33" t="n">
-        <v>521</v>
+        <v>599</v>
       </c>
       <c r="BF33" t="n">
-        <v>46800000</v>
+        <v>53800000</v>
       </c>
       <c r="BG33" t="n">
-        <v>537</v>
+        <v>615</v>
       </c>
       <c r="BH33" t="n">
         <v>26</v>
@@ -7841,22 +7877,22 @@
         <v>76.09999999999999</v>
       </c>
       <c r="AI34" t="n">
-        <v>25.90909090909091</v>
+        <v>26.2</v>
       </c>
       <c r="AJ34" t="n">
-        <v>186.3636363636364</v>
+        <v>186.7</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.636363636363636</v>
+        <v>1.7</v>
       </c>
       <c r="AL34" t="n">
-        <v>78.90909090909091</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="AM34" t="n">
-        <v>20636363.63636364</v>
+        <v>20050000</v>
       </c>
       <c r="AN34" t="n">
-        <v>81.90909090909091</v>
+        <v>81.7</v>
       </c>
       <c r="AO34" t="n">
         <v>23.26315789473684</v>
@@ -7877,22 +7913,22 @@
         <v>76.36842105263158</v>
       </c>
       <c r="AU34" t="n">
-        <v>23.92</v>
+        <v>23.95833333333333</v>
       </c>
       <c r="AV34" t="n">
-        <v>187.28</v>
+        <v>187.4583333333333</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.16</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="AX34" t="n">
-        <v>75.08</v>
+        <v>74.91666666666667</v>
       </c>
       <c r="AY34" t="n">
-        <v>15893400</v>
+        <v>15451458.33333333</v>
       </c>
       <c r="AZ34" t="n">
-        <v>80.2</v>
+        <v>80.04166666666667</v>
       </c>
       <c r="BA34" t="n">
         <v>27.625</v>
@@ -8061,58 +8097,58 @@
         <v>80.90000000000001</v>
       </c>
       <c r="AI35" t="n">
-        <v>25.5</v>
+        <v>25.55555555555556</v>
       </c>
       <c r="AJ35" t="n">
-        <v>185.8</v>
+        <v>187</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.9</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="AL35" t="n">
-        <v>81.2</v>
+        <v>80.88888888888889</v>
       </c>
       <c r="AM35" t="n">
-        <v>33850000</v>
+        <v>32000000</v>
       </c>
       <c r="AN35" t="n">
-        <v>84.2</v>
+        <v>84.11111111111111</v>
       </c>
       <c r="AO35" t="n">
-        <v>25.34615384615385</v>
+        <v>25.40740740740741</v>
       </c>
       <c r="AP35" t="n">
-        <v>182.8076923076923</v>
+        <v>183.0740740740741</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.961538461538461</v>
+        <v>1.962962962962963</v>
       </c>
       <c r="AR35" t="n">
-        <v>77.34615384615384</v>
+        <v>77.55555555555556</v>
       </c>
       <c r="AS35" t="n">
-        <v>17916346.15384615</v>
+        <v>18604629.62962963</v>
       </c>
       <c r="AT35" t="n">
-        <v>81.19230769230769</v>
+        <v>81.29629629629629</v>
       </c>
       <c r="AU35" t="n">
-        <v>25.30434782608696</v>
+        <v>25.31818181818182</v>
       </c>
       <c r="AV35" t="n">
-        <v>183.4782608695652</v>
+        <v>183.8636363636364</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.956521739130435</v>
+        <v>1.909090909090909</v>
       </c>
       <c r="AX35" t="n">
-        <v>77.39130434782609</v>
+        <v>77.09090909090909</v>
       </c>
       <c r="AY35" t="n">
-        <v>19702173.91304348</v>
+        <v>18302272.72727273</v>
       </c>
       <c r="AZ35" t="n">
-        <v>81.95652173913044</v>
+        <v>81.81818181818181</v>
       </c>
       <c r="BA35" t="inlineStr"/>
       <c r="BB35" t="inlineStr"/>
@@ -8122,25 +8158,25 @@
       <c r="BF35" t="inlineStr"/>
       <c r="BG35" t="inlineStr"/>
       <c r="BH35" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BI35" t="n">
-        <v>184.5</v>
+        <v>183</v>
       </c>
       <c r="BJ35" t="n">
-        <v>2.5</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="BK35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BL35" t="n">
-        <v>159</v>
+        <v>236</v>
       </c>
       <c r="BM35" t="n">
-        <v>52500000</v>
+        <v>59500000</v>
       </c>
       <c r="BN35" t="n">
-        <v>168</v>
+        <v>245</v>
       </c>
     </row>
     <row r="36">
@@ -8243,24 +8279,28 @@
           <t>Iw7eKK25</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
       <c r="AC36" t="n">
-        <v>26.63636363636364</v>
+        <v>26.1</v>
       </c>
       <c r="AD36" t="n">
-        <v>182.6363636363636</v>
+        <v>183.6</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.090909090909091</v>
+        <v>2</v>
       </c>
       <c r="AF36" t="n">
-        <v>81</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="AG36" t="n">
-        <v>36036363.63636363</v>
+        <v>39250000</v>
       </c>
       <c r="AH36" t="n">
-        <v>83.81818181818181</v>
+        <v>84.7</v>
       </c>
       <c r="AI36" t="n">
         <v>25.2</v>
@@ -8281,22 +8321,22 @@
         <v>77.8</v>
       </c>
       <c r="AO36" t="n">
-        <v>22.57894736842105</v>
+        <v>22.05555555555556</v>
       </c>
       <c r="AP36" t="n">
-        <v>185.6842105263158</v>
+        <v>186.3888888888889</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.263157894736842</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="AR36" t="n">
-        <v>74.21052631578948</v>
+        <v>74.16666666666667</v>
       </c>
       <c r="AS36" t="n">
-        <v>17738157.89473684</v>
+        <v>18506944.44444444</v>
       </c>
       <c r="AT36" t="n">
-        <v>81.47368421052632</v>
+        <v>81.83333333333333</v>
       </c>
       <c r="AU36" t="n">
         <v>27.58823529411765</v>
@@ -8519,22 +8559,22 @@
         <v>75.23076923076923</v>
       </c>
       <c r="AU37" t="n">
-        <v>23.77777777777778</v>
+        <v>23.5</v>
       </c>
       <c r="AV37" t="n">
-        <v>183.1481481481482</v>
+        <v>184.4166666666667</v>
       </c>
       <c r="AW37" t="n">
         <v>1</v>
       </c>
       <c r="AX37" t="n">
-        <v>67.48148148148148</v>
+        <v>67.54166666666667</v>
       </c>
       <c r="AY37" t="n">
-        <v>2393518.518518519</v>
+        <v>2542708.333333333</v>
       </c>
       <c r="AZ37" t="n">
-        <v>74.22222222222223</v>
+        <v>75</v>
       </c>
       <c r="BA37" t="n">
         <v>27.75</v>
@@ -8739,22 +8779,22 @@
         <v>75.92592592592592</v>
       </c>
       <c r="AU38" t="n">
-        <v>26.60869565217391</v>
+        <v>26.5</v>
       </c>
       <c r="AV38" t="n">
-        <v>180.3478260869565</v>
+        <v>181.0769230769231</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.782608695652174</v>
+        <v>1.730769230769231</v>
       </c>
       <c r="AX38" t="n">
-        <v>75.52173913043478</v>
+        <v>75.73076923076923</v>
       </c>
       <c r="AY38" t="n">
-        <v>10469565.2173913</v>
+        <v>10973076.92307692</v>
       </c>
       <c r="AZ38" t="n">
-        <v>79.08695652173913</v>
+        <v>79.11538461538461</v>
       </c>
       <c r="BA38" t="n">
         <v>25.66666666666667</v>
@@ -8899,7 +8939,11 @@
           <t>69Dxbc61</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
       <c r="AC39" t="n">
         <v>25.90909090909091</v>
       </c>
@@ -9121,58 +9165,58 @@
         </is>
       </c>
       <c r="AC40" t="n">
-        <v>25.36363636363636</v>
+        <v>25.4</v>
       </c>
       <c r="AD40" t="n">
-        <v>186</v>
+        <v>187.3</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.181818181818182</v>
+        <v>1.2</v>
       </c>
       <c r="AF40" t="n">
-        <v>73.45454545454545</v>
+        <v>73.3</v>
       </c>
       <c r="AG40" t="n">
-        <v>6131818.181818182</v>
+        <v>5995000</v>
       </c>
       <c r="AH40" t="n">
-        <v>77.63636363636364</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="AI40" t="n">
-        <v>26.90909090909091</v>
+        <v>26.2</v>
       </c>
       <c r="AJ40" t="n">
-        <v>182.3636363636364</v>
+        <v>183.7</v>
       </c>
       <c r="AK40" t="n">
-        <v>2.272727272727273</v>
+        <v>2.1</v>
       </c>
       <c r="AL40" t="n">
-        <v>81.27272727272727</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="AM40" t="n">
-        <v>34954545.45454545</v>
+        <v>37400000</v>
       </c>
       <c r="AN40" t="n">
-        <v>83.81818181818181</v>
+        <v>84.2</v>
       </c>
       <c r="AO40" t="n">
-        <v>24.70833333333333</v>
+        <v>24.69565217391304</v>
       </c>
       <c r="AP40" t="n">
-        <v>185.125</v>
+        <v>185.6521739130435</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.166666666666667</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="AR40" t="n">
-        <v>70.33333333333333</v>
+        <v>70.1304347826087</v>
       </c>
       <c r="AS40" t="n">
-        <v>3279166.666666667</v>
+        <v>3095652.173913043</v>
       </c>
       <c r="AT40" t="n">
-        <v>76.54166666666667</v>
+        <v>76.47826086956522</v>
       </c>
       <c r="AU40" t="n">
         <v>28.57142857142857</v>
@@ -9330,47 +9374,51 @@
       <c r="Z41" t="n">
         <v>20232024</v>
       </c>
-      <c r="AA41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
       <c r="AB41" t="inlineStr">
         <is>
           <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="AC41" t="n">
-        <v>24.11111111111111</v>
+        <v>24.6</v>
       </c>
       <c r="AD41" t="n">
-        <v>182.1111111111111</v>
+        <v>183.2</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.222222222222222</v>
+        <v>1.3</v>
       </c>
       <c r="AF41" t="n">
-        <v>72.66666666666667</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="AG41" t="n">
-        <v>8222222.222222222</v>
+        <v>7870000</v>
       </c>
       <c r="AH41" t="n">
-        <v>78.66666666666667</v>
+        <v>78.3</v>
       </c>
       <c r="AI41" t="n">
-        <v>28.09090909090909</v>
+        <v>27.9</v>
       </c>
       <c r="AJ41" t="n">
-        <v>183.0909090909091</v>
+        <v>183.9</v>
       </c>
       <c r="AK41" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AL41" t="n">
-        <v>79.18181818181819</v>
+        <v>79</v>
       </c>
       <c r="AM41" t="n">
-        <v>21745454.54545455</v>
+        <v>21420000</v>
       </c>
       <c r="AN41" t="n">
-        <v>80.54545454545455</v>
+        <v>80.5</v>
       </c>
       <c r="AO41" t="n">
         <v>27.44</v>
@@ -9391,22 +9439,22 @@
         <v>75.2</v>
       </c>
       <c r="AU41" t="n">
-        <v>27</v>
+        <v>26.8695652173913</v>
       </c>
       <c r="AV41" t="n">
-        <v>182.2916666666667</v>
+        <v>182.6086956521739</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.833333333333333</v>
+        <v>1.782608695652174</v>
       </c>
       <c r="AX41" t="n">
-        <v>78</v>
+        <v>77.8695652173913</v>
       </c>
       <c r="AY41" t="n">
-        <v>17191666.66666667</v>
+        <v>16852173.91304348</v>
       </c>
       <c r="AZ41" t="n">
-        <v>80.125</v>
+        <v>80.08695652173913</v>
       </c>
       <c r="BA41" t="n">
         <v>26.5</v>
@@ -9557,22 +9605,22 @@
         </is>
       </c>
       <c r="AC42" t="n">
-        <v>26</v>
+        <v>25.7</v>
       </c>
       <c r="AD42" t="n">
-        <v>187.3</v>
+        <v>187.1</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AF42" t="n">
-        <v>76.8</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="AG42" t="n">
-        <v>15140000</v>
+        <v>15790000</v>
       </c>
       <c r="AH42" t="n">
-        <v>80</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="AI42" t="n">
         <v>24.45454545454545</v>
@@ -9593,22 +9641,22 @@
         <v>80.81818181818181</v>
       </c>
       <c r="AO42" t="n">
-        <v>24.47058823529412</v>
+        <v>24.61111111111111</v>
       </c>
       <c r="AP42" t="n">
-        <v>183.0588235294118</v>
+        <v>182.8888888888889</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.411764705882353</v>
+        <v>1.388888888888889</v>
       </c>
       <c r="AR42" t="n">
-        <v>71.05882352941177</v>
+        <v>71.44444444444444</v>
       </c>
       <c r="AS42" t="n">
-        <v>4405882.352941177</v>
+        <v>4994444.444444444</v>
       </c>
       <c r="AT42" t="n">
-        <v>75.29411764705883</v>
+        <v>75.44444444444444</v>
       </c>
       <c r="AU42" t="n">
         <v>23.03571428571428</v>
@@ -9766,7 +9814,11 @@
       <c r="Z43" t="n">
         <v>20232024</v>
       </c>
-      <c r="AA43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
       <c r="AB43" t="inlineStr">
         <is>
           <t>69Dxbc61</t>
@@ -9993,22 +10045,22 @@
         </is>
       </c>
       <c r="AC44" t="n">
-        <v>24.66666666666667</v>
+        <v>24.81818181818182</v>
       </c>
       <c r="AD44" t="n">
-        <v>182.2222222222222</v>
+        <v>181.4545454545455</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.444444444444444</v>
+        <v>1.454545454545455</v>
       </c>
       <c r="AF44" t="n">
-        <v>74.44444444444444</v>
+        <v>75</v>
       </c>
       <c r="AG44" t="n">
-        <v>9388888.888888888</v>
+        <v>10454545.45454546</v>
       </c>
       <c r="AH44" t="n">
-        <v>79.22222222222223</v>
+        <v>79.27272727272727</v>
       </c>
       <c r="AI44" t="n">
         <v>25.27272727272727</v>
@@ -10029,40 +10081,40 @@
         <v>77.81818181818181</v>
       </c>
       <c r="AO44" t="n">
-        <v>25.20833333333333</v>
+        <v>25.28</v>
       </c>
       <c r="AP44" t="n">
-        <v>182.5416666666667</v>
+        <v>182.84</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AR44" t="n">
-        <v>74.54166666666667</v>
+        <v>74.68000000000001</v>
       </c>
       <c r="AS44" t="n">
-        <v>13033333.33333333</v>
+        <v>13172000</v>
       </c>
       <c r="AT44" t="n">
-        <v>79.16666666666667</v>
+        <v>79.12</v>
       </c>
       <c r="AU44" t="n">
-        <v>23.77777777777778</v>
+        <v>23.625</v>
       </c>
       <c r="AV44" t="n">
-        <v>182.1851851851852</v>
+        <v>183.3333333333333</v>
       </c>
       <c r="AW44" t="n">
-        <v>1.074074074074074</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="AX44" t="n">
-        <v>70.29629629629629</v>
+        <v>69.70833333333333</v>
       </c>
       <c r="AY44" t="n">
-        <v>3714814.814814815</v>
+        <v>3241666.666666667</v>
       </c>
       <c r="AZ44" t="n">
-        <v>77.22222222222223</v>
+        <v>77.125</v>
       </c>
       <c r="BA44" t="n">
         <v>26</v>
@@ -10249,22 +10301,22 @@
         <v>76.54545454545455</v>
       </c>
       <c r="AO45" t="n">
-        <v>25.80769230769231</v>
+        <v>26.17391304347826</v>
       </c>
       <c r="AP45" t="n">
-        <v>185.9230769230769</v>
+        <v>186.304347826087</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.576923076923077</v>
+        <v>1.652173913043478</v>
       </c>
       <c r="AR45" t="n">
-        <v>76.5</v>
+        <v>76.17391304347827</v>
       </c>
       <c r="AS45" t="n">
-        <v>17759038.46153846</v>
+        <v>16618913.04347826</v>
       </c>
       <c r="AT45" t="n">
-        <v>79.69230769230769</v>
+        <v>79.1304347826087</v>
       </c>
       <c r="AU45" t="n">
         <v>25.5</v>
@@ -10433,40 +10485,40 @@
         </is>
       </c>
       <c r="AC46" t="n">
-        <v>26.72727272727273</v>
+        <v>26.2</v>
       </c>
       <c r="AD46" t="n">
-        <v>183.4545454545455</v>
+        <v>183.3</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.727272727272727</v>
+        <v>1.7</v>
       </c>
       <c r="AF46" t="n">
-        <v>80.72727272727273</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="AG46" t="n">
-        <v>36945454.54545455</v>
+        <v>40370000</v>
       </c>
       <c r="AH46" t="n">
-        <v>82.18181818181819</v>
+        <v>83</v>
       </c>
       <c r="AI46" t="n">
-        <v>26.77777777777778</v>
+        <v>26.8</v>
       </c>
       <c r="AJ46" t="n">
-        <v>183.3333333333333</v>
+        <v>184</v>
       </c>
       <c r="AK46" t="n">
         <v>2</v>
       </c>
       <c r="AL46" t="n">
-        <v>78.88888888888889</v>
+        <v>79.3</v>
       </c>
       <c r="AM46" t="n">
-        <v>22811111.11111111</v>
+        <v>24180000</v>
       </c>
       <c r="AN46" t="n">
-        <v>80.55555555555556</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="AO46" t="n">
         <v>24.16666666666667</v>
@@ -10877,58 +10929,58 @@
         <v>84.90909090909091</v>
       </c>
       <c r="AI48" t="n">
-        <v>25.63636363636364</v>
+        <v>25.2</v>
       </c>
       <c r="AJ48" t="n">
-        <v>186.0909090909091</v>
+        <v>186.5</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.363636363636364</v>
+        <v>1.3</v>
       </c>
       <c r="AL48" t="n">
-        <v>76.54545454545455</v>
+        <v>76.5</v>
       </c>
       <c r="AM48" t="n">
-        <v>14472727.27272727</v>
+        <v>15070000</v>
       </c>
       <c r="AN48" t="n">
-        <v>80.27272727272727</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="AO48" t="n">
-        <v>27.67857142857143</v>
+        <v>26.92</v>
       </c>
       <c r="AP48" t="n">
-        <v>181.4285714285714</v>
+        <v>182.92</v>
       </c>
       <c r="AQ48" t="n">
-        <v>2.035714285714286</v>
+        <v>1.8</v>
       </c>
       <c r="AR48" t="n">
-        <v>78.75</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="AS48" t="n">
-        <v>21196428.57142857</v>
+        <v>22480000</v>
       </c>
       <c r="AT48" t="n">
-        <v>81.60714285714286</v>
+        <v>81.8</v>
       </c>
       <c r="AU48" t="n">
-        <v>26.42857142857143</v>
+        <v>26.3125</v>
       </c>
       <c r="AV48" t="n">
-        <v>186.7857142857143</v>
+        <v>185.8125</v>
       </c>
       <c r="AW48" t="n">
-        <v>1.214285714285714</v>
+        <v>1.125</v>
       </c>
       <c r="AX48" t="n">
-        <v>71.57142857142857</v>
+        <v>72.4375</v>
       </c>
       <c r="AY48" t="n">
-        <v>4200000</v>
+        <v>5956250</v>
       </c>
       <c r="AZ48" t="n">
-        <v>74.5</v>
+        <v>75</v>
       </c>
       <c r="BA48" t="n">
         <v>27</v>
@@ -11079,22 +11131,22 @@
         </is>
       </c>
       <c r="AC49" t="n">
-        <v>26.36363636363636</v>
+        <v>26</v>
       </c>
       <c r="AD49" t="n">
-        <v>183.3636363636364</v>
+        <v>184.2</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.818181818181818</v>
+        <v>1.7</v>
       </c>
       <c r="AF49" t="n">
-        <v>78.18181818181819</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AG49" t="n">
-        <v>20609090.90909091</v>
+        <v>20170000</v>
       </c>
       <c r="AH49" t="n">
-        <v>80.90909090909091</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="AI49" t="n">
         <v>24.45454545454545</v>
@@ -11115,22 +11167,22 @@
         <v>77.36363636363636</v>
       </c>
       <c r="AO49" t="n">
-        <v>27.70833333333333</v>
+        <v>27.60869565217391</v>
       </c>
       <c r="AP49" t="n">
-        <v>181.75</v>
+        <v>182.0434782608696</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.916666666666667</v>
+        <v>1.869565217391304</v>
       </c>
       <c r="AR49" t="n">
-        <v>77.20833333333333</v>
+        <v>77.04347826086956</v>
       </c>
       <c r="AS49" t="n">
-        <v>16365000</v>
+        <v>15989565.2173913</v>
       </c>
       <c r="AT49" t="n">
-        <v>79.33333333333333</v>
+        <v>79.26086956521739</v>
       </c>
       <c r="AU49" t="n">
         <v>25</v>
@@ -11317,40 +11369,40 @@
         <v>84.44444444444444</v>
       </c>
       <c r="AI50" t="n">
-        <v>25.81818181818182</v>
+        <v>25.2</v>
       </c>
       <c r="AJ50" t="n">
-        <v>185.6363636363636</v>
+        <v>186.9</v>
       </c>
       <c r="AK50" t="n">
-        <v>1.727272727272727</v>
+        <v>1.6</v>
       </c>
       <c r="AL50" t="n">
-        <v>78.72727272727273</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="AM50" t="n">
-        <v>24081818.18181818</v>
+        <v>26100000</v>
       </c>
       <c r="AN50" t="n">
-        <v>82.36363636363636</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="AO50" t="n">
-        <v>24.68181818181818</v>
+        <v>25</v>
       </c>
       <c r="AP50" t="n">
-        <v>182.6818181818182</v>
+        <v>183.7</v>
       </c>
       <c r="AQ50" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR50" t="n">
-        <v>77.77272727272727</v>
+        <v>76.8</v>
       </c>
       <c r="AS50" t="n">
-        <v>21847727.27272727</v>
+        <v>16807500</v>
       </c>
       <c r="AT50" t="n">
-        <v>82.22727272727273</v>
+        <v>81.55</v>
       </c>
       <c r="AU50" t="n">
         <v>22.52</v>
@@ -11508,8 +11560,16 @@
       <c r="Z51" t="n">
         <v>20232024</v>
       </c>
-      <c r="AA51" t="inlineStr"/>
-      <c r="AB51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
       <c r="AC51" t="n">
         <v>24</v>
       </c>
@@ -11529,22 +11589,22 @@
         <v>77.72727272727273</v>
       </c>
       <c r="AI51" t="n">
-        <v>24.4</v>
+        <v>24.81818181818182</v>
       </c>
       <c r="AJ51" t="n">
-        <v>181.8</v>
+        <v>182.8181818181818</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.2</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="AL51" t="n">
-        <v>72.2</v>
+        <v>72.45454545454545</v>
       </c>
       <c r="AM51" t="n">
-        <v>6240000</v>
+        <v>6100000</v>
       </c>
       <c r="AN51" t="n">
-        <v>78.09999999999999</v>
+        <v>77.81818181818181</v>
       </c>
       <c r="AO51" t="n">
         <v>23.68</v>
@@ -11767,22 +11827,22 @@
         <v>76.90000000000001</v>
       </c>
       <c r="AO52" t="n">
-        <v>23.86666666666667</v>
+        <v>23.62962962962963</v>
       </c>
       <c r="AP52" t="n">
-        <v>184.6333333333333</v>
+        <v>185.9259259259259</v>
       </c>
       <c r="AQ52" t="n">
         <v>1</v>
       </c>
       <c r="AR52" t="n">
-        <v>67.83333333333333</v>
+        <v>67.92592592592592</v>
       </c>
       <c r="AS52" t="n">
-        <v>2202500</v>
+        <v>2313888.888888889</v>
       </c>
       <c r="AT52" t="n">
-        <v>73.73333333333333</v>
+        <v>74.37037037037037</v>
       </c>
       <c r="AU52" t="n">
         <v>24</v>
@@ -11824,25 +11884,25 @@
         <v>220</v>
       </c>
       <c r="BH52" t="n">
-        <v>29.5</v>
+        <v>30.42857142857143</v>
       </c>
       <c r="BI52" t="n">
-        <v>184.5</v>
+        <v>183.8571428571429</v>
       </c>
       <c r="BJ52" t="n">
-        <v>1.833333333333333</v>
+        <v>2</v>
       </c>
       <c r="BK52" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BL52" t="n">
-        <v>449</v>
+        <v>527</v>
       </c>
       <c r="BM52" t="n">
-        <v>38100000</v>
+        <v>42900000</v>
       </c>
       <c r="BN52" t="n">
-        <v>456</v>
+        <v>534</v>
       </c>
     </row>
     <row r="53">
@@ -11987,40 +12047,40 @@
         <v>80.8</v>
       </c>
       <c r="AO53" t="n">
-        <v>25.75</v>
+        <v>26.04761904761905</v>
       </c>
       <c r="AP53" t="n">
-        <v>182.4</v>
+        <v>182.8095238095238</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.05</v>
+        <v>1.047619047619048</v>
       </c>
       <c r="AR53" t="n">
-        <v>70.34999999999999</v>
+        <v>70.71428571428571</v>
       </c>
       <c r="AS53" t="n">
-        <v>2620000</v>
+        <v>2828571.428571429</v>
       </c>
       <c r="AT53" t="n">
-        <v>74.3</v>
+        <v>74.47619047619048</v>
       </c>
       <c r="AU53" t="n">
-        <v>27.42857142857143</v>
+        <v>27.4</v>
       </c>
       <c r="AV53" t="n">
-        <v>184.7380952380952</v>
+        <v>185.0888888888889</v>
       </c>
       <c r="AW53" t="n">
-        <v>2.261904761904762</v>
+        <v>2.244444444444444</v>
       </c>
       <c r="AX53" t="n">
-        <v>78.57142857142857</v>
+        <v>78.86666666666666</v>
       </c>
       <c r="AY53" t="n">
-        <v>20411904.76190476</v>
+        <v>21484444.44444444</v>
       </c>
       <c r="AZ53" t="n">
-        <v>80.45238095238095</v>
+        <v>80.68888888888888</v>
       </c>
       <c r="BA53" t="n">
         <v>27</v>
@@ -12193,40 +12253,40 @@
         <v>85.27272727272727</v>
       </c>
       <c r="AO54" t="n">
-        <v>26.04545454545455</v>
+        <v>25.76190476190476</v>
       </c>
       <c r="AP54" t="n">
-        <v>182.6363636363636</v>
+        <v>183.0952380952381</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.590909090909091</v>
+        <v>1.523809523809524</v>
       </c>
       <c r="AR54" t="n">
-        <v>77.72727272727273</v>
+        <v>77.85714285714286</v>
       </c>
       <c r="AS54" t="n">
-        <v>20728409.09090909</v>
+        <v>21529761.9047619</v>
       </c>
       <c r="AT54" t="n">
-        <v>81.72727272727273</v>
+        <v>82.04761904761905</v>
       </c>
       <c r="AU54" t="n">
-        <v>26.75862068965517</v>
+        <v>26.5</v>
       </c>
       <c r="AV54" t="n">
-        <v>182.6551724137931</v>
+        <v>183.1428571428571</v>
       </c>
       <c r="AW54" t="n">
-        <v>1.931034482758621</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="AX54" t="n">
-        <v>79.37931034482759</v>
+        <v>79.35714285714286</v>
       </c>
       <c r="AY54" t="n">
-        <v>24479310.34482758</v>
+        <v>24978571.42857143</v>
       </c>
       <c r="AZ54" t="n">
-        <v>82</v>
+        <v>82.07142857142857</v>
       </c>
       <c r="BA54" t="n">
         <v>29.25</v>
@@ -12363,22 +12423,22 @@
         </is>
       </c>
       <c r="AC55" t="n">
-        <v>27.2</v>
+        <v>27.18181818181818</v>
       </c>
       <c r="AD55" t="n">
-        <v>182.8</v>
+        <v>183.4545454545455</v>
       </c>
       <c r="AE55" t="n">
-        <v>2.3</v>
+        <v>2.272727272727273</v>
       </c>
       <c r="AF55" t="n">
-        <v>79.09999999999999</v>
+        <v>79.45454545454545</v>
       </c>
       <c r="AG55" t="n">
-        <v>22430000</v>
+        <v>23709090.90909091</v>
       </c>
       <c r="AH55" t="n">
-        <v>79.7</v>
+        <v>80.09090909090909</v>
       </c>
       <c r="AI55" t="n">
         <v>25</v>
@@ -12572,47 +12632,51 @@
       <c r="Z56" t="n">
         <v>20232024</v>
       </c>
-      <c r="AA56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
       <c r="AB56" t="inlineStr">
         <is>
           <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="AC56" t="n">
-        <v>25.33333333333333</v>
+        <v>25.7</v>
       </c>
       <c r="AD56" t="n">
-        <v>182.6666666666667</v>
+        <v>183.7</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.333333333333333</v>
+        <v>1.4</v>
       </c>
       <c r="AF56" t="n">
-        <v>73.88888888888889</v>
+        <v>74</v>
       </c>
       <c r="AG56" t="n">
-        <v>8577777.777777778</v>
+        <v>8190000</v>
       </c>
       <c r="AH56" t="n">
-        <v>77.66666666666667</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="AI56" t="n">
-        <v>24.90909090909091</v>
+        <v>25.1</v>
       </c>
       <c r="AJ56" t="n">
-        <v>186.1818181818182</v>
+        <v>186.5</v>
       </c>
       <c r="AK56" t="n">
-        <v>1.272727272727273</v>
+        <v>1.3</v>
       </c>
       <c r="AL56" t="n">
-        <v>77.36363636363636</v>
+        <v>77.2</v>
       </c>
       <c r="AM56" t="n">
-        <v>17363636.36363636</v>
+        <v>16450000</v>
       </c>
       <c r="AN56" t="n">
-        <v>81.45454545454545</v>
+        <v>81.2</v>
       </c>
       <c r="AO56" t="n">
         <v>25.44</v>
@@ -12633,22 +12697,22 @@
         <v>77.88</v>
       </c>
       <c r="AU56" t="n">
-        <v>26.51851851851852</v>
+        <v>26.65384615384615</v>
       </c>
       <c r="AV56" t="n">
-        <v>186.7777777777778</v>
+        <v>186.9230769230769</v>
       </c>
       <c r="AW56" t="n">
-        <v>1.666666666666667</v>
+        <v>1.692307692307692</v>
       </c>
       <c r="AX56" t="n">
-        <v>76</v>
+        <v>75.88461538461539</v>
       </c>
       <c r="AY56" t="n">
-        <v>14305000</v>
+        <v>13835961.53846154</v>
       </c>
       <c r="AZ56" t="n">
-        <v>79.11111111111111</v>
+        <v>78.92307692307692</v>
       </c>
       <c r="BA56" t="n">
         <v>27</v>
@@ -12799,22 +12863,22 @@
         </is>
       </c>
       <c r="AC57" t="n">
-        <v>25.5</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="AD57" t="n">
-        <v>186.5</v>
+        <v>185.7777777777778</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.5</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="AF57" t="n">
-        <v>71</v>
+        <v>71.77777777777777</v>
       </c>
       <c r="AG57" t="n">
-        <v>2715625</v>
+        <v>2947222.222222222</v>
       </c>
       <c r="AH57" t="n">
-        <v>77.5</v>
+        <v>77.55555555555556</v>
       </c>
       <c r="AI57" t="n">
         <v>25.7</v>
@@ -12835,40 +12899,40 @@
         <v>79.3</v>
       </c>
       <c r="AO57" t="n">
-        <v>24.125</v>
+        <v>24.6</v>
       </c>
       <c r="AP57" t="n">
-        <v>185.5</v>
+        <v>185.28</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.041666666666667</v>
+        <v>1.12</v>
       </c>
       <c r="AR57" t="n">
-        <v>69.625</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="AS57" t="n">
-        <v>3267708.333333333</v>
+        <v>3329000</v>
       </c>
       <c r="AT57" t="n">
-        <v>75.75</v>
+        <v>75.84</v>
       </c>
       <c r="AU57" t="n">
-        <v>25.72222222222222</v>
+        <v>25.73913043478261</v>
       </c>
       <c r="AV57" t="n">
-        <v>184.6666666666667</v>
+        <v>183.7391304347826</v>
       </c>
       <c r="AW57" t="n">
-        <v>1.5</v>
+        <v>1.521739130434783</v>
       </c>
       <c r="AX57" t="n">
-        <v>74.38888888888889</v>
+        <v>75.08695652173913</v>
       </c>
       <c r="AY57" t="n">
-        <v>9861111.111111112</v>
+        <v>11086956.52173913</v>
       </c>
       <c r="AZ57" t="n">
-        <v>78.77777777777777</v>
+        <v>78.8695652173913</v>
       </c>
       <c r="BA57" t="n">
         <v>27.83333333333333</v>
@@ -13019,22 +13083,22 @@
         </is>
       </c>
       <c r="AC58" t="n">
-        <v>26.54545454545455</v>
+        <v>26.2</v>
       </c>
       <c r="AD58" t="n">
-        <v>185.3636363636364</v>
+        <v>185.7</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.363636363636364</v>
+        <v>1.3</v>
       </c>
       <c r="AF58" t="n">
-        <v>76.54545454545455</v>
+        <v>76.5</v>
       </c>
       <c r="AG58" t="n">
-        <v>12963636.36363636</v>
+        <v>13410000</v>
       </c>
       <c r="AH58" t="n">
-        <v>79</v>
+        <v>79.2</v>
       </c>
       <c r="AI58" t="n">
         <v>24.09090909090909</v>
@@ -13055,40 +13119,40 @@
         <v>76.90909090909091</v>
       </c>
       <c r="AO58" t="n">
-        <v>24.5</v>
+        <v>24.94117647058824</v>
       </c>
       <c r="AP58" t="n">
-        <v>185.1428571428571</v>
+        <v>184.2352941176471</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.214285714285714</v>
+        <v>1.176470588235294</v>
       </c>
       <c r="AR58" t="n">
-        <v>71.07142857142857</v>
+        <v>72.29411764705883</v>
       </c>
       <c r="AS58" t="n">
-        <v>4407142.857142857</v>
+        <v>6276470.588235294</v>
       </c>
       <c r="AT58" t="n">
-        <v>76.07142857142857</v>
+        <v>76.41176470588235</v>
       </c>
       <c r="AU58" t="n">
-        <v>23.11538461538462</v>
+        <v>22.73913043478261</v>
       </c>
       <c r="AV58" t="n">
-        <v>183.7692307692308</v>
+        <v>185.1739130434783</v>
       </c>
       <c r="AW58" t="n">
         <v>1</v>
       </c>
       <c r="AX58" t="n">
-        <v>67.30769230769231</v>
+        <v>67.34782608695652</v>
       </c>
       <c r="AY58" t="n">
-        <v>2629807.692307692</v>
+        <v>2816304.347826087</v>
       </c>
       <c r="AZ58" t="n">
-        <v>74.26923076923077</v>
+        <v>75.08695652173913</v>
       </c>
       <c r="BA58" t="n">
         <v>23</v>
@@ -13233,24 +13297,28 @@
           <t>0M9xNN8N</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr"/>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
       <c r="AC59" t="n">
-        <v>26.72727272727273</v>
+        <v>26.9</v>
       </c>
       <c r="AD59" t="n">
-        <v>184.2727272727273</v>
+        <v>185.4</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.272727272727273</v>
+        <v>1.3</v>
       </c>
       <c r="AF59" t="n">
-        <v>74.18181818181819</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AG59" t="n">
-        <v>5781818.181818182</v>
+        <v>5610000</v>
       </c>
       <c r="AH59" t="n">
-        <v>76.63636363636364</v>
+        <v>76.5</v>
       </c>
       <c r="AI59" t="n">
         <v>24</v>
@@ -13509,22 +13577,22 @@
         <v>75.22222222222223</v>
       </c>
       <c r="AU60" t="n">
-        <v>25</v>
+        <v>25.41176470588235</v>
       </c>
       <c r="AV60" t="n">
-        <v>184.75</v>
+        <v>185.1176470588235</v>
       </c>
       <c r="AW60" t="n">
-        <v>1.0625</v>
+        <v>1.058823529411765</v>
       </c>
       <c r="AX60" t="n">
-        <v>69.9375</v>
+        <v>70.41176470588235</v>
       </c>
       <c r="AY60" t="n">
-        <v>2481250</v>
+        <v>2747058.823529412</v>
       </c>
       <c r="AZ60" t="n">
-        <v>74.0625</v>
+        <v>74.29411764705883</v>
       </c>
       <c r="BA60" t="n">
         <v>27.5</v>
@@ -13693,22 +13761,22 @@
         <v>76.18181818181819</v>
       </c>
       <c r="AI61" t="n">
-        <v>26.45454545454545</v>
+        <v>25.9</v>
       </c>
       <c r="AJ61" t="n">
-        <v>182.1818181818182</v>
+        <v>181.9</v>
       </c>
       <c r="AK61" t="n">
-        <v>1.909090909090909</v>
+        <v>1.9</v>
       </c>
       <c r="AL61" t="n">
-        <v>80.72727272727273</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="AM61" t="n">
-        <v>38200000</v>
+        <v>41750000</v>
       </c>
       <c r="AN61" t="n">
-        <v>83.09090909090909</v>
+        <v>84</v>
       </c>
       <c r="AO61" t="n">
         <v>24.81481481481481</v>
@@ -13913,22 +13981,22 @@
         <v>76.63636363636364</v>
       </c>
       <c r="AI62" t="n">
-        <v>25.1</v>
+        <v>25.11111111111111</v>
       </c>
       <c r="AJ62" t="n">
-        <v>185.4</v>
+        <v>186.5555555555555</v>
       </c>
       <c r="AK62" t="n">
-        <v>1.8</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="AL62" t="n">
-        <v>80.7</v>
+        <v>80.33333333333333</v>
       </c>
       <c r="AM62" t="n">
-        <v>32700000</v>
+        <v>30722222.22222222</v>
       </c>
       <c r="AN62" t="n">
-        <v>84.59999999999999</v>
+        <v>84.55555555555556</v>
       </c>
       <c r="AO62" t="n">
         <v>25.62068965517241</v>
@@ -13949,22 +14017,22 @@
         <v>74.51724137931035</v>
       </c>
       <c r="AU62" t="n">
-        <v>25.31578947368421</v>
+        <v>25.65</v>
       </c>
       <c r="AV62" t="n">
-        <v>183.9473684210526</v>
+        <v>183.75</v>
       </c>
       <c r="AW62" t="n">
-        <v>1.842105263157895</v>
+        <v>1.9</v>
       </c>
       <c r="AX62" t="n">
-        <v>76.47368421052632</v>
+        <v>76.5</v>
       </c>
       <c r="AY62" t="n">
-        <v>14955263.15789474</v>
+        <v>14557500</v>
       </c>
       <c r="AZ62" t="n">
-        <v>80.94736842105263</v>
+        <v>80.75</v>
       </c>
       <c r="BA62" t="n">
         <v>32</v>
@@ -14104,7 +14172,11 @@
       <c r="Z63" t="n">
         <v>20232024</v>
       </c>
-      <c r="AA63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
       <c r="AB63" t="inlineStr">
         <is>
           <t>zVqqL0ma</t>
@@ -14129,22 +14201,22 @@
         <v>78.59999999999999</v>
       </c>
       <c r="AI63" t="n">
-        <v>27.09090909090909</v>
+        <v>26.8</v>
       </c>
       <c r="AJ63" t="n">
-        <v>183.1818181818182</v>
+        <v>184</v>
       </c>
       <c r="AK63" t="n">
-        <v>1.818181818181818</v>
+        <v>1.7</v>
       </c>
       <c r="AL63" t="n">
-        <v>76.90909090909091</v>
+        <v>76.5</v>
       </c>
       <c r="AM63" t="n">
-        <v>16900000</v>
+        <v>16090000</v>
       </c>
       <c r="AN63" t="n">
-        <v>79.09090909090909</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="AO63" t="n">
         <v>27.33333333333333</v>
@@ -14165,22 +14237,22 @@
         <v>72.42857142857143</v>
       </c>
       <c r="AU63" t="n">
-        <v>26.23809523809524</v>
+        <v>26.05</v>
       </c>
       <c r="AV63" t="n">
-        <v>181.4761904761905</v>
+        <v>181.8</v>
       </c>
       <c r="AW63" t="n">
-        <v>1.714285714285714</v>
+        <v>1.65</v>
       </c>
       <c r="AX63" t="n">
-        <v>76.80952380952381</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="AY63" t="n">
-        <v>16793333.33333333</v>
+        <v>16383000</v>
       </c>
       <c r="AZ63" t="n">
-        <v>79.57142857142857</v>
+        <v>79.5</v>
       </c>
       <c r="BA63" t="n">
         <v>26.4</v>
@@ -14331,22 +14403,22 @@
         </is>
       </c>
       <c r="AC64" t="n">
-        <v>24.90909090909091</v>
+        <v>25.1</v>
       </c>
       <c r="AD64" t="n">
-        <v>188.7272727272727</v>
+        <v>189.3</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.363636363636364</v>
+        <v>1.4</v>
       </c>
       <c r="AF64" t="n">
-        <v>78.18181818181819</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="AG64" t="n">
-        <v>20045454.54545455</v>
+        <v>19400000</v>
       </c>
       <c r="AH64" t="n">
-        <v>82.27272727272727</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="AI64" t="n">
         <v>25.54545454545455</v>
@@ -14545,7 +14617,11 @@
           <t>C06aJvIB</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr"/>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
       <c r="AC65" t="n">
         <v>26.09090909090909</v>
       </c>
@@ -14583,22 +14659,22 @@
         <v>76.8</v>
       </c>
       <c r="AO65" t="n">
-        <v>25.39130434782609</v>
+        <v>25.46428571428572</v>
       </c>
       <c r="AP65" t="n">
-        <v>183.695652173913</v>
+        <v>183.1071428571429</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.652173913043478</v>
+        <v>1.642857142857143</v>
       </c>
       <c r="AR65" t="n">
-        <v>75.43478260869566</v>
+        <v>75.82142857142857</v>
       </c>
       <c r="AS65" t="n">
-        <v>13600000</v>
+        <v>13939285.71428571</v>
       </c>
       <c r="AT65" t="n">
-        <v>79.52173913043478</v>
+        <v>79.46428571428571</v>
       </c>
       <c r="AU65" t="n">
         <v>27.12</v>
@@ -14767,22 +14843,22 @@
         </is>
       </c>
       <c r="AC66" t="n">
-        <v>29.18181818181818</v>
+        <v>28.7</v>
       </c>
       <c r="AD66" t="n">
-        <v>182.3636363636364</v>
+        <v>183.7</v>
       </c>
       <c r="AE66" t="n">
-        <v>2.545454545454545</v>
+        <v>2.4</v>
       </c>
       <c r="AF66" t="n">
-        <v>82.63636363636364</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="AG66" t="n">
-        <v>33681818.18181818</v>
+        <v>36000000</v>
       </c>
       <c r="AH66" t="n">
-        <v>84.45454545454545</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="AI66" t="n">
         <v>24.72727272727273</v>
@@ -14803,22 +14879,22 @@
         <v>75.81818181818181</v>
       </c>
       <c r="AO66" t="n">
-        <v>27.59259259259259</v>
+        <v>27.34615384615385</v>
       </c>
       <c r="AP66" t="n">
-        <v>183.037037037037</v>
+        <v>183.5769230769231</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.925925925925926</v>
+        <v>1.846153846153846</v>
       </c>
       <c r="AR66" t="n">
-        <v>78.81481481481481</v>
+        <v>78.76923076923077</v>
       </c>
       <c r="AS66" t="n">
-        <v>19629629.62962963</v>
+        <v>19980769.23076923</v>
       </c>
       <c r="AT66" t="n">
-        <v>80.88888888888889</v>
+        <v>80.92307692307692</v>
       </c>
       <c r="AU66" t="n">
         <v>26.38461538461538</v>
@@ -15005,40 +15081,40 @@
         <v>77.27272727272727</v>
       </c>
       <c r="AI67" t="n">
-        <v>25.90909090909091</v>
+        <v>25.3</v>
       </c>
       <c r="AJ67" t="n">
-        <v>184.4545454545455</v>
+        <v>185.6</v>
       </c>
       <c r="AK67" t="n">
-        <v>1.727272727272727</v>
+        <v>1.6</v>
       </c>
       <c r="AL67" t="n">
-        <v>79.09090909090909</v>
+        <v>79.5</v>
       </c>
       <c r="AM67" t="n">
-        <v>26400000</v>
+        <v>28650000</v>
       </c>
       <c r="AN67" t="n">
-        <v>82.09090909090909</v>
+        <v>82.8</v>
       </c>
       <c r="AO67" t="n">
-        <v>24.92857142857143</v>
+        <v>24.92</v>
       </c>
       <c r="AP67" t="n">
-        <v>182.9285714285714</v>
+        <v>184.12</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.142857142857143</v>
+        <v>1.16</v>
       </c>
       <c r="AR67" t="n">
-        <v>71.53571428571429</v>
+        <v>71.12</v>
       </c>
       <c r="AS67" t="n">
-        <v>4435714.285714285</v>
+        <v>4068000</v>
       </c>
       <c r="AT67" t="n">
-        <v>76.71428571428571</v>
+        <v>76.56</v>
       </c>
       <c r="AU67" t="n">
         <v>25</v>
@@ -15261,43 +15337,43 @@
         <v>78.52631578947368</v>
       </c>
       <c r="AU68" t="n">
-        <v>23.32</v>
+        <v>22.95454545454545</v>
       </c>
       <c r="AV68" t="n">
-        <v>183.6</v>
+        <v>185.0454545454545</v>
       </c>
       <c r="AW68" t="n">
         <v>1</v>
       </c>
       <c r="AX68" t="n">
-        <v>66.95999999999999</v>
+        <v>66.95454545454545</v>
       </c>
       <c r="AY68" t="n">
-        <v>2415000</v>
+        <v>2580681.818181818</v>
       </c>
       <c r="AZ68" t="n">
-        <v>73.40000000000001</v>
+        <v>74.13636363636364</v>
       </c>
       <c r="BA68" t="n">
-        <v>26.66666666666667</v>
+        <v>24</v>
       </c>
       <c r="BB68" t="n">
-        <v>182.6666666666667</v>
+        <v>181.5</v>
       </c>
       <c r="BC68" t="n">
-        <v>1.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="BD68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BE68" t="n">
-        <v>225</v>
+        <v>151</v>
       </c>
       <c r="BF68" t="n">
-        <v>20700000</v>
+        <v>18000000</v>
       </c>
       <c r="BG68" t="n">
-        <v>232</v>
+        <v>158</v>
       </c>
       <c r="BH68" t="n">
         <v>22.5</v>
@@ -15421,7 +15497,11 @@
           <t>Q3A3IbXH</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr"/>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
       <c r="AC69" t="n">
         <v>24.81818181818182</v>
       </c>
@@ -15441,22 +15521,22 @@
         <v>79.90909090909091</v>
       </c>
       <c r="AI69" t="n">
-        <v>24.88888888888889</v>
+        <v>25.3</v>
       </c>
       <c r="AJ69" t="n">
-        <v>182.5555555555555</v>
+        <v>183.6</v>
       </c>
       <c r="AK69" t="n">
-        <v>1.222222222222222</v>
+        <v>1.3</v>
       </c>
       <c r="AL69" t="n">
-        <v>73.33333333333333</v>
+        <v>73.5</v>
       </c>
       <c r="AM69" t="n">
-        <v>8411111.111111112</v>
+        <v>8040000</v>
       </c>
       <c r="AN69" t="n">
-        <v>78.22222222222223</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AO69" t="n">
         <v>22.93333333333333</v>
@@ -15643,76 +15723,76 @@
         </is>
       </c>
       <c r="AC70" t="n">
-        <v>26.6</v>
+        <v>26.3</v>
       </c>
       <c r="AD70" t="n">
-        <v>185.3</v>
+        <v>185.1</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AF70" t="n">
-        <v>76.8</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="AG70" t="n">
-        <v>13610000</v>
+        <v>14260000</v>
       </c>
       <c r="AH70" t="n">
-        <v>79.2</v>
+        <v>79.3</v>
       </c>
       <c r="AI70" t="n">
-        <v>26.2</v>
+        <v>26.33333333333333</v>
       </c>
       <c r="AJ70" t="n">
-        <v>186</v>
+        <v>187.2222222222222</v>
       </c>
       <c r="AK70" t="n">
-        <v>2</v>
+        <v>1.888888888888889</v>
       </c>
       <c r="AL70" t="n">
-        <v>82.09999999999999</v>
+        <v>81.88888888888889</v>
       </c>
       <c r="AM70" t="n">
-        <v>36700000</v>
+        <v>35166666.66666666</v>
       </c>
       <c r="AN70" t="n">
-        <v>84.59999999999999</v>
+        <v>84.55555555555556</v>
       </c>
       <c r="AO70" t="n">
-        <v>24.94444444444444</v>
+        <v>25.05263157894737</v>
       </c>
       <c r="AP70" t="n">
-        <v>185.6666666666667</v>
+        <v>185.3684210526316</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.166666666666667</v>
+        <v>1.157894736842105</v>
       </c>
       <c r="AR70" t="n">
-        <v>72.05555555555556</v>
+        <v>72.36842105263158</v>
       </c>
       <c r="AS70" t="n">
-        <v>4911111.111111111</v>
+        <v>5442105.263157895</v>
       </c>
       <c r="AT70" t="n">
-        <v>75.94444444444444</v>
+        <v>76.05263157894737</v>
       </c>
       <c r="AU70" t="n">
-        <v>23.71428571428572</v>
+        <v>24.73913043478261</v>
       </c>
       <c r="AV70" t="n">
-        <v>183.2380952380952</v>
+        <v>183.1739130434783</v>
       </c>
       <c r="AW70" t="n">
-        <v>1.571428571428571</v>
+        <v>1.695652173913043</v>
       </c>
       <c r="AX70" t="n">
-        <v>75.95238095238095</v>
+        <v>75.73913043478261</v>
       </c>
       <c r="AY70" t="n">
-        <v>16102380.95238095</v>
+        <v>13419565.2173913</v>
       </c>
       <c r="AZ70" t="n">
-        <v>82.47619047619048</v>
+        <v>81.65217391304348</v>
       </c>
       <c r="BA70" t="n">
         <v>23.5</v>
@@ -15852,7 +15932,11 @@
       <c r="Z71" t="n">
         <v>20232024</v>
       </c>
-      <c r="AA71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
       <c r="AB71" t="inlineStr">
         <is>
           <t>Q3A3IbXH</t>
@@ -16079,76 +16163,76 @@
         </is>
       </c>
       <c r="AC72" t="n">
-        <v>27.09090909090909</v>
+        <v>26.8</v>
       </c>
       <c r="AD72" t="n">
-        <v>183.1818181818182</v>
+        <v>184</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.818181818181818</v>
+        <v>1.7</v>
       </c>
       <c r="AF72" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>16090000</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>26.63636363636364</v>
+      </c>
+      <c r="AJ72" t="n">
+        <v>185.3636363636364</v>
+      </c>
+      <c r="AK72" t="n">
+        <v>1.545454545454545</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>72.09090909090909</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>3222727.272727273</v>
+      </c>
+      <c r="AN72" t="n">
         <v>76.90909090909091</v>
       </c>
-      <c r="AG72" t="n">
-        <v>16900000</v>
-      </c>
-      <c r="AH72" t="n">
-        <v>79.09090909090909</v>
-      </c>
-      <c r="AI72" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="AJ72" t="n">
-        <v>185.9</v>
-      </c>
-      <c r="AK72" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AL72" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="AM72" t="n">
-        <v>3065000</v>
-      </c>
-      <c r="AN72" t="n">
-        <v>76.8</v>
-      </c>
       <c r="AO72" t="n">
-        <v>25.45</v>
+        <v>25.57894736842105</v>
       </c>
       <c r="AP72" t="n">
-        <v>181.55</v>
+        <v>181.6315789473684</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.55</v>
+        <v>1.578947368421053</v>
       </c>
       <c r="AR72" t="n">
-        <v>74.3</v>
+        <v>74.84210526315789</v>
       </c>
       <c r="AS72" t="n">
-        <v>12013000</v>
+        <v>12597894.73684211</v>
       </c>
       <c r="AT72" t="n">
-        <v>78.2</v>
+        <v>78.68421052631579</v>
       </c>
       <c r="AU72" t="n">
-        <v>25.57894736842105</v>
+        <v>26.1</v>
       </c>
       <c r="AV72" t="n">
-        <v>184.7894736842105</v>
+        <v>184.55</v>
       </c>
       <c r="AW72" t="n">
-        <v>1.368421052631579</v>
+        <v>1.45</v>
       </c>
       <c r="AX72" t="n">
-        <v>70.84210526315789</v>
+        <v>71.2</v>
       </c>
       <c r="AY72" t="n">
-        <v>3271052.631578947</v>
+        <v>3347500</v>
       </c>
       <c r="AZ72" t="n">
-        <v>75.78947368421052</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="BA72" t="n">
         <v>28.4</v>
@@ -16335,40 +16419,40 @@
         <v>84.54545454545455</v>
       </c>
       <c r="AO73" t="n">
-        <v>24.52</v>
+        <v>24.80769230769231</v>
       </c>
       <c r="AP73" t="n">
-        <v>181.44</v>
+        <v>181.8076923076923</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.04</v>
+        <v>1.038461538461539</v>
       </c>
       <c r="AR73" t="n">
-        <v>71.16</v>
+        <v>71.42307692307692</v>
       </c>
       <c r="AS73" t="n">
-        <v>3652000</v>
+        <v>3780769.230769231</v>
       </c>
       <c r="AT73" t="n">
-        <v>75.48</v>
+        <v>75.57692307692308</v>
       </c>
       <c r="AU73" t="n">
-        <v>28.42307692307692</v>
+        <v>27.69565217391304</v>
       </c>
       <c r="AV73" t="n">
-        <v>181.7692307692308</v>
+        <v>183.4347826086957</v>
       </c>
       <c r="AW73" t="n">
-        <v>2.038461538461538</v>
+        <v>1.782608695652174</v>
       </c>
       <c r="AX73" t="n">
-        <v>78.76923076923077</v>
+        <v>78.60869565217391</v>
       </c>
       <c r="AY73" t="n">
-        <v>18096153.84615385</v>
+        <v>19086956.52173913</v>
       </c>
       <c r="AZ73" t="n">
-        <v>80.84615384615384</v>
+        <v>80.95652173913044</v>
       </c>
       <c r="BA73" t="n">
         <v>25</v>
@@ -16519,76 +16603,76 @@
         </is>
       </c>
       <c r="AC74" t="n">
-        <v>26.2</v>
+        <v>26.33333333333333</v>
       </c>
       <c r="AD74" t="n">
-        <v>186</v>
+        <v>187.2222222222222</v>
       </c>
       <c r="AE74" t="n">
-        <v>2</v>
+        <v>1.888888888888889</v>
       </c>
       <c r="AF74" t="n">
-        <v>82.09999999999999</v>
+        <v>81.88888888888889</v>
       </c>
       <c r="AG74" t="n">
-        <v>36700000</v>
+        <v>35166666.66666666</v>
       </c>
       <c r="AH74" t="n">
-        <v>84.59999999999999</v>
+        <v>84.55555555555556</v>
       </c>
       <c r="AI74" t="n">
-        <v>27.1</v>
+        <v>26.90909090909091</v>
       </c>
       <c r="AJ74" t="n">
-        <v>185.3</v>
+        <v>185.2727272727273</v>
       </c>
       <c r="AK74" t="n">
-        <v>1.7</v>
+        <v>1.636363636363636</v>
       </c>
       <c r="AL74" t="n">
-        <v>76.8</v>
+        <v>76.81818181818181</v>
       </c>
       <c r="AM74" t="n">
-        <v>12880000</v>
+        <v>12981818.18181818</v>
       </c>
       <c r="AN74" t="n">
-        <v>79.59999999999999</v>
+        <v>79.63636363636364</v>
       </c>
       <c r="AO74" t="n">
-        <v>23.65</v>
+        <v>24</v>
       </c>
       <c r="AP74" t="n">
-        <v>182.9</v>
+        <v>183.15</v>
       </c>
       <c r="AQ74" t="n">
         <v>1.6</v>
       </c>
       <c r="AR74" t="n">
-        <v>75.84999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="AS74" t="n">
-        <v>16032500</v>
+        <v>13857500</v>
       </c>
       <c r="AT74" t="n">
-        <v>82.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="AU74" t="n">
-        <v>24.48</v>
+        <v>24.625</v>
       </c>
       <c r="AV74" t="n">
-        <v>179.48</v>
+        <v>181.0416666666667</v>
       </c>
       <c r="AW74" t="n">
-        <v>1.32</v>
+        <v>1.375</v>
       </c>
       <c r="AX74" t="n">
-        <v>75.08</v>
+        <v>75.04166666666667</v>
       </c>
       <c r="AY74" t="n">
-        <v>11640000</v>
+        <v>11645833.33333333</v>
       </c>
       <c r="AZ74" t="n">
-        <v>79.72</v>
+        <v>79.54166666666667</v>
       </c>
       <c r="BA74" t="n">
         <v>27</v>
@@ -16743,22 +16827,22 @@
         <v>76.36363636363636</v>
       </c>
       <c r="AI75" t="n">
-        <v>27.63636363636364</v>
+        <v>28.1</v>
       </c>
       <c r="AJ75" t="n">
-        <v>185.0909090909091</v>
+        <v>185.3</v>
       </c>
       <c r="AK75" t="n">
-        <v>1.818181818181818</v>
+        <v>1.9</v>
       </c>
       <c r="AL75" t="n">
-        <v>79.45454545454545</v>
+        <v>79.5</v>
       </c>
       <c r="AM75" t="n">
-        <v>21000000</v>
+        <v>20450000</v>
       </c>
       <c r="AN75" t="n">
-        <v>81.27272727272727</v>
+        <v>81</v>
       </c>
       <c r="AO75" t="n">
         <v>26.13793103448276</v>
@@ -16939,7 +17023,11 @@
           <t>69Dxbc61</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr"/>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
       <c r="AC76" t="n">
         <v>25.36363636363636</v>
       </c>
@@ -17150,47 +17238,51 @@
       <c r="Z77" t="n">
         <v>20232024</v>
       </c>
-      <c r="AA77" t="inlineStr"/>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
       <c r="AB77" t="inlineStr">
         <is>
           <t>C06aJvIB</t>
         </is>
       </c>
       <c r="AC77" t="n">
-        <v>27</v>
+        <v>27.2</v>
       </c>
       <c r="AD77" t="n">
-        <v>183.1111111111111</v>
+        <v>184.1</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.333333333333333</v>
+        <v>1.4</v>
       </c>
       <c r="AF77" t="n">
-        <v>74.66666666666667</v>
+        <v>74.7</v>
       </c>
       <c r="AG77" t="n">
-        <v>7522222.222222222</v>
+        <v>7240000</v>
       </c>
       <c r="AH77" t="n">
-        <v>76.88888888888889</v>
+        <v>76.7</v>
       </c>
       <c r="AI77" t="n">
-        <v>26.72727272727273</v>
+        <v>26.2</v>
       </c>
       <c r="AJ77" t="n">
-        <v>183.4545454545455</v>
+        <v>183.3</v>
       </c>
       <c r="AK77" t="n">
-        <v>1.818181818181818</v>
+        <v>1.8</v>
       </c>
       <c r="AL77" t="n">
-        <v>81</v>
+        <v>81.7</v>
       </c>
       <c r="AM77" t="n">
-        <v>37972727.27272727</v>
+        <v>41500000</v>
       </c>
       <c r="AN77" t="n">
-        <v>82.54545454545455</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="AO77" t="n">
         <v>23.80769230769231</v>
@@ -17449,25 +17541,25 @@
         <v>78.21428571428571</v>
       </c>
       <c r="BA78" t="n">
-        <v>23.4</v>
+        <v>22.75</v>
       </c>
       <c r="BB78" t="n">
-        <v>184.2</v>
+        <v>187</v>
       </c>
       <c r="BC78" t="n">
         <v>1</v>
       </c>
       <c r="BD78" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BE78" t="n">
-        <v>331</v>
+        <v>264</v>
       </c>
       <c r="BF78" t="n">
-        <v>7975000</v>
+        <v>6775000</v>
       </c>
       <c r="BG78" t="n">
-        <v>363</v>
+        <v>295</v>
       </c>
       <c r="BH78" t="n">
         <v>26.33333333333333</v>
@@ -17615,22 +17707,22 @@
         <v>75.72727272727273</v>
       </c>
       <c r="AI79" t="n">
-        <v>26.6</v>
+        <v>26.3</v>
       </c>
       <c r="AJ79" t="n">
-        <v>185.3</v>
+        <v>185.1</v>
       </c>
       <c r="AK79" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AL79" t="n">
-        <v>76.8</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="AM79" t="n">
-        <v>13610000</v>
+        <v>14260000</v>
       </c>
       <c r="AN79" t="n">
-        <v>79.2</v>
+        <v>79.3</v>
       </c>
       <c r="AO79" t="n">
         <v>24.18518518518519</v>
@@ -17651,22 +17743,22 @@
         <v>75.33333333333333</v>
       </c>
       <c r="AU79" t="n">
-        <v>25.15</v>
+        <v>24.89473684210526</v>
       </c>
       <c r="AV79" t="n">
-        <v>185.2</v>
+        <v>185.3684210526316</v>
       </c>
       <c r="AW79" t="n">
-        <v>1.25</v>
+        <v>1.210526315789474</v>
       </c>
       <c r="AX79" t="n">
-        <v>72.05</v>
+        <v>71.78947368421052</v>
       </c>
       <c r="AY79" t="n">
-        <v>4770000</v>
+        <v>4573684.210526315</v>
       </c>
       <c r="AZ79" t="n">
-        <v>76.15000000000001</v>
+        <v>76.10526315789474</v>
       </c>
       <c r="BA79" t="n">
         <v>29</v>
@@ -17817,40 +17909,40 @@
         </is>
       </c>
       <c r="AC80" t="n">
-        <v>27.7</v>
+        <v>27.63636363636364</v>
       </c>
       <c r="AD80" t="n">
-        <v>182.4</v>
+        <v>183.0909090909091</v>
       </c>
       <c r="AE80" t="n">
-        <v>2.5</v>
+        <v>2.454545454545455</v>
       </c>
       <c r="AF80" t="n">
-        <v>79.5</v>
+        <v>79.81818181818181</v>
       </c>
       <c r="AG80" t="n">
-        <v>24030000</v>
+        <v>25163636.36363636</v>
       </c>
       <c r="AH80" t="n">
-        <v>80</v>
+        <v>80.36363636363636</v>
       </c>
       <c r="AI80" t="n">
-        <v>26.54545454545455</v>
+        <v>26.2</v>
       </c>
       <c r="AJ80" t="n">
-        <v>184.4545454545455</v>
+        <v>185.4</v>
       </c>
       <c r="AK80" t="n">
-        <v>1.909090909090909</v>
+        <v>1.8</v>
       </c>
       <c r="AL80" t="n">
-        <v>77.09090909090909</v>
+        <v>76.7</v>
       </c>
       <c r="AM80" t="n">
-        <v>17400000</v>
+        <v>16640000</v>
       </c>
       <c r="AN80" t="n">
-        <v>80</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="AO80" t="n">
         <v>25.76923076923077</v>
@@ -18031,7 +18123,11 @@
           <t>Iw7eKK25</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr"/>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
       <c r="AC81" t="n">
         <v>25.45454545454545</v>
       </c>
@@ -18069,22 +18165,22 @@
         <v>77.63636363636364</v>
       </c>
       <c r="AO81" t="n">
-        <v>24.51851851851852</v>
+        <v>24.23076923076923</v>
       </c>
       <c r="AP81" t="n">
-        <v>183.1111111111111</v>
+        <v>183.5</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.666666666666667</v>
+        <v>1.615384615384615</v>
       </c>
       <c r="AR81" t="n">
-        <v>75.74074074074075</v>
+        <v>75.76923076923077</v>
       </c>
       <c r="AS81" t="n">
-        <v>17680555.55555556</v>
+        <v>18210576.92307692</v>
       </c>
       <c r="AT81" t="n">
-        <v>81.92592592592592</v>
+        <v>82.19230769230769</v>
       </c>
       <c r="AU81" t="n">
         <v>22.61538461538462</v>
@@ -18253,22 +18349,22 @@
         </is>
       </c>
       <c r="AC82" t="n">
-        <v>23.88888888888889</v>
+        <v>25.1</v>
       </c>
       <c r="AD82" t="n">
-        <v>184.2222222222222</v>
+        <v>183.8</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.111111111111111</v>
+        <v>1.3</v>
       </c>
       <c r="AF82" t="n">
-        <v>70.33333333333333</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="AG82" t="n">
-        <v>2961111.111111111</v>
+        <v>3145000</v>
       </c>
       <c r="AH82" t="n">
-        <v>76.88888888888889</v>
+        <v>77</v>
       </c>
       <c r="AI82" t="n">
         <v>26.63636363636364</v>
@@ -18307,22 +18403,22 @@
         <v>75.15384615384616</v>
       </c>
       <c r="AU82" t="n">
-        <v>24.61538461538462</v>
+        <v>24.56521739130435</v>
       </c>
       <c r="AV82" t="n">
-        <v>185.2307692307692</v>
+        <v>186.8260869565217</v>
       </c>
       <c r="AW82" t="n">
-        <v>1.115384615384615</v>
+        <v>1.130434782608696</v>
       </c>
       <c r="AX82" t="n">
-        <v>71.73076923076923</v>
+        <v>71.30434782608695</v>
       </c>
       <c r="AY82" t="n">
-        <v>4234615.384615385</v>
+        <v>3808695.652173913</v>
       </c>
       <c r="AZ82" t="n">
-        <v>77.23076923076923</v>
+        <v>77.1304347826087</v>
       </c>
       <c r="BA82" t="n">
         <v>28.25</v>
@@ -18509,22 +18605,22 @@
         <v>76.09090909090909</v>
       </c>
       <c r="AO83" t="n">
-        <v>26.53846153846154</v>
+        <v>25.56521739130435</v>
       </c>
       <c r="AP83" t="n">
-        <v>180.1538461538462</v>
+        <v>181.6086956521739</v>
       </c>
       <c r="AQ83" t="n">
-        <v>2</v>
+        <v>1.739130434782609</v>
       </c>
       <c r="AR83" t="n">
-        <v>79.5</v>
+        <v>79.43478260869566</v>
       </c>
       <c r="AS83" t="n">
-        <v>26226923.07692308</v>
+        <v>28278260.86956522</v>
       </c>
       <c r="AT83" t="n">
-        <v>82.34615384615384</v>
+        <v>82.65217391304348</v>
       </c>
       <c r="AU83" t="n">
         <v>24.68181818181818</v>
@@ -18682,7 +18778,11 @@
       <c r="Z84" t="n">
         <v>20232024</v>
       </c>
-      <c r="AA84" t="inlineStr"/>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
       <c r="AB84" t="inlineStr">
         <is>
           <t>URcSl02h</t>
@@ -18707,22 +18807,22 @@
         <v>78.18181818181819</v>
       </c>
       <c r="AI84" t="n">
-        <v>25.11111111111111</v>
+        <v>25.3</v>
       </c>
       <c r="AJ84" t="n">
-        <v>180.1111111111111</v>
+        <v>181.1</v>
       </c>
       <c r="AK84" t="n">
         <v>2</v>
       </c>
       <c r="AL84" t="n">
-        <v>77.33333333333333</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AM84" t="n">
-        <v>16811111.11111111</v>
+        <v>18780000</v>
       </c>
       <c r="AN84" t="n">
-        <v>80.77777777777777</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="AO84" t="n">
         <v>24.26086956521739</v>
@@ -19129,22 +19229,22 @@
         </is>
       </c>
       <c r="AC86" t="n">
-        <v>26.72727272727273</v>
+        <v>26.9</v>
       </c>
       <c r="AD86" t="n">
-        <v>185</v>
+        <v>186.2</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.272727272727273</v>
+        <v>1.3</v>
       </c>
       <c r="AF86" t="n">
-        <v>74.09090909090909</v>
+        <v>74</v>
       </c>
       <c r="AG86" t="n">
-        <v>5672727.272727272</v>
+        <v>5490000</v>
       </c>
       <c r="AH86" t="n">
-        <v>76.54545454545455</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="AI86" t="n">
         <v>25.36363636363636</v>
@@ -19165,40 +19265,40 @@
         <v>77.36363636363636</v>
       </c>
       <c r="AO86" t="n">
-        <v>24.79166666666667</v>
+        <v>24.78260869565218</v>
       </c>
       <c r="AP86" t="n">
-        <v>183.6666666666667</v>
+        <v>184.1304347826087</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.208333333333333</v>
+        <v>1.217391304347826</v>
       </c>
       <c r="AR86" t="n">
-        <v>71.83333333333333</v>
+        <v>71.69565217391305</v>
       </c>
       <c r="AS86" t="n">
-        <v>4891666.666666667</v>
+        <v>4778260.869565218</v>
       </c>
       <c r="AT86" t="n">
-        <v>77.45833333333333</v>
+        <v>77.43478260869566</v>
       </c>
       <c r="AU86" t="n">
-        <v>25.95</v>
+        <v>26.23809523809524</v>
       </c>
       <c r="AV86" t="n">
-        <v>184.55</v>
+        <v>184.8571428571429</v>
       </c>
       <c r="AW86" t="n">
-        <v>1.05</v>
+        <v>1.047619047619048</v>
       </c>
       <c r="AX86" t="n">
-        <v>71.25</v>
+        <v>71.57142857142857</v>
       </c>
       <c r="AY86" t="n">
-        <v>2985000</v>
+        <v>3176190.476190476</v>
       </c>
       <c r="AZ86" t="n">
-        <v>74.34999999999999</v>
+        <v>74.52380952380952</v>
       </c>
       <c r="BA86" t="n">
         <v>26.5</v>
@@ -19367,22 +19467,22 @@
         <v>79</v>
       </c>
       <c r="AI87" t="n">
-        <v>24.55555555555556</v>
+        <v>25.7</v>
       </c>
       <c r="AJ87" t="n">
-        <v>185.5555555555555</v>
+        <v>185</v>
       </c>
       <c r="AK87" t="n">
-        <v>1.111111111111111</v>
+        <v>1.3</v>
       </c>
       <c r="AL87" t="n">
-        <v>70.22222222222223</v>
+        <v>71</v>
       </c>
       <c r="AM87" t="n">
-        <v>2900000</v>
+        <v>3090000</v>
       </c>
       <c r="AN87" t="n">
-        <v>76.22222222222223</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="AO87" t="n">
         <v>23.41379310344828</v>
@@ -19569,10 +19669,10 @@
         </is>
       </c>
       <c r="AC88" t="n">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
       <c r="AD88" t="n">
-        <v>181.5</v>
+        <v>183.4</v>
       </c>
       <c r="AE88" t="n">
         <v>1.9</v>
@@ -19584,43 +19684,43 @@
         <v>12450000</v>
       </c>
       <c r="AH88" t="n">
-        <v>79.3</v>
+        <v>79.2</v>
       </c>
       <c r="AI88" t="n">
-        <v>26.45454545454545</v>
+        <v>25.9</v>
       </c>
       <c r="AJ88" t="n">
-        <v>184</v>
+        <v>185.1</v>
       </c>
       <c r="AK88" t="n">
-        <v>1.909090909090909</v>
+        <v>1.8</v>
       </c>
       <c r="AL88" t="n">
-        <v>81.45454545454545</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="AM88" t="n">
-        <v>37854545.45454545</v>
+        <v>41250000</v>
       </c>
       <c r="AN88" t="n">
-        <v>84.18181818181819</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="AO88" t="n">
-        <v>23.80769230769231</v>
+        <v>23.92592592592593</v>
       </c>
       <c r="AP88" t="n">
-        <v>182</v>
+        <v>182.2962962962963</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.269230769230769</v>
+        <v>1.296296296296296</v>
       </c>
       <c r="AR88" t="n">
-        <v>74.19230769230769</v>
+        <v>74.33333333333333</v>
       </c>
       <c r="AS88" t="n">
-        <v>12676923.07692308</v>
+        <v>12818518.51851852</v>
       </c>
       <c r="AT88" t="n">
-        <v>79.92307692307692</v>
+        <v>79.85185185185185</v>
       </c>
       <c r="AU88" t="n">
         <v>22.92592592592593</v>
@@ -19789,40 +19889,40 @@
         </is>
       </c>
       <c r="AC89" t="n">
-        <v>26.2</v>
+        <v>25.77777777777778</v>
       </c>
       <c r="AD89" t="n">
-        <v>182.9</v>
+        <v>183.7777777777778</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.8</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="AF89" t="n">
-        <v>77.2</v>
+        <v>76.77777777777777</v>
       </c>
       <c r="AG89" t="n">
-        <v>18690000</v>
+        <v>17988888.88888889</v>
       </c>
       <c r="AH89" t="n">
-        <v>79.59999999999999</v>
+        <v>79.44444444444444</v>
       </c>
       <c r="AI89" t="n">
-        <v>26</v>
+        <v>26.11111111111111</v>
       </c>
       <c r="AJ89" t="n">
-        <v>185.5</v>
+        <v>186.6666666666667</v>
       </c>
       <c r="AK89" t="n">
-        <v>1.9</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="AL89" t="n">
-        <v>80.2</v>
+        <v>79.77777777777777</v>
       </c>
       <c r="AM89" t="n">
-        <v>28350000</v>
+        <v>25888888.88888889</v>
       </c>
       <c r="AN89" t="n">
-        <v>83.7</v>
+        <v>83.55555555555556</v>
       </c>
       <c r="AO89" t="n">
         <v>27.56521739130435</v>
@@ -19843,22 +19943,22 @@
         <v>80.26086956521739</v>
       </c>
       <c r="AU89" t="n">
-        <v>23.18181818181818</v>
+        <v>23.09523809523809</v>
       </c>
       <c r="AV89" t="n">
-        <v>183.1818181818182</v>
+        <v>183.5714285714286</v>
       </c>
       <c r="AW89" t="n">
-        <v>1.5</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="AX89" t="n">
-        <v>73.45454545454545</v>
+        <v>72.95238095238095</v>
       </c>
       <c r="AY89" t="n">
-        <v>11115909.09090909</v>
+        <v>9240476.19047619</v>
       </c>
       <c r="AZ89" t="n">
-        <v>80</v>
+        <v>79.76190476190476</v>
       </c>
       <c r="BA89" t="n">
         <v>25.75</v>
@@ -19882,25 +19982,25 @@
         <v>324</v>
       </c>
       <c r="BH89" t="n">
-        <v>25.66666666666667</v>
+        <v>26.57142857142857</v>
       </c>
       <c r="BI89" t="n">
-        <v>184.1666666666667</v>
+        <v>183.5714285714286</v>
       </c>
       <c r="BJ89" t="n">
-        <v>2.333333333333333</v>
+        <v>2.428571428571428</v>
       </c>
       <c r="BK89" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BL89" t="n">
-        <v>480</v>
+        <v>557</v>
       </c>
       <c r="BM89" t="n">
-        <v>180500000</v>
+        <v>187500000</v>
       </c>
       <c r="BN89" t="n">
-        <v>504</v>
+        <v>581</v>
       </c>
     </row>
     <row r="90">
@@ -19998,7 +20098,11 @@
       <c r="Z90" t="n">
         <v>20232024</v>
       </c>
-      <c r="AA90" t="inlineStr"/>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
       <c r="AB90" t="inlineStr">
         <is>
           <t>0M9xNN8N</t>
@@ -20219,60 +20323,64 @@
           <t>C06aJvIB</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr"/>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
       <c r="AC91" t="n">
-        <v>26.36363636363636</v>
+        <v>26</v>
       </c>
       <c r="AD91" t="n">
-        <v>184.4545454545455</v>
+        <v>184.7</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.454545454545455</v>
+        <v>1.4</v>
       </c>
       <c r="AF91" t="n">
-        <v>76.54545454545455</v>
+        <v>76.5</v>
       </c>
       <c r="AG91" t="n">
-        <v>12863636.36363636</v>
+        <v>13300000</v>
       </c>
       <c r="AH91" t="n">
-        <v>79</v>
+        <v>79.2</v>
       </c>
       <c r="AI91" t="n">
-        <v>25.66666666666667</v>
+        <v>26</v>
       </c>
       <c r="AJ91" t="n">
-        <v>184.3333333333333</v>
+        <v>185.2</v>
       </c>
       <c r="AK91" t="n">
-        <v>1.333333333333333</v>
+        <v>1.4</v>
       </c>
       <c r="AL91" t="n">
-        <v>74.55555555555556</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="AM91" t="n">
-        <v>8944444.444444444</v>
+        <v>8520000</v>
       </c>
       <c r="AN91" t="n">
-        <v>78.55555555555556</v>
+        <v>78.2</v>
       </c>
       <c r="AO91" t="n">
-        <v>24.93333333333333</v>
+        <v>25</v>
       </c>
       <c r="AP91" t="n">
-        <v>187.6</v>
+        <v>186.5882352941177</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.066666666666667</v>
+        <v>1</v>
       </c>
       <c r="AR91" t="n">
-        <v>71.26666666666667</v>
+        <v>72.11764705882354</v>
       </c>
       <c r="AS91" t="n">
-        <v>3960000</v>
+        <v>5641176.470588235</v>
       </c>
       <c r="AT91" t="n">
-        <v>76.26666666666667</v>
+        <v>76.52941176470588</v>
       </c>
       <c r="AU91" t="n">
         <v>24.96153846153846</v>
@@ -20441,40 +20549,40 @@
         </is>
       </c>
       <c r="AC92" t="n">
-        <v>27.45454545454545</v>
+        <v>27</v>
       </c>
       <c r="AD92" t="n">
-        <v>180.1818181818182</v>
+        <v>179.7</v>
       </c>
       <c r="AE92" t="n">
-        <v>1.818181818181818</v>
+        <v>1.8</v>
       </c>
       <c r="AF92" t="n">
-        <v>80.63636363636364</v>
+        <v>81.3</v>
       </c>
       <c r="AG92" t="n">
-        <v>30109090.90909091</v>
+        <v>32850000</v>
       </c>
       <c r="AH92" t="n">
-        <v>81.72727272727273</v>
+        <v>82.5</v>
       </c>
       <c r="AI92" t="n">
-        <v>26.36363636363636</v>
+        <v>26.7</v>
       </c>
       <c r="AJ92" t="n">
-        <v>187.1818181818182</v>
+        <v>187.6</v>
       </c>
       <c r="AK92" t="n">
-        <v>1.727272727272727</v>
+        <v>1.8</v>
       </c>
       <c r="AL92" t="n">
-        <v>78.72727272727273</v>
+        <v>78.7</v>
       </c>
       <c r="AM92" t="n">
-        <v>18954545.45454545</v>
+        <v>18200000</v>
       </c>
       <c r="AN92" t="n">
-        <v>81.54545454545455</v>
+        <v>81.3</v>
       </c>
       <c r="AO92" t="n">
         <v>25.45833333333333</v>
@@ -20679,40 +20787,40 @@
         <v>85.27272727272727</v>
       </c>
       <c r="AI93" t="n">
-        <v>26.63636363636364</v>
+        <v>26.1</v>
       </c>
       <c r="AJ93" t="n">
-        <v>181.1818181818182</v>
+        <v>180.8</v>
       </c>
       <c r="AK93" t="n">
-        <v>1.636363636363636</v>
+        <v>1.6</v>
       </c>
       <c r="AL93" t="n">
-        <v>80.18181818181819</v>
+        <v>80.8</v>
       </c>
       <c r="AM93" t="n">
-        <v>29927272.72727273</v>
+        <v>32650000</v>
       </c>
       <c r="AN93" t="n">
-        <v>81.72727272727273</v>
+        <v>82.5</v>
       </c>
       <c r="AO93" t="n">
-        <v>26.52</v>
+        <v>25.5</v>
       </c>
       <c r="AP93" t="n">
-        <v>182.32</v>
+        <v>184.1363636363636</v>
       </c>
       <c r="AQ93" t="n">
-        <v>2.04</v>
+        <v>1.772727272727273</v>
       </c>
       <c r="AR93" t="n">
-        <v>78.88</v>
+        <v>78.72727272727273</v>
       </c>
       <c r="AS93" t="n">
-        <v>24640000</v>
+        <v>26568181.81818182</v>
       </c>
       <c r="AT93" t="n">
-        <v>81.8</v>
+        <v>82.04545454545455</v>
       </c>
       <c r="AU93" t="n">
         <v>25.5</v>
@@ -20867,40 +20975,40 @@
         </is>
       </c>
       <c r="AC94" t="n">
-        <v>27.9</v>
+        <v>27.81818181818182</v>
       </c>
       <c r="AD94" t="n">
-        <v>184.1</v>
+        <v>184.6363636363636</v>
       </c>
       <c r="AE94" t="n">
-        <v>2.4</v>
+        <v>2.363636363636364</v>
       </c>
       <c r="AF94" t="n">
-        <v>78.7</v>
+        <v>79.09090909090909</v>
       </c>
       <c r="AG94" t="n">
-        <v>18680000</v>
+        <v>20300000</v>
       </c>
       <c r="AH94" t="n">
-        <v>79.5</v>
+        <v>79.90909090909091</v>
       </c>
       <c r="AI94" t="n">
-        <v>27</v>
+        <v>27.2</v>
       </c>
       <c r="AJ94" t="n">
-        <v>185.4545454545455</v>
+        <v>186.7</v>
       </c>
       <c r="AK94" t="n">
-        <v>1.272727272727273</v>
+        <v>1.3</v>
       </c>
       <c r="AL94" t="n">
-        <v>73.90909090909091</v>
+        <v>73.8</v>
       </c>
       <c r="AM94" t="n">
-        <v>5445454.545454546</v>
+        <v>5240000</v>
       </c>
       <c r="AN94" t="n">
-        <v>76.36363636363636</v>
+        <v>76.2</v>
       </c>
       <c r="AO94" t="n">
         <v>24.2962962962963</v>
@@ -21141,22 +21249,22 @@
         <v>75.5925925925926</v>
       </c>
       <c r="AU95" t="n">
-        <v>26.15384615384615</v>
+        <v>25.92</v>
       </c>
       <c r="AV95" t="n">
-        <v>184.1538461538462</v>
+        <v>184.6</v>
       </c>
       <c r="AW95" t="n">
-        <v>1.692307692307692</v>
+        <v>1.64</v>
       </c>
       <c r="AX95" t="n">
-        <v>77.5</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="AY95" t="n">
-        <v>16166346.15384615</v>
+        <v>16657000</v>
       </c>
       <c r="AZ95" t="n">
-        <v>81.80769230769231</v>
+        <v>82.08</v>
       </c>
       <c r="BA95" t="n">
         <v>27.66666666666667</v>
@@ -21301,21 +21409,25 @@
           <t>Iw7eKK25</t>
         </is>
       </c>
-      <c r="AB96" t="inlineStr"/>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
       <c r="AC96" t="n">
-        <v>25.3</v>
+        <v>25.33333333333333</v>
       </c>
       <c r="AD96" t="n">
-        <v>184.9</v>
+        <v>186</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.9</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="AF96" t="n">
-        <v>81.2</v>
+        <v>80.88888888888889</v>
       </c>
       <c r="AG96" t="n">
-        <v>33850000</v>
+        <v>32000000</v>
       </c>
       <c r="AH96" t="n">
         <v>85</v>
@@ -21339,22 +21451,22 @@
         <v>78.90909090909091</v>
       </c>
       <c r="AO96" t="n">
-        <v>24.43478260869565</v>
+        <v>24.73913043478261</v>
       </c>
       <c r="AP96" t="n">
-        <v>184.3913043478261</v>
+        <v>184.6086956521739</v>
       </c>
       <c r="AQ96" t="n">
         <v>1.739130434782609</v>
       </c>
       <c r="AR96" t="n">
-        <v>76.34782608695652</v>
+        <v>76.04347826086956</v>
       </c>
       <c r="AS96" t="n">
-        <v>17332608.69565218</v>
+        <v>15441304.34782609</v>
       </c>
       <c r="AT96" t="n">
-        <v>81.78260869565217</v>
+        <v>81.43478260869566</v>
       </c>
       <c r="AU96" t="n">
         <v>26.32</v>
@@ -21523,76 +21635,76 @@
         </is>
       </c>
       <c r="AC97" t="n">
-        <v>24.27272727272727</v>
+        <v>24.1</v>
       </c>
       <c r="AD97" t="n">
-        <v>184.2727272727273</v>
+        <v>185.4</v>
       </c>
       <c r="AE97" t="n">
         <v>1</v>
       </c>
       <c r="AF97" t="n">
-        <v>71.18181818181819</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="AG97" t="n">
-        <v>4536363.636363637</v>
+        <v>4870000</v>
       </c>
       <c r="AH97" t="n">
-        <v>76.36363636363636</v>
+        <v>77.2</v>
       </c>
       <c r="AI97" t="n">
-        <v>27.36363636363636</v>
+        <v>27.1</v>
       </c>
       <c r="AJ97" t="n">
-        <v>183</v>
+        <v>183.8</v>
       </c>
       <c r="AK97" t="n">
-        <v>1.909090909090909</v>
+        <v>1.8</v>
       </c>
       <c r="AL97" t="n">
-        <v>78.81818181818181</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="AM97" t="n">
-        <v>20700000</v>
+        <v>20270000</v>
       </c>
       <c r="AN97" t="n">
-        <v>80.72727272727273</v>
+        <v>80.7</v>
       </c>
       <c r="AO97" t="n">
-        <v>23.17857142857143</v>
+        <v>23.07407407407407</v>
       </c>
       <c r="AP97" t="n">
-        <v>184.0357142857143</v>
+        <v>184.4444444444445</v>
       </c>
       <c r="AQ97" t="n">
         <v>1</v>
       </c>
       <c r="AR97" t="n">
-        <v>67.89285714285714</v>
+        <v>67.92592592592592</v>
       </c>
       <c r="AS97" t="n">
-        <v>2329464.285714286</v>
+        <v>2371296.296296296</v>
       </c>
       <c r="AT97" t="n">
-        <v>74.75</v>
+        <v>75</v>
       </c>
       <c r="AU97" t="n">
-        <v>26.48</v>
+        <v>26.47826086956522</v>
       </c>
       <c r="AV97" t="n">
-        <v>180.84</v>
+        <v>181.1304347826087</v>
       </c>
       <c r="AW97" t="n">
-        <v>1.88</v>
+        <v>1.869565217391304</v>
       </c>
       <c r="AX97" t="n">
-        <v>75.95999999999999</v>
+        <v>76.26086956521739</v>
       </c>
       <c r="AY97" t="n">
-        <v>15050400</v>
+        <v>15233043.47826087</v>
       </c>
       <c r="AZ97" t="n">
-        <v>78.72</v>
+        <v>79.04347826086956</v>
       </c>
       <c r="BA97" t="n">
         <v>23.5</v>
@@ -21737,24 +21849,28 @@
           <t>69Dxbc61</t>
         </is>
       </c>
-      <c r="AB98" t="inlineStr"/>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
       <c r="AC98" t="n">
-        <v>25.88888888888889</v>
+        <v>26.9</v>
       </c>
       <c r="AD98" t="n">
-        <v>183.3333333333333</v>
+        <v>183</v>
       </c>
       <c r="AE98" t="n">
-        <v>1.111111111111111</v>
+        <v>1.3</v>
       </c>
       <c r="AF98" t="n">
-        <v>72.11111111111111</v>
+        <v>72.7</v>
       </c>
       <c r="AG98" t="n">
-        <v>3550000</v>
+        <v>3675000</v>
       </c>
       <c r="AH98" t="n">
-        <v>76</v>
+        <v>76.2</v>
       </c>
       <c r="AI98" t="n">
         <v>24.72727272727273</v>
@@ -21948,29 +22064,33 @@
       <c r="Z99" t="n">
         <v>20232024</v>
       </c>
-      <c r="AA99" t="inlineStr"/>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
       <c r="AB99" t="inlineStr">
         <is>
           <t>69Dxbc61</t>
         </is>
       </c>
       <c r="AC99" t="n">
-        <v>24</v>
+        <v>24.5</v>
       </c>
       <c r="AD99" t="n">
-        <v>182.8888888888889</v>
+        <v>183.9</v>
       </c>
       <c r="AE99" t="n">
-        <v>1.222222222222222</v>
+        <v>1.3</v>
       </c>
       <c r="AF99" t="n">
-        <v>73.33333333333333</v>
+        <v>73.5</v>
       </c>
       <c r="AG99" t="n">
-        <v>8833333.333333334</v>
+        <v>8420000</v>
       </c>
       <c r="AH99" t="n">
-        <v>79.44444444444444</v>
+        <v>79</v>
       </c>
       <c r="AI99" t="n">
         <v>26.72727272727273</v>
@@ -22193,58 +22313,58 @@
         <v>76.09090909090909</v>
       </c>
       <c r="AI100" t="n">
-        <v>25.63636363636364</v>
+        <v>25.2</v>
       </c>
       <c r="AJ100" t="n">
-        <v>187.1818181818182</v>
+        <v>187.7</v>
       </c>
       <c r="AK100" t="n">
-        <v>1.272727272727273</v>
+        <v>1.2</v>
       </c>
       <c r="AL100" t="n">
-        <v>75.18181818181819</v>
+        <v>75</v>
       </c>
       <c r="AM100" t="n">
-        <v>12218181.81818182</v>
+        <v>12590000</v>
       </c>
       <c r="AN100" t="n">
-        <v>79.18181818181819</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="AO100" t="n">
-        <v>24.92307692307692</v>
+        <v>25.18518518518519</v>
       </c>
       <c r="AP100" t="n">
-        <v>183.8076923076923</v>
+        <v>184.0740740740741</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.076923076923077</v>
+        <v>1.074074074074074</v>
       </c>
       <c r="AR100" t="n">
-        <v>70.80769230769231</v>
+        <v>71.07407407407408</v>
       </c>
       <c r="AS100" t="n">
-        <v>3180769.230769231</v>
+        <v>3322222.222222222</v>
       </c>
       <c r="AT100" t="n">
-        <v>75.34615384615384</v>
+        <v>75.44444444444444</v>
       </c>
       <c r="AU100" t="n">
-        <v>23.36842105263158</v>
+        <v>23.86363636363636</v>
       </c>
       <c r="AV100" t="n">
-        <v>186.7894736842105</v>
+        <v>185.8636363636364</v>
       </c>
       <c r="AW100" t="n">
-        <v>1.210526315789474</v>
+        <v>1.181818181818182</v>
       </c>
       <c r="AX100" t="n">
-        <v>71.21052631578948</v>
+        <v>72.13636363636364</v>
       </c>
       <c r="AY100" t="n">
-        <v>5617105.263157895</v>
+        <v>6896590.909090909</v>
       </c>
       <c r="AZ100" t="n">
-        <v>77.10526315789474</v>
+        <v>77.22727272727273</v>
       </c>
       <c r="BA100" t="n">
         <v>25.33333333333333</v>
